--- a/saitama-kobun4/gas/古典クエスト_問題マスター.xlsx
+++ b/saitama-kobun4/gas/古典クエスト_問題マスター.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -551,182 +551,234 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>本文HTML  : 縦書き表示される本文。&lt;p&gt;で段落、傍線部は</t>
+          <t>本文HTML  : 縦書き表示される本文。書き方は下の【本文HTMLの書き方】を参照。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            &lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;本文&lt;/span&gt; の形で囲む。</t>
+          <t>注        : （注）欄。&lt;b&gt;語&lt;/b&gt;＝意味。 を「　」区切りで並べる。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>注        : （注）欄。&lt;b&gt;語&lt;/b&gt;＝意味。 を「　」区切りで並べる。</t>
+          <t>現代語訳  : 採点後に開く全文の現代語訳。&lt;p&gt;で段落。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>現代語訳  : 採点後に開く現代語訳。&lt;p&gt;で段落。</t>
+          <t>表示順    : ステージの並び順（小さい順）。空欄なら本文IDの順。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>表示順    : ステージの並び順（小さい順）。空欄なら本文IDの順。</t>
+          <t>公開      : TRUE で出題対象。FALSE にすると一覧から外れる。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>公開      : TRUE で出題対象。FALSE にすると一覧から外れる。</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>【本文HTMLの書き方】</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>【設問シートの列】</t>
+          <t>段落      : &lt;p&gt;…&lt;/p&gt; で囲む。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>問題ID    : S01-1 など。全体で重複しないこと（誤答記録の追跡に使う）。</t>
+          <t>傍線部    : &lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;本文&lt;/span&gt;</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>本文ID    : 本文シートの本文IDと一致させる。</t>
+          <t>口語訳    : 入試と同じく、難しい箇所だけ本文中に小さく訳を添えられる。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>問番号    : 問1〜問4。画面の見出しになる。</t>
+          <t xml:space="preserve">            &lt;span class="gl"&gt;古文の語句&lt;i&gt;（口語訳）&lt;/i&gt;&lt;/span&gt;</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>設問タイプ: 仮名遣い / 主語・語意 / 内容理解 / 要旨・話し合い のいずれか。</t>
+          <t xml:space="preserve">            のように書くと、古文のすぐあとに小さな字で訳が出る。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            この4つ以外を書くと弱点分析に集計されない。</t>
+          <t xml:space="preserve">            画面の「口語訳あり／なし」ボタンで生徒が消すこともできる。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>設問文    : 問いの文。&lt;span class="kb"&gt;…&lt;/span&gt; で傍線部を示せる。</t>
+          <t xml:space="preserve">            ※設問で問われている箇所には付けないこと（答えが出てしまう）。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>話し合い文: 先生と生徒の会話。空欄可。&lt;span class="sp"&gt;先生&lt;/span&gt;「…」&lt;br&gt; の形。</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            空欄部分は &lt;span class="blank"&gt;　　&lt;/span&gt; と書く。</t>
+          <t>【設問シートの列】</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>選択肢ア〜エ : 4つすべて埋めること（空欄があると出題されない）。</t>
+          <t>問題ID    : S01-1 など。全体で重複しないこと（誤答記録の追跡に使う）。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>正解      : ア／イ／ウ／エ のいずれか。</t>
+          <t>本文ID    : 本文シートの本文IDと一致させる。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>解説      : 採点後に表示される。&lt;b&gt;…&lt;/b&gt; で強調できる。</t>
+          <t>問番号    : 問1〜問4。画面の見出しになる。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>配点      : 既定3点。合計が12点になるようにする。</t>
+          <t>設問タイプ: 仮名遣い / 主語・語意 / 内容理解 / 要旨・話し合い のいずれか。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            この4つ以外を書くと弱点分析に集計されない。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>【問題を追加・修正したら】</t>
+          <t>設問文    : 問いの文。&lt;span class="kb"&gt;…&lt;/span&gt; で傍線部を示せる。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>集計スプレッドシートのメニュー「古典クエスト管理」→</t>
+          <t>話し合い文: 先生と生徒の会話。空欄可。&lt;span class="sp"&gt;先生&lt;/span&gt;「…」&lt;br&gt; の形。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>「問題プールのキャッシュをクリア」を実行すると、次回出題から反映されます。</t>
+          <t xml:space="preserve">            空欄部分は &lt;span class="blank"&gt;　　&lt;/span&gt; と書く。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>選択肢ア〜エ : 4つすべて埋めること（空欄があると出題されない）。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>【出典について】</t>
+          <t>正解      : ア／イ／ウ／エ のいずれか。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>本文は『宇治拾遺物語』『徒然草』『十訓抄』『沙石集』『伊曽保物語』から採り、</t>
+          <t>解説      : 採点後に表示される。&lt;b&gt;…&lt;/b&gt; で強調できる。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>配点      : 1問3点。1ステージの合計が12点になるようにする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>【問題を追加・修正したら】</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>集計スプレッドシートのメニュー「⚙ 古典クエスト管理」→</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>「問題プールのキャッシュをクリア」を実行すると、次回出題から反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>【出典について】</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>本文は『宇治拾遺物語』『徒然草』『十訓抄』『沙石集』『伊曽保物語』から採り、</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>読みやすさのため表記を一部改めています。設問・解説はオリジナルです。</t>
         </is>
@@ -827,7 +879,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;これも今は昔、絵仏師良秀といふありけり。家の隣より火出で来て、風おしおほひてせめければ、逃げ出でて大路へ出でにけり。人の書かする仏もおはしけり。また、衣着ぬ妻子なども、さながら内にありけり。それも知らず、ただ逃げ出でたるをことにして、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;向かひ&lt;/span&gt;のつらに立てり。&lt;/p&gt;&lt;p&gt;見れば、すでにわが家に移りて、煙・炎くゆりけるまで、おほかた、向かひのつらに立ちて眺めければ、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;あさましきこと&lt;/span&gt;」とて、人ども来とぶらひけれど、騒がず。「いかに」と人言ひければ、向かひに立ちて、家の焼くるを見て、うちうなづきて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;時々笑ひけり&lt;/span&gt;。「あはれ、しつるせうとくかな。年ごろはわろく書きけるものかな」と言ふ時に、とぶらひに来たる者ども、「こはいかに、かくては立ち給へるぞ。もののつき給へるか」と言ひければ、「なんでふ物のつくべきぞ。年ごろ不動尊の火焰をあしく書きけるなり。今見れば、かうこそ燃えけれと、心得つるなり。これこそせうとくよ」と言ひて、あざ笑ひてこそ立てりけれ。&lt;/p&gt;&lt;p&gt;その後にや、良秀がよぢり不動とて、今に人々めで合へり。&lt;/p&gt;</t>
+          <t>&lt;p&gt;これも今は昔、絵仏師良秀といふありけり。家の隣より火出で来て、風おしおほひてせめければ、逃げ出でて大路へ出でにけり。&lt;span class="gl"&gt;人の書かする仏もおはしけり&lt;i&gt;（人が注文して描かせている仏の絵もあった）&lt;/i&gt;&lt;/span&gt;。また、衣着ぬ妻子なども、&lt;span class="gl"&gt;さながら内にありけり&lt;i&gt;（そのまま家の中にいた）&lt;/i&gt;&lt;/span&gt;。それも知らず、&lt;span class="gl"&gt;ただ逃げ出でたるをことにして&lt;i&gt;（自分が逃げ出したことだけをよいことにして）&lt;/i&gt;&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;向かひ&lt;/span&gt;のつらに立てり。&lt;/p&gt;&lt;p&gt;見れば、すでにわが家に移りて、&lt;span class="gl"&gt;煙・炎くゆりけるまで&lt;i&gt;（煙や炎がくすぶり出すまで）&lt;/i&gt;&lt;/span&gt;、おほかた、向かひのつらに立ちて眺めければ、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;あさましきこと&lt;/span&gt;」とて、人ども来とぶらひけれど、騒がず。「いかに」と人言ひければ、向かひに立ちて、家の焼くるを見て、うちうなづきて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;時々笑ひけり&lt;/span&gt;。「あはれ、しつるせうとくかな。年ごろはわろく書きけるものかな」と言ふ時に、とぶらひに来たる者ども、「こはいかに、かくては立ち給へるぞ。&lt;span class="gl"&gt;もののつき給へるか&lt;i&gt;（物の怪でも取りついたのか）&lt;/i&gt;&lt;/span&gt;」と言ひければ、「なんでふ物のつくべきぞ。年ごろ不動尊の火焰をあしく書きけるなり。今見れば、かうこそ燃えけれと、心得つるなり。これこそせうとくよ」と言ひて、あざ笑ひてこそ立てりけれ。&lt;/p&gt;&lt;p&gt;その後にや、良秀がよぢり不動とて、&lt;span class="gl"&gt;今に人々めで合へり&lt;i&gt;（今でも人々がほめ合っている）&lt;/i&gt;&lt;/span&gt;。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -872,7 +924,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;和泉式部、保昌が妻にて丹後に下りけるほどに、京に歌合ありけるに、小式部内侍、歌よみにとられてよみけるを、定頼中納言たはぶれて、小式部内侍ありけるに、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;丹後へつかはしける人は参りたりや。いかに心もとなくおぼすらむ&lt;/span&gt;」と言ひて、局の前を過ぎられけるを、御簾よりなから出でて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;わづかに&lt;/span&gt;直衣の袖をひかへて、&lt;/p&gt;&lt;p&gt;　大江山いくのの道の遠ければまだふみもみず天の橋立&lt;/p&gt;&lt;p&gt;とよみかけけり。思はずにあさましくて、「こはいかに、かかるやうやはある」とばかり言ひて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;返しにも及ばず、袖を引き放ちて逃げられけり&lt;/span&gt;。小式部、これより歌よみの世おぼえ出で来にけり。&lt;/p&gt;</t>
+          <t>&lt;p&gt;和泉式部、&lt;span class="gl"&gt;保昌が妻にて丹後に下りけるほどに&lt;i&gt;（保昌の妻として丹後に下っていたころ）&lt;/i&gt;&lt;/span&gt;、京に歌合ありけるに、小式部内侍、&lt;span class="gl"&gt;歌よみにとられてよみけるを&lt;i&gt;（歌のよみ手に選ばれて歌をよんだが）&lt;/i&gt;&lt;/span&gt;、定頼中納言たはぶれて、小式部内侍ありけるに、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;丹後へつかはしける人は参りたりや。いかに心もとなくおぼすらむ&lt;/span&gt;」と言ひて、&lt;span class="gl"&gt;局の前を過ぎられけるを&lt;i&gt;（部屋の前を通り過ぎなさったのを）&lt;/i&gt;&lt;/span&gt;、&lt;span class="gl"&gt;御簾よりなから出でて&lt;i&gt;（御簾から身を半分ほど乗り出して）&lt;/i&gt;&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;わづかに&lt;/span&gt;&lt;span class="gl"&gt;直衣の袖をひかへて&lt;i&gt;（直衣の袖を引きとめて）&lt;/i&gt;&lt;/span&gt;、&lt;/p&gt;&lt;p&gt;　大江山いくのの道の遠ければまだふみもみず天の橋立&lt;/p&gt;&lt;p&gt;とよみかけけり。思はずにあさましくて、「こはいかに、かかるやうやはある」とばかり言ひて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;返しにも及ばず、袖を引き放ちて逃げられけり&lt;/span&gt;。小式部、これより&lt;span class="gl"&gt;歌よみの世おぼえ出で来にけり&lt;i&gt;（歌よみとしての評判が世に立つようになった）&lt;/i&gt;&lt;/span&gt;。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -917,7 +969,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;高名の木登りといひしをのこ、人を掟てて、高き木に登せて梢を切らせしに、いと&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;危ふく&lt;/span&gt;見えしほどは言ふこともなくて、下るるときに、軒たけばかりになりて、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;あやまちすな。心して降りよ&lt;/span&gt;」と言葉をかけ侍りしを、「かばかりになりては、飛び降るとも降りなん。いかにかく言ふぞ」と申し侍りしかば、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;その事に候ふ。目くるめき、枝危ふきほどは、おのれが恐れ侍れば申さず。あやまちは、安き所になりて、必ず仕る事に候ふ&lt;/span&gt;」と言ふ。&lt;/p&gt;&lt;p&gt;あやしき下臈なれども、聖人の戒めにかなへり。鞠も、難き所を蹴出して後、安く思へば、必ず落つと侍るやらん。&lt;/p&gt;</t>
+          <t>&lt;p&gt;高名の木登りといひしをのこ、&lt;span class="gl"&gt;人を掟てて、高き木に登せて梢を切らせしに&lt;i&gt;（人に指図して高い木に登らせ、枝の先を切らせたときに）&lt;/i&gt;&lt;/span&gt;、いと&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;危ふく&lt;/span&gt;見えしほどは&lt;span class="gl"&gt;言ふこともなくて&lt;i&gt;（何も言わないで）&lt;/i&gt;&lt;/span&gt;、下るるときに、軒たけばかりになりて、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;あやまちすな。心して降りよ&lt;/span&gt;」と言葉をかけ侍りしを、「&lt;span class="gl"&gt;かばかりになりては、飛び降るとも降りなん&lt;i&gt;（これくらいの高さになれば、飛び降りても降りられるだろう）&lt;/i&gt;&lt;/span&gt;。いかにかく言ふぞ」と申し侍りしかば、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;&lt;span class="gl"&gt;その事に候ふ&lt;i&gt;（そのことでございます）&lt;/i&gt;&lt;/span&gt;。目くるめき、枝危ふきほどは、おのれが恐れ侍れば申さず。あやまちは、安き所になりて、必ず仕る事に候ふ&lt;/span&gt;」と言ふ。&lt;/p&gt;&lt;p&gt;あやしき下臈なれども、聖人の戒めにかなへり。鞠も、&lt;span class="gl"&gt;難き所を蹴出して後&lt;i&gt;（難しい所を蹴り出したあと）&lt;/i&gt;&lt;/span&gt;、安く思へば、必ず落つと侍るやらん。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -962,7 +1014,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;仁和寺にある法師、年寄るまで石清水を拝まざりければ、心うく覚えて、あるとき思ひ立ちて、ただひとり、徒歩より&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;まうでけり&lt;/span&gt;。極楽寺・高良などを拝みて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;かばかりと心得て帰りにけり&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;さて、かたへの人にあひて、「年ごろ思ひつること、果たし侍りぬ。聞きしにも過ぎて尊くこそおはしけれ。&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;そも、参りたる人ごとに山へ登りしは、何事かありけん、ゆかしかりしかど、神へ参るこそ本意なれと思ひて、山までは見ず&lt;/span&gt;」とぞ言ひける。&lt;/p&gt;&lt;p&gt;少しのことにも、先達はあらまほしきことなり。&lt;/p&gt;</t>
+          <t>&lt;p&gt;仁和寺にある法師、&lt;span class="gl"&gt;年寄るまで石清水を拝まざりければ&lt;i&gt;（年をとるまで石清水八幡宮を参拝しなかったので）&lt;/i&gt;&lt;/span&gt;、心うく覚えて、あるとき思ひ立ちて、ただひとり、徒歩より&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;まうでけり&lt;/span&gt;。&lt;span class="gl"&gt;極楽寺・高良などを拝みて&lt;i&gt;（極楽寺や高良神社などを拝んで）&lt;/i&gt;&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;かばかりと心得て帰りにけり&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;さて、かたへの人にあひて、「&lt;span class="gl"&gt;年ごろ思ひつること、果たし侍りぬ&lt;i&gt;（長年思っていたことを果たしました）&lt;/i&gt;&lt;/span&gt;。&lt;span class="gl"&gt;聞きしにも過ぎて尊くこそおはしけれ&lt;i&gt;（聞いていた以上に尊くていらっしゃった）&lt;/i&gt;&lt;/span&gt;。&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;そも、参りたる人ごとに山へ登りしは、何事かありけん、ゆかしかりしかど、神へ参るこそ本意なれと思ひて、山までは見ず&lt;/span&gt;」とぞ言ひける。&lt;/p&gt;&lt;p&gt;少しのことにも、先達はあらまほしきことなり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1007,7 +1059,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;これも今は昔、比叡の山に児ありけり。僧たち、宵のつれづれに、「いざ、かいもちひせむ」と言ひけるを、この児、心寄せに聞きけり。さりとて、し出ださむを待ちて寝ざらむも、わろかりなむと思ひて、片方に寄りて、寝たるよしにて、出で来るを待ちけるに、すでにし出だしたるさまにて、ひしめき合ひたり。&lt;/p&gt;&lt;p&gt;この児、さだめて驚かさむずらむと待ちゐたるに、僧の、「もの申しさぶらはむ。驚かせたまへ」と言ふを、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;うれしとは思へども、ただ一度に&lt;span class="mk"&gt;②&lt;/span&gt;いらへむも、待ちけるかともぞ思ふ&lt;/span&gt;とて、今一声呼ばれていらへむと、念じて寝たるほどに、「や、な起こしたてまつりそ。幼き人は寝入りたまひにけり」と言ふ声のしければ、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;あな、わびし&lt;/span&gt;と思ひて、いま一度起こせかしと、思ひ寝に聞けば、ひしひしと、ただ食ひに食ふ音のしければ、ずちなくて、無期ののちに、「えい」といらへたりければ、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;僧たち笑ふこと限りなし&lt;/span&gt;。&lt;/p&gt;</t>
+          <t>&lt;p&gt;これも今は昔、比叡の山に児ありけり。僧たち、宵のつれづれに、「いざ、かいもちひせむ」と言ひけるを、この児、心寄せに聞きけり。&lt;span class="gl"&gt;さりとて、し出ださむを待ちて寝ざらむも、わろかりなむと思ひて&lt;i&gt;（とはいっても、作り上げるのを待って寝ないでいるのもみっともないだろうと思って）&lt;/i&gt;&lt;/span&gt;、&lt;span class="gl"&gt;片方に寄りて、寝たるよしにて&lt;i&gt;（部屋の片隅に寄って、寝たふりをして）&lt;/i&gt;&lt;/span&gt;、出で来るを待ちけるに、&lt;span class="gl"&gt;すでにし出だしたるさまにて&lt;i&gt;（もう作り上げた様子で）&lt;/i&gt;&lt;/span&gt;、ひしめき合ひたり。&lt;/p&gt;&lt;p&gt;この児、&lt;span class="gl"&gt;さだめて驚かさむずらむと待ちゐたるに&lt;i&gt;（きっと起こしてくれるだろうと待っていたところ）&lt;/i&gt;&lt;/span&gt;、僧の、「もの申しさぶらはむ。驚かせたまへ」と言ふを、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;うれしとは思へども、ただ一度に&lt;span class="mk"&gt;②&lt;/span&gt;いらへむも、待ちけるかともぞ思ふ&lt;/span&gt;とて、今一声呼ばれていらへむと、念じて寝たるほどに、「や、な起こしたてまつりそ。幼き人は寝入りたまひにけり」と言ふ声のしければ、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;あな、わびし&lt;/span&gt;と思ひて、いま一度起こせかしと、&lt;span class="gl"&gt;思ひ寝に聞けば&lt;i&gt;（そう思いながら寝て聞いていると）&lt;/i&gt;&lt;/span&gt;、&lt;span class="gl"&gt;ひしひしと、ただ食ひに食ふ音のしければ&lt;i&gt;（むしゃむしゃと、ひたすら食べる音がしたので）&lt;/i&gt;&lt;/span&gt;、ずちなくて、無期ののちに、「えい」といらへたりければ、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;僧たち笑ふこと限りなし&lt;/span&gt;。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -1052,7 +1104,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;ある川のほとりに、蟻遊ぶことありけり。にはかに水かさまさりて、かの蟻を誘ひ流る。浮きぬ沈みぬする所に、鳩、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;こずゑ&lt;/span&gt;よりこれを見て、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;あはれなるありさまかな&lt;/span&gt;」と、こずゑをちと食ひ切つて川の中へ落としければ、蟻これに乗りて、渚に上がりぬ。&lt;/p&gt;&lt;p&gt;かかりける所に、ある人、竿の先に鳥もちを付けて、かの鳩をささんとす。&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;蟻、心に思ふやう、「ただ今の恩を送らん」と思ひ、かの人の足にしつかと食ひつきければ&lt;/span&gt;、おびえあがつて、竿をかしこに投げ捨てけり。鳩これを悟りて、はるかの空へぞ逃げ延びにける。&lt;/p&gt;&lt;p&gt;そのごとく、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;人の恩を受けたらん者は、いかさまにもその報いをなすべきなり&lt;/span&gt;。&lt;/p&gt;</t>
+          <t>&lt;p&gt;ある川のほとりに、蟻遊ぶことありけり。&lt;span class="gl"&gt;にはかに水かさまさりて、かの蟻を誘ひ流る&lt;i&gt;（急に水かさが増して、その蟻をさらって流す）&lt;/i&gt;&lt;/span&gt;。&lt;span class="gl"&gt;浮きぬ沈みぬする所に&lt;i&gt;（浮いたり沈んだりしているところに）&lt;/i&gt;&lt;/span&gt;、鳩、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;こずゑ&lt;/span&gt;よりこれを見て、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;あはれなるありさまかな&lt;/span&gt;」と、こずゑ&lt;span class="gl"&gt;をちと食ひ切つて川の中へ落としければ&lt;i&gt;（を少し食い切って川の中へ落としたところ）&lt;/i&gt;&lt;/span&gt;、&lt;span class="gl"&gt;蟻これに乗りて、渚に上がりぬ&lt;i&gt;（蟻はこれに乗って、水ぎわに上がった）&lt;/i&gt;&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;かかりける所に、ある人、竿の先に鳥もちを付けて、かの鳩をささんとす。&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;蟻、心に思ふやう、「ただ今の恩を送らん」と思ひ、かの人の足にしつかと食ひつきければ&lt;/span&gt;、おびえあがつて、&lt;span class="gl"&gt;竿をかしこに投げ捨てけり&lt;i&gt;（竿をあちらへ投げ捨ててしまった）&lt;/i&gt;&lt;/span&gt;。鳩これを悟りて、はるかの空へぞ逃げ延びにける。&lt;/p&gt;&lt;p&gt;そのごとく、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;人の恩を受けたらん者は、いかさまにもその報いをなすべきなり&lt;/span&gt;。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1097,7 +1149,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;今は昔、小野篁といふ人おはしけり。嵯峨の帝の御時に、内裏に札を立てたりけるに、「無悪善」と書きたりけり。帝、篁に、「読め」と仰せられたりければ、「読みは読み候ひなん。されど、恐れにて候へば、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;え申し候はじ&lt;/span&gt;」と奏しければ、「ただ申せ」と、たびたび仰せられければ、「さがなくてよからんと申して候ふぞ。されば、君を呪ひ参らせて候ふなり」と申しければ、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;おのれ放ちては、誰か書かん&lt;/span&gt;」と仰せられければ、「さればこそ、申し候はじとは申して候ひつれ」と申すに、帝、「さて、何も書きたらん物は、読みてんや」と仰せられければ、「何にても読み候ひなん」と申しければ、片仮名の子文字を十二書かせ&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;給ひて&lt;/span&gt;、「読め」と仰せられければ、「ねこの子のこねこ、ししの子のこじし」と読みたりければ、帝、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;ほほ笑ませ給ひて、事なくてやみにけり&lt;/span&gt;。&lt;/p&gt;</t>
+          <t>&lt;p&gt;今は昔、小野篁といふ人おはしけり。嵯峨の帝の御時に、&lt;span class="gl"&gt;内裏に札を立てたりけるに&lt;i&gt;（内裏に札が立ててあったが）&lt;/i&gt;&lt;/span&gt;、「無悪善」と書きたりけり。帝、篁に、「読め」と仰せられたりければ、「&lt;span class="gl"&gt;読みは読み候ひなん&lt;i&gt;（読むことは読めるでしょう）&lt;/i&gt;&lt;/span&gt;。されど、恐れにて候へば、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;え申し候はじ&lt;/span&gt;」と奏しければ、&lt;span class="gl"&gt;「ただ申せ」と、たびたび仰せられければ&lt;i&gt;（「かまわないから申せ」と、たびたびおっしゃったので）&lt;/i&gt;&lt;/span&gt;、「さがなくてよからんと申して候ふぞ。されば、君を呪ひ参らせて候ふなり」と申しければ、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;おのれ放ちては、誰か書かん&lt;/span&gt;」と仰せられければ、「&lt;span class="gl"&gt;さればこそ、申し候はじとは申して候ひつれ&lt;i&gt;（だからこそ、申し上げますまいと申したのでございます）&lt;/i&gt;&lt;/span&gt;」と申すに、帝、「&lt;span class="gl"&gt;さて、何も書きたらん物は、読みてんや&lt;i&gt;（それでは、どんなものが書いてあっても読めるのか）&lt;/i&gt;&lt;/span&gt;」と仰せられければ、「何にても読み候ひなん」と申しければ、片仮名の子文字を十二書かせ&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;給ひて&lt;/span&gt;、「読め」と仰せられければ、「ねこの子のこねこ、ししの子のこじし」と読みたりければ、帝、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;ほほ笑ませ給ひて、事なくてやみにけり&lt;/span&gt;。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1142,7 +1194,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;ある人、弓射ることを習ふに、諸矢をたばさみて的に向かふ。師の&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;言はく&lt;/span&gt;、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;初心の人、二つの矢を持つことなかれ&lt;/span&gt;。後の矢を頼みて、初めの矢に等閑の心あり。毎度ただ得失なく、この一矢に定むべしと思へ」と言ふ。わづかに二つの矢、師の前にて一つをおろかにせんと思はんや。&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;懈怠の心、みづから知らずといへども、師これを知る&lt;/span&gt;。この戒め、万事にわたるべし。&lt;/p&gt;&lt;p&gt;道を学する人、夕べには朝あらんことを思ひ、朝には夕べあらんことを思ひて、重ねてねんごろに修せんことを期す。いはんや一刹那のうちにおいて、懈怠の心あることを知らんや。なんぞ、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;ただ今の一念において、直ちにすることの、はなはだ難き&lt;/span&gt;。&lt;/p&gt;</t>
+          <t>&lt;p&gt;ある人、弓射ることを習ふに、諸矢をたばさみて的に向かふ。師の&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;言はく&lt;/span&gt;、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;初心の人、二つの矢を持つことなかれ&lt;/span&gt;。後の矢を頼みて、初めの矢に等閑の心あり。&lt;span class="gl"&gt;毎度ただ得失なく、この一矢に定むべしと思へ&lt;i&gt;（毎回ただ当たり外れを考えず、この一本の矢で決めようと思え）&lt;/i&gt;&lt;/span&gt;」と言ふ。&lt;span class="gl"&gt;わづかに二つの矢、師の前にて一つをおろかにせんと思はんや&lt;i&gt;（わずか二本の矢を、師の前で一本をいいかげんにしようと思うだろうか、いや思わない）&lt;/i&gt;&lt;/span&gt;。&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;懈怠の心、みづから知らずといへども、師これを知る&lt;/span&gt;。&lt;span class="gl"&gt;この戒め、万事にわたるべし&lt;i&gt;（この戒めは、すべてのことにあてはまるはずだ）&lt;/i&gt;&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;道を学する人、&lt;span class="gl"&gt;夕べには朝あらんことを思ひ、朝には夕べあらんことを思ひて、重ねてねんごろに修せんことを期す&lt;i&gt;（夜には翌朝があると思い、朝には夕方があると思って、あらためて念入りに修行しようとあてにする）&lt;/i&gt;&lt;/span&gt;。&lt;span class="gl"&gt;いはんや一刹那のうちにおいて、懈怠の心あることを知らんや&lt;i&gt;（まして、ほんの一瞬のうちに、なまけ心があることに気づくだろうか、いや気づかない）&lt;/i&gt;&lt;/span&gt;。なんぞ、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;ただ今の一念において、直ちにすることの、はなはだ難き&lt;/span&gt;。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1187,7 +1239,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;ある山寺に、四人の僧集まりて、七日の間、無言の行をぞ始めける。一夜、風吹きて、灯明の消えたりけるに、下座の僧、こらへかねて、「火が消えたり。とく点せ」と言ふ。&lt;/p&gt;&lt;p&gt;第二の僧、これを聞きて、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;無言の行に、もの&lt;span class="mk"&gt;②&lt;/span&gt;言ふべきか&lt;/span&gt;」と、にがにがしげにとがめけり。第三の僧、「二人ながらもの言ひたり。口惜しきことなり」と言ふ。&lt;/p&gt;&lt;p&gt;上座の僧、うちうなづきて、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;われ一人こそもの言はね&lt;/span&gt;」と言ひけり。&lt;/p&gt;</t>
+          <t>&lt;p&gt;ある山寺に、四人の僧集まりて、七日の間、無言の行をぞ始めける。&lt;span class="gl"&gt;一夜、風吹きて、灯明の消えたりけるに&lt;i&gt;（ある夜、風が吹いて仏前のあかりが消えてしまったので）&lt;/i&gt;&lt;/span&gt;、下座の僧、&lt;span class="gl"&gt;こらへかねて&lt;i&gt;（こらえきれずに）&lt;/i&gt;&lt;/span&gt;、「火が消えたり。とく点せ」と言ふ。&lt;/p&gt;&lt;p&gt;第二の僧、これを聞きて、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;無言の行に、もの&lt;span class="mk"&gt;②&lt;/span&gt;言ふべきか&lt;/span&gt;」と、にがにがしげにとがめけり。第三の僧、「二人ながらもの言ひたり。口惜しきことなり」と言ふ。&lt;/p&gt;&lt;p&gt;上座の僧、うちうなづきて、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;われ一人こそもの言はね&lt;/span&gt;」と言ひけり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1232,7 +1284,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;九月二十日のころ、ある人に誘はれたてまつりて、明くるまで月見ありくこと侍りしに、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;思し出づる所ありて、案内せさせて入り給ひぬ&lt;/span&gt;。荒れたる庭の露しげきに、わざとならぬ匂ひ、しめやかにうち薫りて、忍びたるけはひ、いとものあはれなり。&lt;/p&gt;&lt;p&gt;よきほどにて出で給ひぬれど、なほ事ざまの優におぼえて、物の隠れよりしばし&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;見ゐたる&lt;/span&gt;に、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;妻戸をいま少し押し開けて、月見るけしきなり&lt;/span&gt;。やがてかけこもらましかば、口惜しからまし。&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;あとまで見る人ありとは、いかでか知らん。かやうのことは、ただ朝夕の心づかひによるべし&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;その人、ほどなく失せにけりと聞き侍りし。&lt;/p&gt;</t>
+          <t>&lt;p&gt;九月二十日のころ、&lt;span class="gl"&gt;ある人に誘はれたてまつりて、明くるまで月見ありくこと侍りしに&lt;i&gt;（ある人にお誘いいただいて、夜明けまで月を見て歩き回ることがありましたが）&lt;/i&gt;&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;思し出づる所ありて、案内せさせて入り給ひぬ&lt;/span&gt;。荒れたる庭の露しげきに、わざとならぬ匂ひ、しめやかにうち薫りて、忍びたるけはひ、&lt;span class="gl"&gt;いとものあはれなり&lt;i&gt;（たいそうしみじみと趣深い）&lt;/i&gt;&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;よきほどにて出で給ひぬれど、なほ事ざまの優におぼえて、物の隠れよりしばし&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;見ゐたる&lt;/span&gt;に、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;妻戸をいま少し押し開けて、月見るけしきなり&lt;/span&gt;。やがてかけこもらましかば、口惜しからまし。&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;あとまで見る人ありとは、いかでか知らん。かやうのことは、ただ朝夕の心づかひによるべし&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;その人、ほどなく失せにけりと聞き侍りし。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">

--- a/saitama-kobun4/gas/古典クエスト_問題マスター.xlsx
+++ b/saitama-kobun4/gas/古典クエスト_問題マスター.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -475,14 +475,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>このスプレッドシートは「古典クエスト」(GASウェブアプリ)の問題プールです。</t>
+          <t>「古典クエスト」(GASウェブアプリ)の問題プールです。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GAS側 Code.gs 冒頭の MASTER_ID に、このスプレッドシートのIDを設定すると参照されます。</t>
+          <t>Code.gs 冒頭の MASTER_ID に、このスプレッドシートのIDを設定すると参照されます。</t>
         </is>
       </c>
     </row>
@@ -492,153 +492,153 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>【シート構成】</t>
+          <t>【出題形式】埼玉県公立高校入試 大問4に合わせています</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>本文  : 大問1つ分の古文本文（1行＝1ステージ）</t>
+          <t>本文の前に現代語の前書きを置き、本文には注と、難語句の口語訳を添えます。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>設問  : 各本文にひもづく小問（1行＝1問）。すべて4択。</t>
+          <t>小問は4問・各3点の12点満点で、すべてア〜エの4択です。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　問1 傍線部Ａ〜Ｃの主語（または指示内容）の組み合わせ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>【本文シートの列】</t>
+          <t xml:space="preserve">　問2 歴史的仮名遣いを現代仮名遣いに直す（傍線部①）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>本文ID    : S01, S02 … 重複しないこと。設問シートから参照される。</t>
+          <t xml:space="preserve">　問3 傍線部②について、空欄にあてはまる内容を選ぶ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>出典      : 『宇治拾遺物語』など。画面に表示される。</t>
+          <t xml:space="preserve">　問4 先生とＡさんの会話の空欄にあてはまる内容を選ぶ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>タイトル  : ステージ名。</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>リード文  : ステージ一覧カードに出る一行紹介。</t>
+          <t>【シート構成】</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>本文HTML  : 縦書き表示される本文。書き方は下の【本文HTMLの書き方】を参照。</t>
+          <t>本文  : 大問1つ分（1行＝1ステージ）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>注        : （注）欄。&lt;b&gt;語&lt;/b&gt;＝意味。 を「　」区切りで並べる。</t>
+          <t>設問  : 各本文にひもづく小問（1行＝1問）</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>現代語訳  : 採点後に開く全文の現代語訳。&lt;p&gt;で段落。</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>表示順    : ステージの並び順（小さい順）。空欄なら本文IDの順。</t>
+          <t>【本文シートの列】</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>公開      : TRUE で出題対象。FALSE にすると一覧から外れる。</t>
+          <t>本文ID    : S01, S02 … 重複しないこと。設問シートから参照される。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>出典      : 『宇治拾遺物語』など。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>【本文HTMLの書き方】</t>
+          <t>タイトル  : ステージ名。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>段落      : &lt;p&gt;…&lt;/p&gt; で囲む。</t>
+          <t>リード文  : ステージ一覧カードに出る一行紹介。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>傍線部    : &lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;本文&lt;/span&gt;</t>
+          <t>前書き    : 本文の前に置く現代語の状況説明。入試と同じ役割。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>口語訳    : 入試と同じく、難しい箇所だけ本文中に小さく訳を添えられる。</t>
+          <t>本文HTML  : 縦書き表示される本文。書き方は下記参照。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            &lt;span class="gl"&gt;古文の語句&lt;i&gt;（口語訳）&lt;/i&gt;&lt;/span&gt;</t>
+          <t>注        : （注）欄。&lt;b&gt;語&lt;/b&gt;＝意味。 を「　」区切りで並べる。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            のように書くと、古文のすぐあとに小さな字で訳が出る。</t>
+          <t>現代語訳  : 採点後に開く全文の現代語訳。&lt;p&gt;で段落。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            画面の「口語訳あり／なし」ボタンで生徒が消すこともできる。</t>
+          <t>表示順    : ステージの並び順（小さい順）。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            ※設問で問われている箇所には付けないこと（答えが出てしまう）。</t>
+          <t>公開      : TRUE で出題対象。FALSE で一覧から外す。</t>
         </is>
       </c>
     </row>
@@ -648,139 +648,205 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>【設問シートの列】</t>
+          <t>【本文HTMLの書き方】</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>問題ID    : S01-1 など。全体で重複しないこと（誤答記録の追跡に使う）。</t>
+          <t>段落        : &lt;p&gt;…&lt;/p&gt; で囲む。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>本文ID    : 本文シートの本文IDと一致させる。</t>
+          <t>傍線部      : &lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;本文&lt;/span&gt;</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>問番号    : 問1〜問4。画面の見出しになる。</t>
+          <t xml:space="preserve">              記号は Ａ Ｂ Ｃ（問1用）と ① ②（問2・問3用）の5か所。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>設問タイプ: 仮名遣い / 主語・語意 / 内容理解 / 要旨・話し合い のいずれか。</t>
+          <t>口語訳      : &lt;ruby class="gl"&gt;古語&lt;rt&gt;訳&lt;/rt&gt;&lt;/ruby&gt;</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            この4つ以外を書くと弱点分析に集計されない。</t>
+          <t xml:space="preserve">              語句の隣（縦書きなら左側）に小さく訳が出る。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>設問文    : 問いの文。&lt;span class="kb"&gt;…&lt;/span&gt; で傍線部を示せる。</t>
+          <t xml:space="preserve">              入試にならい、1ステージ2〜5か所、短い語句にだけ付ける。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>話し合い文: 先生と生徒の会話。空欄可。&lt;span class="sp"&gt;先生&lt;/span&gt;「…」&lt;br&gt; の形。</t>
+          <t xml:space="preserve">              設問で問われている箇所には付けないこと（答えが出てしまう）。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">            空欄部分は &lt;span class="blank"&gt;　　&lt;/span&gt; と書く。</t>
+          <t xml:space="preserve">              生徒は「口語訳あり／なし」ボタンで消せる。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>選択肢ア〜エ : 4つすべて埋めること（空欄があると出題されない）。</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>正解      : ア／イ／ウ／エ のいずれか。</t>
+          <t>【設問シートの列】</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>解説      : 採点後に表示される。&lt;b&gt;…&lt;/b&gt; で強調できる。</t>
+          <t>問題ID    : S01-1 など。全体で重複しないこと。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>配点      : 1問3点。1ステージの合計が12点になるようにする。</t>
+          <t>本文ID    : 本文シートの本文IDと一致させる。</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>問番号    : 問1〜問4。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>【問題を追加・修正したら】</t>
+          <t>設問タイプ: 仮名遣い / 主語・指示語 / 内容理解 / 要旨・話し合い のいずれか。</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>集計スプレッドシートのメニュー「⚙ 古典クエスト管理」→</t>
+          <t xml:space="preserve">            この4つ以外を書くと弱点分析に集計されない。</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>「問題プールのキャッシュをクリア」を実行すると、次回出題から反映されます。</t>
+          <t>設問文    : 問いの文。&lt;span class="kb"&gt;…&lt;/span&gt; で傍線部を示せる。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>空欄文    : 問3で使う「〜こと。」の一文。空欄は &lt;span class="blank"&gt;　　&lt;/span&gt;。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>【出典について】</t>
+          <t>話し合い文: 問4で使う先生とＡさんの会話。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>本文は『宇治拾遺物語』『徒然草』『十訓抄』『沙石集』『伊曽保物語』から採り、</t>
+          <t xml:space="preserve">            &lt;span class="sp"&gt;先生&lt;/span&gt;「…」&lt;br&gt; の形。空欄は &lt;span class="blank"&gt;　　&lt;/span&gt;。</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>読みやすさのため表記を一部改めています。設問・解説はオリジナルです。</t>
+          <t>選択肢ア〜エ : 4つすべて埋めること（空欄があると出題されない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>正解      : ア／イ／ウ／エ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>解説      : 採点後に表示される。&lt;b&gt;…&lt;/b&gt; で強調できる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>配点      : 1問3点。1ステージ合計12点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>【反映のしかた】</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>集計スプレッドシートのメニュー「⚙ 古典クエスト管理」→</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>「問題プールのキャッシュをクリア」を実行すると、次回出題から反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>【出典】本文は『宇治拾遺物語』『徒然草』『十訓抄』『沙石集』『伊曽保物語』から採り、</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>表記を一部改めています。設問・解説はオリジナルです。</t>
         </is>
       </c>
     </row>
@@ -795,18 +861,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="66" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -832,25 +899,30 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
+          <t>前書き</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>本文HTML</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>注</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>現代語訳</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>表示順</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>公開</t>
         </is>
@@ -879,23 +951,28 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;これも今は昔、絵仏師良秀といふありけり。家の隣より火出で来て、風おしおほひてせめければ、逃げ出でて大路へ出でにけり。&lt;span class="gl"&gt;人の書かする仏もおはしけり&lt;i&gt;（人が注文して描かせている仏の絵もあった）&lt;/i&gt;&lt;/span&gt;。また、衣着ぬ妻子なども、&lt;span class="gl"&gt;さながら内にありけり&lt;i&gt;（そのまま家の中にいた）&lt;/i&gt;&lt;/span&gt;。それも知らず、&lt;span class="gl"&gt;ただ逃げ出でたるをことにして&lt;i&gt;（自分が逃げ出したことだけをよいことにして）&lt;/i&gt;&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;向かひ&lt;/span&gt;のつらに立てり。&lt;/p&gt;&lt;p&gt;見れば、すでにわが家に移りて、&lt;span class="gl"&gt;煙・炎くゆりけるまで&lt;i&gt;（煙や炎がくすぶり出すまで）&lt;/i&gt;&lt;/span&gt;、おほかた、向かひのつらに立ちて眺めければ、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;あさましきこと&lt;/span&gt;」とて、人ども来とぶらひけれど、騒がず。「いかに」と人言ひければ、向かひに立ちて、家の焼くるを見て、うちうなづきて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;時々笑ひけり&lt;/span&gt;。「あはれ、しつるせうとくかな。年ごろはわろく書きけるものかな」と言ふ時に、とぶらひに来たる者ども、「こはいかに、かくては立ち給へるぞ。&lt;span class="gl"&gt;もののつき給へるか&lt;i&gt;（物の怪でも取りついたのか）&lt;/i&gt;&lt;/span&gt;」と言ひければ、「なんでふ物のつくべきぞ。年ごろ不動尊の火焰をあしく書きけるなり。今見れば、かうこそ燃えけれと、心得つるなり。これこそせうとくよ」と言ひて、あざ笑ひてこそ立てりけれ。&lt;/p&gt;&lt;p&gt;その後にや、良秀がよぢり不動とて、&lt;span class="gl"&gt;今に人々めで合へり&lt;i&gt;（今でも人々がほめ合っている）&lt;/i&gt;&lt;/span&gt;。&lt;/p&gt;</t>
+          <t>絵仏師の良秀は、仏の絵をかくことを職業とする人である。ある日、良秀の家の隣から火が出た。</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;絵仏師&lt;/b&gt;＝仏の絵をかくことを職業とする人。　&lt;b&gt;おしおほひて&lt;/b&gt;＝吹きつけて。　&lt;b&gt;つら&lt;/b&gt;＝側。　&lt;b&gt;とぶらひ&lt;/b&gt;＝見舞い。　&lt;b&gt;せうとく&lt;/b&gt;＝もうけもの。得をしたこと。　&lt;b&gt;なんでふ&lt;/b&gt;＝どうして。　&lt;b&gt;不動尊&lt;/b&gt;＝不動明王。　&lt;b&gt;火焰&lt;/b&gt;＝不動明王の背後に描かれる炎。　&lt;b&gt;よぢり不動&lt;/b&gt;＝良秀のかいた不動明王の絵。</t>
+          <t>&lt;p&gt;これも今は昔、絵仏師良秀といふありけり。家の隣より火出で来て、風おしおほひてせめければ、逃げ出でて大路へ出でにけり。人の書かする仏もおはしけり。また、衣着ぬ妻子なども、&lt;ruby class="gl"&gt;さながら&lt;rt&gt;そのまま&lt;/rt&gt;&lt;/ruby&gt;内にありけり。それも知らず、ただ逃げ出でたるをことにして、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;向かひ&lt;/span&gt;のつらに立てり。&lt;/p&gt;&lt;p&gt;見れば、すでにわが家に移りて、煙・炎くゆりけるまで、&lt;ruby class="gl"&gt;おほかた&lt;rt&gt;ずっと&lt;/rt&gt;&lt;/ruby&gt;、向かひのつらに立ちて眺めければ、「あさましきこと」とて、人ども来とぶらひけれど、&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;騒がず&lt;/span&gt;。「いかに」と人言ひければ、向かひに立ちて、家の焼くるを見て、うちうなづきて、時々笑ひけり。「あはれ、しつるせうとくかな。&lt;ruby class="gl"&gt;年ごろはわろく&lt;rt&gt;長年へたに&lt;/rt&gt;&lt;/ruby&gt;書きけるものかな」と言ふ時に、とぶらひに来たる者ども、「こはいかに、かくては立ち給へるぞ。もののつき給へるか」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;言ひければ&lt;/span&gt;、「なんでふ物のつくべきぞ。年ごろ不動尊の火焰をあしく書きけるなり。今見れば、かうこそ燃えけれと、心得つるなり。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;これこそせうとくよ&lt;/span&gt;」と言ひて、&lt;ruby class="gl"&gt;あざ笑ひて&lt;rt&gt;あざけり笑って&lt;/rt&gt;&lt;/ruby&gt;&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;立てりけれ&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;その後にや、良秀がよぢり不動とて、今に人々めで合へり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;これも今となっては昔のことだが、絵仏師の良秀という者がいた。隣の家から火が出て、風が吹きつけて火が迫ってきたので、（良秀は）逃げ出して大通りへ出てしまった。家の中には、人が注文して描かせている仏の絵もあった。また、着物も着ていない妻子などもそのまま家の中にいた。良秀はそれも気にかけず、ただ自分が逃げ出したことだけをよいことにして、向かい側に立っていた。&lt;/p&gt;&lt;p&gt;見ると、すでに火は自分の家に燃え移って、煙や炎がくすぶり出すまで、ずっと向かい側に立って眺めていたので、「驚きあきれたことだ」と言って、人々が見舞いに来たけれども、（良秀は）騒がない。「どうしたのか」と人が言うと、向かい側に立って、自分の家が焼けるのを見て、うなずいて、時々笑った。「ああ、たいそうなもうけものをしたことだ。長年、まずく描いていたものだなあ」と言うので、見舞いに来ていた者たちが、「これはどうしたことか、こうして立っていらっしゃるのか。物の怪でも取りつきなさったのか」と言うと、「どうして物の怪が取りつくものか。長年、不動明王の火炎をうまく描けずにいたのだ。今見ると、このように燃えるのだったのだなと、会得したのだ。これこそもうけものだ」と言って、あざ笑って立っていた。&lt;/p&gt;&lt;p&gt;その後のことであろうか、良秀のよじり不動といって、今でも人々がほめ合っている。&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n">
+          <t>&lt;b&gt;絵仏師&lt;/b&gt;＝仏の絵をかくことを職業とする人。　&lt;b&gt;おしおほひて&lt;/b&gt;＝吹きつけて。　&lt;b&gt;つら&lt;/b&gt;＝側。　&lt;b&gt;とぶらひ&lt;/b&gt;＝見舞い。　&lt;b&gt;せうとく&lt;/b&gt;＝もうけもの。得をしたこと。　&lt;b&gt;不動尊&lt;/b&gt;＝不動明王。　&lt;b&gt;火焰&lt;/b&gt;＝不動明王の背後に描かれる炎。　&lt;b&gt;よぢり不動&lt;/b&gt;＝良秀のかいた不動明王の絵。</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;これも今となっては昔のことだが、絵仏師の良秀という者がいた。隣の家から火が出て、風が吹きつけて火が迫ってきたので、逃げ出して大通りへ出てしまった。家の中には、人が注文して描かせている仏の絵もあった。また、着物も着ていない妻子などもそのまま家の中にいた。良秀はそれも気にかけず、ただ自分が逃げ出したことだけをよいことにして、向かい側に立っていた。&lt;/p&gt;&lt;p&gt;見ると、すでに火は自分の家に燃え移って、煙や炎がくすぶり出すまで、ずっと向かい側に立って眺めていたので、「驚きあきれたことだ」と言って、人々が見舞いに来たけれども、（良秀は）騒がない。「どうしたのか」と人が言うと、向かい側に立って、自分の家が焼けるのを見て、うなずいて、時々笑った。「ああ、たいそうなもうけものをしたことだ。長年、まずく描いていたものだなあ」と言うので、見舞いに来ていた者たちが、「これはどうしたことか、こうして立っていらっしゃるのか。物の怪でも取りつきなさったのか」と言うと、「どうして物の怪が取りつくものか。長年、不動明王の火炎をうまく描けずにいたのだ。今見ると、このように燃えるのだったのだなと、会得したのだ。これこそもうけものだ」と言って、あざ笑って立っていた。&lt;/p&gt;&lt;p&gt;その後のことであろうか、良秀のよじり不動といって、今でも人々がほめ合っている。&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -924,23 +1001,28 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;和泉式部、&lt;span class="gl"&gt;保昌が妻にて丹後に下りけるほどに&lt;i&gt;（保昌の妻として丹後に下っていたころ）&lt;/i&gt;&lt;/span&gt;、京に歌合ありけるに、小式部内侍、&lt;span class="gl"&gt;歌よみにとられてよみけるを&lt;i&gt;（歌のよみ手に選ばれて歌をよんだが）&lt;/i&gt;&lt;/span&gt;、定頼中納言たはぶれて、小式部内侍ありけるに、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;丹後へつかはしける人は参りたりや。いかに心もとなくおぼすらむ&lt;/span&gt;」と言ひて、&lt;span class="gl"&gt;局の前を過ぎられけるを&lt;i&gt;（部屋の前を通り過ぎなさったのを）&lt;/i&gt;&lt;/span&gt;、&lt;span class="gl"&gt;御簾よりなから出でて&lt;i&gt;（御簾から身を半分ほど乗り出して）&lt;/i&gt;&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;わづかに&lt;/span&gt;&lt;span class="gl"&gt;直衣の袖をひかへて&lt;i&gt;（直衣の袖を引きとめて）&lt;/i&gt;&lt;/span&gt;、&lt;/p&gt;&lt;p&gt;　大江山いくのの道の遠ければまだふみもみず天の橋立&lt;/p&gt;&lt;p&gt;とよみかけけり。思はずにあさましくて、「こはいかに、かかるやうやはある」とばかり言ひて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;返しにも及ばず、袖を引き放ちて逃げられけり&lt;/span&gt;。小式部、これより&lt;span class="gl"&gt;歌よみの世おぼえ出で来にけり&lt;i&gt;（歌よみとしての評判が世に立つようになった）&lt;/i&gt;&lt;/span&gt;。&lt;/p&gt;</t>
+          <t>歌人の和泉式部が、夫の保昌とともに京を離れて丹後の国にいたころ、その娘の小式部内侍が、京で開かれる歌合のよみ手に選ばれた。小式部内侍の歌は母の代作だという噂が立っていた。</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;和泉式部&lt;/b&gt;＝平安時代の歌人。小式部内侍の母。　&lt;b&gt;保昌&lt;/b&gt;＝藤原保昌。和泉式部の夫。　&lt;b&gt;丹後&lt;/b&gt;＝今の京都府北部。　&lt;b&gt;歌合&lt;/b&gt;＝左右に分かれて和歌の優劣を競う会。　&lt;b&gt;小式部内侍&lt;/b&gt;＝和泉式部の娘。歌人。　&lt;b&gt;定頼中納言&lt;/b&gt;＝藤原定頼。　&lt;b&gt;局&lt;/b&gt;＝宮中に仕える女性の部屋。　&lt;b&gt;御簾&lt;/b&gt;＝すだれ。　&lt;b&gt;なから&lt;/b&gt;＝半分。　&lt;b&gt;直衣&lt;/b&gt;＝貴族の平服。　&lt;b&gt;大江山・いくの&lt;/b&gt;＝丹後へ行く道にある地名。「いくの」に「行く野」を掛ける。　&lt;b&gt;ふみ&lt;/b&gt;＝「踏み」と「文（手紙）」を掛ける。　&lt;b&gt;天の橋立&lt;/b&gt;＝丹後の名所。　&lt;b&gt;返し&lt;/b&gt;＝返歌。</t>
+          <t>&lt;p&gt;和泉式部、保昌が妻にて丹後に&lt;ruby class="gl"&gt;下りけるほどに&lt;rt&gt;下っていたころ&lt;/rt&gt;&lt;/ruby&gt;、京に歌合ありけるに、小式部内侍、歌よみにとられてよみけるを、定頼中納言たはぶれて、小式部内侍ありけるに、「丹後へつかはしける人は参りたりや。いかに心もとなくおぼすらむ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;言ひて&lt;/span&gt;、局の前を過ぎられけるを、御簾よりなから出でて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;わづかに&lt;/span&gt;直衣の袖をひかへて、&lt;/p&gt;&lt;p&gt;　大江山いくのの道の遠ければまだふみもみず天の橋立&lt;/p&gt;&lt;p&gt;と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;よみかけけり&lt;/span&gt;。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;思はずにあさましくて&lt;/span&gt;、「こはいかに、&lt;ruby class="gl"&gt;かかるやうやはある&lt;rt&gt;こんなことがあるものか&lt;/rt&gt;&lt;/ruby&gt;」とばかり言ひて、返しにも及ばず、袖を引き放ちて&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;逃げられけり&lt;/span&gt;。小式部、&lt;ruby class="gl"&gt;これより&lt;rt&gt;これ以降&lt;/rt&gt;&lt;/ruby&gt;歌よみの世&lt;ruby class="gl"&gt;おぼえ&lt;rt&gt;評判&lt;/rt&gt;&lt;/ruby&gt;出で来にけり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;和泉式部&lt;/b&gt;＝平安時代の歌人。小式部内侍の母。　&lt;b&gt;保昌&lt;/b&gt;＝藤原保昌。和泉式部の夫。　&lt;b&gt;丹後&lt;/b&gt;＝今の京都府北部。　&lt;b&gt;歌合&lt;/b&gt;＝左右に分かれて和歌の優劣を競う会。　&lt;b&gt;小式部内侍&lt;/b&gt;＝和泉式部の娘。歌人。　&lt;b&gt;定頼中納言&lt;/b&gt;＝藤原定頼。　&lt;b&gt;たはぶれて&lt;/b&gt;＝ふざけて。　&lt;b&gt;局&lt;/b&gt;＝宮中に仕える女性の部屋。　&lt;b&gt;御簾&lt;/b&gt;＝すだれ。　&lt;b&gt;なから&lt;/b&gt;＝半分。　&lt;b&gt;直衣&lt;/b&gt;＝貴族の平服。　&lt;b&gt;大江山・いくの&lt;/b&gt;＝丹後へ行く道にある地名。「いくの」に「行く野」を掛ける。　&lt;b&gt;ふみ&lt;/b&gt;＝「踏み」と「文（手紙）」を掛ける。　&lt;b&gt;天の橋立&lt;/b&gt;＝丹後の名所。　&lt;b&gt;返し&lt;/b&gt;＝返歌。</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>&lt;p&gt;和泉式部が、（夫の）保昌の妻として丹後の国に下っていたころ、京で歌合があったが、（娘の）小式部内侍が歌のよみ手に選ばれて歌をよんだところ、定頼中納言がふざけて、小式部内侍がいたところに来て、「丹後へおやりになった使いは帰って参りましたか。（返事が来ないので）どんなに待ち遠しくお思いでしょう」と言って、部屋の前を通り過ぎられたのを、（小式部内侍は）御簾から身を半分ほど乗り出して、わずかに（定頼の）直衣の袖を引きとめて、&lt;/p&gt;&lt;p&gt;「大江山を越え、生野を通って行く道が遠いので、まだ天の橋立の地を踏んでもいませんし、母からの手紙も見ていません」&lt;/p&gt;&lt;p&gt;とよみかけた。（定頼は）思いがけないことに驚きあきれて、「これはどうしたことだ、こんなことがあってよいものか」とだけ言って、返歌をすることもできず、袖を引き放ってお逃げになった。小式部内侍は、これ以降、歌よみとしての評判が世に立つようになった。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -969,23 +1051,28 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;高名の木登りといひしをのこ、&lt;span class="gl"&gt;人を掟てて、高き木に登せて梢を切らせしに&lt;i&gt;（人に指図して高い木に登らせ、枝の先を切らせたときに）&lt;/i&gt;&lt;/span&gt;、いと&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;危ふく&lt;/span&gt;見えしほどは&lt;span class="gl"&gt;言ふこともなくて&lt;i&gt;（何も言わないで）&lt;/i&gt;&lt;/span&gt;、下るるときに、軒たけばかりになりて、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;あやまちすな。心して降りよ&lt;/span&gt;」と言葉をかけ侍りしを、「&lt;span class="gl"&gt;かばかりになりては、飛び降るとも降りなん&lt;i&gt;（これくらいの高さになれば、飛び降りても降りられるだろう）&lt;/i&gt;&lt;/span&gt;。いかにかく言ふぞ」と申し侍りしかば、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;&lt;span class="gl"&gt;その事に候ふ&lt;i&gt;（そのことでございます）&lt;/i&gt;&lt;/span&gt;。目くるめき、枝危ふきほどは、おのれが恐れ侍れば申さず。あやまちは、安き所になりて、必ず仕る事に候ふ&lt;/span&gt;」と言ふ。&lt;/p&gt;&lt;p&gt;あやしき下臈なれども、聖人の戒めにかなへり。鞠も、&lt;span class="gl"&gt;難き所を蹴出して後&lt;i&gt;（難しい所を蹴り出したあと）&lt;/i&gt;&lt;/span&gt;、安く思へば、必ず落つと侍るやらん。&lt;/p&gt;</t>
+          <t>木登りの名人といわれた男が、人に指図して高い木の枝を切らせたときのことである。</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>&lt;p&gt;高名の木登りといひしをのこ、人を掟てて、高き木に&lt;ruby class="gl"&gt;登せて&lt;rt&gt;登らせて&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby class="gl"&gt;梢&lt;rt&gt;枝の先&lt;/rt&gt;&lt;/ruby&gt;を切らせしに、いと&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;危ふく&lt;/span&gt;見えしほどは言ふこともなくて、下るるときに、軒たけばかりになりて、「あやまちすな。心して降りよ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;言葉をかけ侍りし&lt;/span&gt;を、「かばかりになりては、飛び降るとも&lt;ruby class="gl"&gt;降りなん&lt;rt&gt;降りられるだろう&lt;/rt&gt;&lt;/ruby&gt;。いかにかく言ふぞ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;申し侍りしかば&lt;/span&gt;、「その事に候ふ。目くるめき、枝危ふきほどは、おのれが恐れ侍れば申さず。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;あやまちは、安き所になりて、必ず仕る事に候ふ&lt;/span&gt;」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;言ふ&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;あやしき下臈なれども、聖人の戒めにかなへり。鞠も、難き所を蹴出して後、&lt;ruby class="gl"&gt;安く思へば&lt;rt&gt;簡単だと思うと&lt;/rt&gt;&lt;/ruby&gt;、必ず落つと侍るやらん。&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>&lt;b&gt;高名の&lt;/b&gt;＝有名な。　&lt;b&gt;をのこ&lt;/b&gt;＝男。　&lt;b&gt;掟てて&lt;/b&gt;＝指図して。　&lt;b&gt;軒たけ&lt;/b&gt;＝家の軒の高さ。　&lt;b&gt;あやまち&lt;/b&gt;＝失敗。けが。　&lt;b&gt;候ふ&lt;/b&gt;＝ございます。　&lt;b&gt;目くるめき&lt;/b&gt;＝目がくらみ。　&lt;b&gt;仕る&lt;/b&gt;＝いたす。　&lt;b&gt;あやしき下臈&lt;/b&gt;＝身分の低い者。　&lt;b&gt;聖人の戒め&lt;/b&gt;＝すぐれた人の教え。　&lt;b&gt;鞠&lt;/b&gt;＝蹴鞠。</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>&lt;p&gt;木登りの名人といわれた男が、人に指図して高い木に登らせて枝の先を切らせたときに、たいそう危なく見えたうちは何も言わないで、（その人が）降りるときに、軒の高さくらいになって、「けがをするな。気をつけて降りろ」と声をかけましたので、「これくらいの高さになれば、飛び降りても降りられるでしょう。どうしてそのように言うのか」と申しましたところ、「そのことでございます。目がくらむほど高く、枝が危ないうちは、本人が自分で恐れておりますので、（私は）何も申しません。けがは、安全な所になってから、必ずするものでございます」と言う。&lt;/p&gt;&lt;p&gt;身分の低い者であるけれども、その言葉は聖人の戒めと一致している。蹴鞠でも、難しい所を蹴り出したあと、（もう）簡単だと思うと、必ず落とすと申すようです。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1014,23 +1101,28 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;仁和寺にある法師、&lt;span class="gl"&gt;年寄るまで石清水を拝まざりければ&lt;i&gt;（年をとるまで石清水八幡宮を参拝しなかったので）&lt;/i&gt;&lt;/span&gt;、心うく覚えて、あるとき思ひ立ちて、ただひとり、徒歩より&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;まうでけり&lt;/span&gt;。&lt;span class="gl"&gt;極楽寺・高良などを拝みて&lt;i&gt;（極楽寺や高良神社などを拝んで）&lt;/i&gt;&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;かばかりと心得て帰りにけり&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;さて、かたへの人にあひて、「&lt;span class="gl"&gt;年ごろ思ひつること、果たし侍りぬ&lt;i&gt;（長年思っていたことを果たしました）&lt;/i&gt;&lt;/span&gt;。&lt;span class="gl"&gt;聞きしにも過ぎて尊くこそおはしけれ&lt;i&gt;（聞いていた以上に尊くていらっしゃった）&lt;/i&gt;&lt;/span&gt;。&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;そも、参りたる人ごとに山へ登りしは、何事かありけん、ゆかしかりしかど、神へ参るこそ本意なれと思ひて、山までは見ず&lt;/span&gt;」とぞ言ひける。&lt;/p&gt;&lt;p&gt;少しのことにも、先達はあらまほしきことなり。&lt;/p&gt;</t>
+          <t>仁和寺にいるある法師が、長年の願いであった石清水八幡宮の参拝に、ただ一人で出かけた。</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
+          <t>&lt;p&gt;仁和寺にある法師、年寄るまで石清水を&lt;ruby class="gl"&gt;拝まざりければ&lt;rt&gt;参拝しなかったので&lt;/rt&gt;&lt;/ruby&gt;、心うく覚えて、あるとき思ひ立ちて、ただひとり、徒歩より&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;まうでけり&lt;/span&gt;。極楽寺・高良などを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;拝みて&lt;/span&gt;、かばかりと心得て帰りにけり。&lt;/p&gt;&lt;p&gt;さて、かたへの人にあひて、「年ごろ思ひつること、&lt;ruby class="gl"&gt;果たし侍りぬ&lt;rt&gt;果たしました&lt;/rt&gt;&lt;/ruby&gt;。&lt;ruby class="gl"&gt;聞きしにも過ぎて&lt;rt&gt;聞いていた以上に&lt;/rt&gt;&lt;/ruby&gt;尊くこそ&lt;ruby class="gl"&gt;おはしけれ&lt;rt&gt;いらっしゃった&lt;/rt&gt;&lt;/ruby&gt;。そも、参りたる人ごとに山へ&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;登りし&lt;/span&gt;は、何事かありけん、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;ゆかしかりしかど&lt;/span&gt;、神へ参るこそ本意なれと思ひて、山までは見ず」とぞ&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;言ひける&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;少しのことにも、先達は&lt;ruby class="gl"&gt;あらまほしき&lt;rt&gt;あってほしい&lt;/rt&gt;&lt;/ruby&gt;ことなり。&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>&lt;b&gt;仁和寺&lt;/b&gt;＝京都にある寺。　&lt;b&gt;石清水&lt;/b&gt;＝石清水八幡宮。京都府八幡市の男山の山上にある。　&lt;b&gt;心うく&lt;/b&gt;＝物足りなく。　&lt;b&gt;徒歩より&lt;/b&gt;＝徒歩で。　&lt;b&gt;極楽寺・高良&lt;/b&gt;＝いずれも男山のふもとにある寺社。　&lt;b&gt;かばかり&lt;/b&gt;＝これだけ。　&lt;b&gt;かたへの人&lt;/b&gt;＝仲間。　&lt;b&gt;年ごろ&lt;/b&gt;＝長年。　&lt;b&gt;ゆかしかりしかど&lt;/b&gt;＝知りたかったけれど。　&lt;b&gt;本意&lt;/b&gt;＝本来の目的。　&lt;b&gt;先達&lt;/b&gt;＝案内者。指導者。</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>&lt;p&gt;仁和寺にいるある法師が、年をとるまで石清水八幡宮を参拝したことがなかったので、物足りなく思って、あるとき思い立って、ただ一人、徒歩で参拝した。（ふもとの）極楽寺や高良神社などを拝んで、これだけのものだと思い込んで帰ってしまった。&lt;/p&gt;&lt;p&gt;さて、仲間に会って、「長年思っていたことを、果たしました。聞いていた以上に尊くていらっしゃった。それにしても、参拝する人がみな山へ登っていたのは、何事があったのだろうか、知りたかったけれど、神にお参りすることこそが本来の目的だと思って、山の上までは見ませんでした」と言った。&lt;/p&gt;&lt;p&gt;ちょっとしたことにも、案内者はいてほしいものである。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1059,23 +1151,28 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;これも今は昔、比叡の山に児ありけり。僧たち、宵のつれづれに、「いざ、かいもちひせむ」と言ひけるを、この児、心寄せに聞きけり。&lt;span class="gl"&gt;さりとて、し出ださむを待ちて寝ざらむも、わろかりなむと思ひて&lt;i&gt;（とはいっても、作り上げるのを待って寝ないでいるのもみっともないだろうと思って）&lt;/i&gt;&lt;/span&gt;、&lt;span class="gl"&gt;片方に寄りて、寝たるよしにて&lt;i&gt;（部屋の片隅に寄って、寝たふりをして）&lt;/i&gt;&lt;/span&gt;、出で来るを待ちけるに、&lt;span class="gl"&gt;すでにし出だしたるさまにて&lt;i&gt;（もう作り上げた様子で）&lt;/i&gt;&lt;/span&gt;、ひしめき合ひたり。&lt;/p&gt;&lt;p&gt;この児、&lt;span class="gl"&gt;さだめて驚かさむずらむと待ちゐたるに&lt;i&gt;（きっと起こしてくれるだろうと待っていたところ）&lt;/i&gt;&lt;/span&gt;、僧の、「もの申しさぶらはむ。驚かせたまへ」と言ふを、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;うれしとは思へども、ただ一度に&lt;span class="mk"&gt;②&lt;/span&gt;いらへむも、待ちけるかともぞ思ふ&lt;/span&gt;とて、今一声呼ばれていらへむと、念じて寝たるほどに、「や、な起こしたてまつりそ。幼き人は寝入りたまひにけり」と言ふ声のしければ、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;あな、わびし&lt;/span&gt;と思ひて、いま一度起こせかしと、&lt;span class="gl"&gt;思ひ寝に聞けば&lt;i&gt;（そう思いながら寝て聞いていると）&lt;/i&gt;&lt;/span&gt;、&lt;span class="gl"&gt;ひしひしと、ただ食ひに食ふ音のしければ&lt;i&gt;（むしゃむしゃと、ひたすら食べる音がしたので）&lt;/i&gt;&lt;/span&gt;、ずちなくて、無期ののちに、「えい」といらへたりければ、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;僧たち笑ふこと限りなし&lt;/span&gt;。&lt;/p&gt;</t>
+          <t>比叡山の寺に、僧たちに交じって暮らす少年（児）がいた。ある夜、僧たちがぼたもちを作ろうと言い出した。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;児&lt;/b&gt;＝寺で修行しながら育てられる少年。　&lt;b&gt;比叡の山&lt;/b&gt;＝比叡山延暦寺。　&lt;b&gt;宵&lt;/b&gt;＝夜のはじめ。　&lt;b&gt;つれづれに&lt;/b&gt;＝手持ちぶさたで。　&lt;b&gt;かいもちひ&lt;/b&gt;＝ぼたもち。　&lt;b&gt;心寄せに&lt;/b&gt;＝期待して。　&lt;b&gt;わろかりなむ&lt;/b&gt;＝みっともないだろう。　&lt;b&gt;よし&lt;/b&gt;＝ふり。　&lt;b&gt;ひしめき合ひたり&lt;/b&gt;＝大騒ぎしている。　&lt;b&gt;驚かす&lt;/b&gt;＝目を覚まさせる。　&lt;b&gt;もの申しさぶらはむ&lt;/b&gt;＝もしもし。　&lt;b&gt;いらへ&lt;/b&gt;＝返事。　&lt;b&gt;念じて&lt;/b&gt;＝我慢して。　&lt;b&gt;な起こしたてまつりそ&lt;/b&gt;＝お起こし申し上げるな。　&lt;b&gt;わびし&lt;/b&gt;＝つらい。がっかりだ。　&lt;b&gt;ずちなくて&lt;/b&gt;＝どうしようもなくて。　&lt;b&gt;無期ののちに&lt;/b&gt;＝ずいぶん時間がたってから。</t>
+          <t>&lt;p&gt;これも今は昔、比叡の山に児ありけり。僧たち、宵のつれづれに、「いざ、かいもちひせむ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;言ひける&lt;/span&gt;を、この児、心寄せに聞きけり。&lt;ruby class="gl"&gt;さりとて&lt;rt&gt;とはいっても&lt;/rt&gt;&lt;/ruby&gt;、し出ださむを待ちて寝ざらむも、わろかりなむと思ひて、片方に寄りて、寝たるよしにて、出で来るを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;待ちける&lt;/span&gt;に、すでにし出だしたるさまにて、ひしめき合ひたり。&lt;/p&gt;&lt;p&gt;この児、&lt;ruby class="gl"&gt;さだめて&lt;rt&gt;きっと&lt;/rt&gt;&lt;/ruby&gt;驚かさむずらむと待ちゐたるに、僧の、「もの申しさぶらはむ。驚かせたまへ」と言ふを、うれしとは思へども、ただ一度に&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;いらへむ&lt;/span&gt;も、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;待ちけるかともぞ思ふ&lt;/span&gt;とて、&lt;ruby class="gl"&gt;今一声&lt;rt&gt;もう一声&lt;/rt&gt;&lt;/ruby&gt;呼ばれていらへむと、念じて寝たるほどに、「や、な起こしたてまつりそ。幼き人は寝入りたまひにけり」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;言ふ声&lt;/span&gt;のしければ、あな、わびしと思ひて、いま一度&lt;ruby class="gl"&gt;起こせかし&lt;rt&gt;起こしてほしい&lt;/rt&gt;&lt;/ruby&gt;と、思ひ寝に聞けば、ひしひしと、ただ食ひに食ふ音のしければ、ずちなくて、無期ののちに、「えい」といらへたりければ、僧たち笑ふこと限りなし。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;児&lt;/b&gt;＝寺で修行しながら育てられる少年。　&lt;b&gt;比叡の山&lt;/b&gt;＝比叡山延暦寺。　&lt;b&gt;つれづれに&lt;/b&gt;＝手持ちぶさたで。　&lt;b&gt;かいもちひ&lt;/b&gt;＝ぼたもち。　&lt;b&gt;心寄せに&lt;/b&gt;＝期待して。　&lt;b&gt;わろかりなむ&lt;/b&gt;＝みっともないだろう。　&lt;b&gt;よし&lt;/b&gt;＝ふり。　&lt;b&gt;驚かす&lt;/b&gt;＝目を覚まさせる。　&lt;b&gt;もの申しさぶらはむ&lt;/b&gt;＝もしもし。　&lt;b&gt;いらへ&lt;/b&gt;＝返事。　&lt;b&gt;念じて&lt;/b&gt;＝我慢して。　&lt;b&gt;な起こしたてまつりそ&lt;/b&gt;＝お起こし申し上げるな。　&lt;b&gt;わびし&lt;/b&gt;＝つらい。がっかりだ。　&lt;b&gt;ずちなくて&lt;/b&gt;＝どうしようもなくて。　&lt;b&gt;無期ののちに&lt;/b&gt;＝ずいぶん時間がたってから。</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
           <t>&lt;p&gt;これも今となっては昔のことだが、比叡山に児がいた。僧たちが、宵の手持ちぶさたなときに、「さあ、ぼたもちを作ろう」と言ったのを、この児は期待して聞いた。とはいっても、作り上げるのを待って寝ないでいるのもみっともないだろうと思って、部屋の片隅に寄って、寝たふりをして、出てくるのを待っていたところ、もう作り上げた様子で、大騒ぎしている。&lt;/p&gt;&lt;p&gt;この児は、きっと（僧たちが）起こしてくれるだろうと待っていたところ、僧が「もしもし。お目をお覚ましください」と言うのを、うれしいとは思うけれども、たった一度で返事をするのも、待っていたのかと思われては困ると思って、もう一声呼ばれてから返事をしようと、我慢して寝ているうちに、「これ、お起こし申し上げるな。幼い人は寝入っておしまいになった」と言う声がしたので、ああ、がっかりだと思って、もう一度起こしてくれよと思いながら寝て聞いていると、むしゃむしゃとひたすら食べる音がしたので、どうしようもなくて、ずいぶん時間がたってから、「はい」と返事をしたので、僧たちは笑うことこのうえなかった。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1104,23 +1201,28 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;ある川のほとりに、蟻遊ぶことありけり。&lt;span class="gl"&gt;にはかに水かさまさりて、かの蟻を誘ひ流る&lt;i&gt;（急に水かさが増して、その蟻をさらって流す）&lt;/i&gt;&lt;/span&gt;。&lt;span class="gl"&gt;浮きぬ沈みぬする所に&lt;i&gt;（浮いたり沈んだりしているところに）&lt;/i&gt;&lt;/span&gt;、鳩、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;こずゑ&lt;/span&gt;よりこれを見て、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;あはれなるありさまかな&lt;/span&gt;」と、こずゑ&lt;span class="gl"&gt;をちと食ひ切つて川の中へ落としければ&lt;i&gt;（を少し食い切って川の中へ落としたところ）&lt;/i&gt;&lt;/span&gt;、&lt;span class="gl"&gt;蟻これに乗りて、渚に上がりぬ&lt;i&gt;（蟻はこれに乗って、水ぎわに上がった）&lt;/i&gt;&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;かかりける所に、ある人、竿の先に鳥もちを付けて、かの鳩をささんとす。&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;蟻、心に思ふやう、「ただ今の恩を送らん」と思ひ、かの人の足にしつかと食ひつきければ&lt;/span&gt;、おびえあがつて、&lt;span class="gl"&gt;竿をかしこに投げ捨てけり&lt;i&gt;（竿をあちらへ投げ捨ててしまった）&lt;/i&gt;&lt;/span&gt;。鳩これを悟りて、はるかの空へぞ逃げ延びにける。&lt;/p&gt;&lt;p&gt;そのごとく、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;人の恩を受けたらん者は、いかさまにもその報いをなすべきなり&lt;/span&gt;。&lt;/p&gt;</t>
+          <t>『伊曽保物語』は、ヨーロッパの「イソップ物語」を江戸時代の初めに日本語に訳した本である。次は、ある川のほとりでの鳩と蟻の話である。</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;伊曽保物語&lt;/b&gt;＝ヨーロッパの「イソップ物語」を、江戸時代の初めに日本語に訳した本。　&lt;b&gt;こずゑ&lt;/b&gt;＝木の枝の先。　&lt;b&gt;ちと&lt;/b&gt;＝少し。　&lt;b&gt;渚&lt;/b&gt;＝水ぎわ。　&lt;b&gt;かかりける所に&lt;/b&gt;＝そうしているところに。　&lt;b&gt;鳥もち&lt;/b&gt;＝鳥を捕らえるための、粘り気のあるもの。　&lt;b&gt;ささんとす&lt;/b&gt;＝（竿で）刺して捕らえようとする。　&lt;b&gt;恩を送らん&lt;/b&gt;＝恩を返そう。　&lt;b&gt;しつかと&lt;/b&gt;＝しっかりと。　&lt;b&gt;おびえあがつて&lt;/b&gt;＝驚いて。　&lt;b&gt;悟りて&lt;/b&gt;＝気づいて。　&lt;b&gt;いかさまにも&lt;/b&gt;＝どのようにしてでも。</t>
+          <t>&lt;p&gt;ある川のほとりに、蟻遊ぶことありけり。&lt;ruby class="gl"&gt;にはかに&lt;rt&gt;急に&lt;/rt&gt;&lt;/ruby&gt;水かさまさりて、かの蟻を&lt;ruby class="gl"&gt;誘ひ流る&lt;rt&gt;さらって流す&lt;/rt&gt;&lt;/ruby&gt;。&lt;ruby class="gl"&gt;浮きぬ沈みぬ&lt;rt&gt;浮いたり沈んだり&lt;/rt&gt;&lt;/ruby&gt;する所に、鳩、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;こずゑ&lt;/span&gt;よりこれを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;見て&lt;/span&gt;、「あはれなるありさまかな」と、こずゑをちと食ひ切つて川の中へ落としければ、蟻これに乗りて、渚に上がりぬ。&lt;/p&gt;&lt;p&gt;かかりける所に、ある人、竿の先に鳥もちを付けて、かの鳩をささんとす。蟻、&lt;ruby class="gl"&gt;心に思ふやう&lt;rt&gt;思うことには&lt;/rt&gt;&lt;/ruby&gt;、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;ただ今の恩を送らん&lt;/span&gt;」と思ひ、かの人の足にしつかと&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;食ひつきければ&lt;/span&gt;、おびえあがつて、竿をかしこに投げ捨てけり。鳩これを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;悟りて&lt;/span&gt;、はるかの空へぞ&lt;ruby class="gl"&gt;逃げ延びにける&lt;rt&gt;逃げのびた&lt;/rt&gt;&lt;/ruby&gt;。&lt;/p&gt;&lt;p&gt;そのごとく、人の恩を受けたらん者は、いかさまにもその報いをなすべきなり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;こずゑ&lt;/b&gt;＝木の枝の先。　&lt;b&gt;ちと&lt;/b&gt;＝少し。　&lt;b&gt;渚&lt;/b&gt;＝水ぎわ。　&lt;b&gt;かかりける所に&lt;/b&gt;＝そうしているところに。　&lt;b&gt;鳥もち&lt;/b&gt;＝鳥を捕らえるための、粘り気のあるもの。　&lt;b&gt;ささんとす&lt;/b&gt;＝（竿で）刺して捕らえようとする。　&lt;b&gt;しつかと&lt;/b&gt;＝しっかりと。　&lt;b&gt;おびえあがつて&lt;/b&gt;＝驚いて。　&lt;b&gt;いかさまにも&lt;/b&gt;＝どのようにしてでも。</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>&lt;p&gt;ある川のほとりで、蟻が遊んでいることがあった。急に水かさが増して、その蟻を（水が）さらって流す。浮いたり沈んだりしているところに、鳩が枝の先からこれを見て、「かわいそうなありさまだなあ」と（思い）、枝を少し食い切って川の中へ落としたところ、蟻はこれに乗って、水ぎわに上がった。&lt;/p&gt;&lt;p&gt;そうしているところに、ある人が、竿の先に鳥もちを付けて、その鳩を捕らえようとする。蟻が心に思うことには、「たった今受けた恩を返そう」と思い、その人の足にしっかりとかみついたので、（その人は）驚いて、竿をあちらへ投げ捨ててしまった。鳩はこれに気づいて、はるかな空へと逃げのびた。&lt;/p&gt;&lt;p&gt;そのように、人の恩を受けたような者は、どのようにしてでもその恩に報いるべきである。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1149,23 +1251,28 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;今は昔、小野篁といふ人おはしけり。嵯峨の帝の御時に、&lt;span class="gl"&gt;内裏に札を立てたりけるに&lt;i&gt;（内裏に札が立ててあったが）&lt;/i&gt;&lt;/span&gt;、「無悪善」と書きたりけり。帝、篁に、「読め」と仰せられたりければ、「&lt;span class="gl"&gt;読みは読み候ひなん&lt;i&gt;（読むことは読めるでしょう）&lt;/i&gt;&lt;/span&gt;。されど、恐れにて候へば、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;え申し候はじ&lt;/span&gt;」と奏しければ、&lt;span class="gl"&gt;「ただ申せ」と、たびたび仰せられければ&lt;i&gt;（「かまわないから申せ」と、たびたびおっしゃったので）&lt;/i&gt;&lt;/span&gt;、「さがなくてよからんと申して候ふぞ。されば、君を呪ひ参らせて候ふなり」と申しければ、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;おのれ放ちては、誰か書かん&lt;/span&gt;」と仰せられければ、「&lt;span class="gl"&gt;さればこそ、申し候はじとは申して候ひつれ&lt;i&gt;（だからこそ、申し上げますまいと申したのでございます）&lt;/i&gt;&lt;/span&gt;」と申すに、帝、「&lt;span class="gl"&gt;さて、何も書きたらん物は、読みてんや&lt;i&gt;（それでは、どんなものが書いてあっても読めるのか）&lt;/i&gt;&lt;/span&gt;」と仰せられければ、「何にても読み候ひなん」と申しければ、片仮名の子文字を十二書かせ&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;給ひて&lt;/span&gt;、「読め」と仰せられければ、「ねこの子のこねこ、ししの子のこじし」と読みたりければ、帝、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;ほほ笑ませ給ひて、事なくてやみにけり&lt;/span&gt;。&lt;/p&gt;</t>
+          <t>嵯峨天皇の御代のこと。学者として名高い小野篁が、内裏に立てられた札をめぐって、天皇と問答をした。</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
+          <t>&lt;p&gt;今は昔、小野篁といふ人&lt;ruby class="gl"&gt;おはしけり&lt;rt&gt;いらっしゃった&lt;/rt&gt;&lt;/ruby&gt;。嵯峨の帝の御時に、内裏に札を立てたりけるに、「無悪善」と書きたりけり。帝、篁に、「読め」と&lt;ruby class="gl"&gt;仰せられたりければ&lt;rt&gt;おっしゃったので&lt;/rt&gt;&lt;/ruby&gt;、「読みは読み候ひなん。されど、恐れにて候へば、え申し候はじ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;奏しければ&lt;/span&gt;、「ただ申せ」と、たびたび仰せられければ、「さがなくて&lt;ruby class="gl"&gt;よからん&lt;rt&gt;よいだろう&lt;/rt&gt;&lt;/ruby&gt;と申して候ふぞ。されば、君を呪ひ参らせて候ふなり」と申しければ、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;おのれ放ちては、誰か書かん&lt;/span&gt;」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;仰せられければ&lt;/span&gt;、「さればこそ、申し候はじとは申して候ひつれ」と申すに、帝、「さて、何も書きたらん物は、読みてんや」と仰せられければ、「&lt;ruby class="gl"&gt;何にても&lt;rt&gt;何であっても&lt;/rt&gt;&lt;/ruby&gt;読み候ひなん」と申しければ、片仮名の子文字を十二書かせ&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;給ひて&lt;/span&gt;、「読め」と仰せられければ、「ねこの子のこねこ、ししの子のこじし」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;読みたりければ&lt;/span&gt;、帝、ほほ笑ませ給ひて、事なくてやみにけり。&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>&lt;b&gt;小野篁&lt;/b&gt;＝平安時代前期の学者・歌人。　&lt;b&gt;嵯峨の帝&lt;/b&gt;＝嵯峨天皇。　&lt;b&gt;内裏&lt;/b&gt;＝天皇の住む御殿。　&lt;b&gt;無悪善&lt;/b&gt;＝「悪（さが）無くて善からん」と読める。　&lt;b&gt;さが&lt;/b&gt;＝「嵯峨」と「性（さが＝悪いところ）」を掛けている。　&lt;b&gt;奏す&lt;/b&gt;＝天皇に申し上げる。　&lt;b&gt;え申し候はじ&lt;/b&gt;＝申し上げることができません。　&lt;b&gt;おのれ放ちては&lt;/b&gt;＝おまえ以外には。　&lt;b&gt;子文字&lt;/b&gt;＝「子」という文字。　&lt;b&gt;事なくてやみにけり&lt;/b&gt;＝何事もなく終わった。</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>&lt;p&gt;今となっては昔のことだが、小野篁という人がいらっしゃった。嵯峨天皇の御代に、内裏に札が立ててあったが、（そこには）「無悪善」と書いてあった。帝が篁に「読め」とおっしゃったので、（篁は）「読むことは読めるでしょう。しかし、恐れ多いことでございますので、申し上げることはできません」と申し上げたところ、「かまわないから申せ」と、たびたびおっしゃったので、「『さが（＝嵯峨天皇）なくてよからん』と書いてございます。つまり、帝を呪い申し上げているのでございます」と申し上げたところ、（帝は）「おまえのほかに、誰がこんなものを書くだろうか」とおっしゃったので、「だからこそ、申し上げますまいと申したのでございます」と申し上げると、帝は「それでは、どんなものが書いてあっても読めるのか」とおっしゃったので、「何であっても読めましょう」と申したので、片仮名の「子」という文字を十二お書かせになって、「読め」とおっしゃったところ、「ねこの子のこねこ、ししの子のこじし」と読んだので、帝はほほえみなさって、何事もなく終わった。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1194,23 +1301,28 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;ある人、弓射ることを習ふに、諸矢をたばさみて的に向かふ。師の&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;言はく&lt;/span&gt;、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;初心の人、二つの矢を持つことなかれ&lt;/span&gt;。後の矢を頼みて、初めの矢に等閑の心あり。&lt;span class="gl"&gt;毎度ただ得失なく、この一矢に定むべしと思へ&lt;i&gt;（毎回ただ当たり外れを考えず、この一本の矢で決めようと思え）&lt;/i&gt;&lt;/span&gt;」と言ふ。&lt;span class="gl"&gt;わづかに二つの矢、師の前にて一つをおろかにせんと思はんや&lt;i&gt;（わずか二本の矢を、師の前で一本をいいかげんにしようと思うだろうか、いや思わない）&lt;/i&gt;&lt;/span&gt;。&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;懈怠の心、みづから知らずといへども、師これを知る&lt;/span&gt;。&lt;span class="gl"&gt;この戒め、万事にわたるべし&lt;i&gt;（この戒めは、すべてのことにあてはまるはずだ）&lt;/i&gt;&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;道を学する人、&lt;span class="gl"&gt;夕べには朝あらんことを思ひ、朝には夕べあらんことを思ひて、重ねてねんごろに修せんことを期す&lt;i&gt;（夜には翌朝があると思い、朝には夕方があると思って、あらためて念入りに修行しようとあてにする）&lt;/i&gt;&lt;/span&gt;。&lt;span class="gl"&gt;いはんや一刹那のうちにおいて、懈怠の心あることを知らんや&lt;i&gt;（まして、ほんの一瞬のうちに、なまけ心があることに気づくだろうか、いや気づかない）&lt;/i&gt;&lt;/span&gt;。なんぞ、&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;ただ今の一念において、直ちにすることの、はなはだ難き&lt;/span&gt;。&lt;/p&gt;</t>
+          <t>ある人が弓を習っていたときの、師とのやりとりである。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
+          <t>&lt;p&gt;ある人、弓射ることを習ふに、諸矢をたばさみて的に&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;向かふ&lt;/span&gt;。師の&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;言はく&lt;/span&gt;、「初心の人、二つの矢を持つことなかれ。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;後の矢を頼みて、初めの矢に等閑の心あり&lt;/span&gt;。毎度ただ得失なく、この一矢に定むべしと思へ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;言ふ&lt;/span&gt;。&lt;ruby class="gl"&gt;わづかに&lt;rt&gt;わずか&lt;/rt&gt;&lt;/ruby&gt;二つの矢、師の前にて一つをおろかにせんと&lt;ruby class="gl"&gt;思はんや&lt;rt&gt;思うだろうか&lt;/rt&gt;&lt;/ruby&gt;。懈怠の心、みづから知らずといへども、師&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;これを知る&lt;/span&gt;。この戒め、万事にわたるべし。&lt;/p&gt;&lt;p&gt;道を学する人、夕べには朝あらんことを思ひ、朝には夕べあらんことを思ひて、重ねてねんごろに修せんことを期す。&lt;ruby class="gl"&gt;いはんや&lt;rt&gt;まして&lt;/rt&gt;&lt;/ruby&gt;一刹那のうちにおいて、懈怠の心あることを知らんや。なんぞ、ただ今の一念において、直ちにすることの、はなはだ難き。&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
           <t>&lt;b&gt;諸矢&lt;/b&gt;＝二本一組の矢。　&lt;b&gt;たばさみて&lt;/b&gt;＝手にはさんで。　&lt;b&gt;初心の人&lt;/b&gt;＝初心者。　&lt;b&gt;頼みて&lt;/b&gt;＝あてにして。　&lt;b&gt;等閑の心&lt;/b&gt;＝いいかげんな気持ち。　&lt;b&gt;得失なく&lt;/b&gt;＝当たり外れを考えず。　&lt;b&gt;おろかに&lt;/b&gt;＝いいかげんに。　&lt;b&gt;懈怠&lt;/b&gt;＝なまけ心。　&lt;b&gt;万事&lt;/b&gt;＝すべてのこと。　&lt;b&gt;道を学する人&lt;/b&gt;＝仏道を学ぶ人。　&lt;b&gt;ねんごろに修せん&lt;/b&gt;＝念入りに修行しよう。　&lt;b&gt;期す&lt;/b&gt;＝あてにする。　&lt;b&gt;一刹那&lt;/b&gt;＝ごくわずかな時間。　&lt;b&gt;一念&lt;/b&gt;＝ほんの一瞬の心。</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>&lt;p&gt;ある人が弓を射ることを習うときに、二本の矢を手にはさんで的に向かった。師が言うことには、「初心者は二本の矢を持ってはならない。あとの矢をあてにして、初めの矢をいいかげんに射る心が生じる。毎回、ただ当たり外れを考えず、この一本の矢で決めようと思え」と言う。わずか二本の矢を、師の前で一本をいいかげんにしようと思うだろうか（いや、思わない）。しかし、なまけ心は、自分では気づかないけれども、師はこれを見抜いている。この戒めは、すべてのことにあてはまるはずだ。&lt;/p&gt;&lt;p&gt;仏道を学ぶ人は、夜には翌朝があると思い、朝には夕方があると思って、あらためて念入りに修行しようとあてにする。まして、ほんの一瞬のうちに、なまけ心があることに気づくだろうか（いや、気づかない）。どうして、ただ今のこの一瞬において、すぐに実行することが、こんなにも難しいのか。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1239,23 +1351,28 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;ある山寺に、四人の僧集まりて、七日の間、無言の行をぞ始めける。&lt;span class="gl"&gt;一夜、風吹きて、灯明の消えたりけるに&lt;i&gt;（ある夜、風が吹いて仏前のあかりが消えてしまったので）&lt;/i&gt;&lt;/span&gt;、下座の僧、&lt;span class="gl"&gt;こらへかねて&lt;i&gt;（こらえきれずに）&lt;/i&gt;&lt;/span&gt;、「火が消えたり。とく点せ」と言ふ。&lt;/p&gt;&lt;p&gt;第二の僧、これを聞きて、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;無言の行に、もの&lt;span class="mk"&gt;②&lt;/span&gt;言ふべきか&lt;/span&gt;」と、にがにがしげにとがめけり。第三の僧、「二人ながらもの言ひたり。口惜しきことなり」と言ふ。&lt;/p&gt;&lt;p&gt;上座の僧、うちうなづきて、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;われ一人こそもの言はね&lt;/span&gt;」と言ひけり。&lt;/p&gt;</t>
+          <t>ある山寺で、四人の僧が、七日の間いっさい口をきかないという修行を始めた。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;無言の行&lt;/b&gt;＝一定の期間、いっさい口をきかない修行。　&lt;b&gt;灯明&lt;/b&gt;＝仏前のあかり。　&lt;b&gt;下座&lt;/b&gt;＝いちばん位の低い者。　&lt;b&gt;とく&lt;/b&gt;＝早く。　&lt;b&gt;点せ&lt;/b&gt;＝ともせ。　&lt;b&gt;にがにがしげに&lt;/b&gt;＝不愉快そうに。　&lt;b&gt;とがめけり&lt;/b&gt;＝非難した。　&lt;b&gt;二人ながら&lt;/b&gt;＝二人とも。　&lt;b&gt;口惜しき&lt;/b&gt;＝残念な。情けない。　&lt;b&gt;上座&lt;/b&gt;＝いちばん位の高い者。　※読みやすいように表記を一部改めています。</t>
+          <t>&lt;p&gt;ある山寺に、四人の僧集まりて、七日の間、無言の行をぞ始めける。一夜、風吹きて、灯明の消えたりけるに、下座の僧、&lt;ruby class="gl"&gt;こらへかねて&lt;rt&gt;こらえきれずに&lt;/rt&gt;&lt;/ruby&gt;、「火が消えたり。とく点せ」と言ふ。&lt;/p&gt;&lt;p&gt;第二の僧、&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;これ&lt;/span&gt;を聞きて、「無言の行に、もの&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;言ふべきか&lt;/span&gt;」と、にがにがしげにとがめけり。第三の僧、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;二人&lt;/span&gt;ながらもの言ひたり。口惜しきことなり」と言ふ。&lt;/p&gt;&lt;p&gt;上座の僧、&lt;ruby class="gl"&gt;うちうなづきて&lt;rt&gt;うなずいて&lt;/rt&gt;&lt;/ruby&gt;、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;われ&lt;/span&gt;一人こそ&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;もの言はね&lt;/span&gt;」と言ひけり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;無言の行&lt;/b&gt;＝一定の期間、いっさい口をきかない修行。　&lt;b&gt;灯明&lt;/b&gt;＝仏前のあかり。　&lt;b&gt;下座&lt;/b&gt;＝いちばん位の低い者。　&lt;b&gt;とく&lt;/b&gt;＝早く。　&lt;b&gt;点せ&lt;/b&gt;＝ともせ。　&lt;b&gt;にがにがしげに&lt;/b&gt;＝不愉快そうに。　&lt;b&gt;とがめけり&lt;/b&gt;＝非難した。　&lt;b&gt;口惜しき&lt;/b&gt;＝残念な。情けない。　&lt;b&gt;上座&lt;/b&gt;＝いちばん位の高い者。　※読みやすいように表記を一部改めています。</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
           <t>&lt;p&gt;ある山寺で、四人の僧が集まって、七日の間、無言の行を始めた。ある夜、風が吹いて、仏前のあかりが消えてしまったので、いちばん下位の僧が、こらえきれずに「火が消えた。早くともせ」と言う。&lt;/p&gt;&lt;p&gt;二番目の僧が、これを聞いて、「無言の行なのに、ものを言ってよいものか」と、不愉快そうに非難した。三番目の僧は、「二人ともものを言ってしまった。情けないことだ」と言う。&lt;/p&gt;&lt;p&gt;いちばん上位の僧は、うなずいて、「私一人だけは、ものを言っていない」と言った。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1284,23 +1401,28 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;九月二十日のころ、&lt;span class="gl"&gt;ある人に誘はれたてまつりて、明くるまで月見ありくこと侍りしに&lt;i&gt;（ある人にお誘いいただいて、夜明けまで月を見て歩き回ることがありましたが）&lt;/i&gt;&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;思し出づる所ありて、案内せさせて入り給ひぬ&lt;/span&gt;。荒れたる庭の露しげきに、わざとならぬ匂ひ、しめやかにうち薫りて、忍びたるけはひ、&lt;span class="gl"&gt;いとものあはれなり&lt;i&gt;（たいそうしみじみと趣深い）&lt;/i&gt;&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;よきほどにて出で給ひぬれど、なほ事ざまの優におぼえて、物の隠れよりしばし&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;見ゐたる&lt;/span&gt;に、&lt;span class="ul"&gt;&lt;span class="mk"&gt;③&lt;/span&gt;妻戸をいま少し押し開けて、月見るけしきなり&lt;/span&gt;。やがてかけこもらましかば、口惜しからまし。&lt;span class="ul"&gt;&lt;span class="mk"&gt;④&lt;/span&gt;あとまで見る人ありとは、いかでか知らん。かやうのことは、ただ朝夕の心づかひによるべし&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;その人、ほどなく失せにけりと聞き侍りし。&lt;/p&gt;</t>
+          <t>作者が、ある人に誘われて、夜通し月を見て歩いたときのことである。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;九月二十日&lt;/b&gt;＝陰暦九月二十日。月の出がおそい。　&lt;b&gt;案内せさせて&lt;/b&gt;＝取り次ぎを頼んで。　&lt;b&gt;露しげき&lt;/b&gt;＝露が多く降りている。　&lt;b&gt;わざとならぬ匂ひ&lt;/b&gt;＝わざとらしくない、自然な香のかおり。　&lt;b&gt;しめやかに&lt;/b&gt;＝しっとりと。　&lt;b&gt;忍びたるけはひ&lt;/b&gt;＝ひっそりと暮らしている様子。　&lt;b&gt;よきほどにて&lt;/b&gt;＝ちょうどよい頃合いで。　&lt;b&gt;事ざまの優に&lt;/b&gt;＝その場のようすが優雅に。　&lt;b&gt;妻戸&lt;/b&gt;＝両開きの戸。　&lt;b&gt;かけこもらましかば&lt;/b&gt;＝（戸を）閉めて引きこもってしまったなら。　&lt;b&gt;口惜しからまし&lt;/b&gt;＝残念であっただろう。　&lt;b&gt;いかでか知らん&lt;/b&gt;＝どうして知っていようか。　&lt;b&gt;失せにけり&lt;/b&gt;＝亡くなってしまった。</t>
+          <t>&lt;p&gt;九月二十日のころ、ある人に誘はれたてまつりて、明くるまで&lt;ruby class="gl"&gt;月見ありく&lt;rt&gt;月を見て歩き回る&lt;/rt&gt;&lt;/ruby&gt;こと侍りしに、思し出づる所ありて、案内せさせて&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;入り給ひぬ&lt;/span&gt;。荒れたる庭の露しげきに、わざとならぬ匂ひ、しめやかに&lt;ruby class="gl"&gt;うち薫りて&lt;rt&gt;漂って&lt;/rt&gt;&lt;/ruby&gt;、忍びたるけはひ、&lt;ruby class="gl"&gt;いとものあはれなり&lt;rt&gt;たいそう趣深い&lt;/rt&gt;&lt;/ruby&gt;。&lt;/p&gt;&lt;p&gt;よきほどにて&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;出で給ひぬれ&lt;/span&gt;ど、&lt;ruby class="gl"&gt;なほ&lt;rt&gt;やはり&lt;/rt&gt;&lt;/ruby&gt;事ざまの優におぼえて、物の隠れよりしばし&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;見ゐたる&lt;/span&gt;に、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;妻戸をいま少し押し開けて&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;月見る&lt;/span&gt;&lt;ruby class="gl"&gt;けしきなり&lt;rt&gt;様子である&lt;/rt&gt;&lt;/ruby&gt;。やがてかけこもらましかば、口惜しからまし。あとまで見る人ありとは、いかでか知らん。かやうのことは、ただ朝夕の心づかひによるべし。&lt;/p&gt;&lt;p&gt;その人、&lt;ruby class="gl"&gt;ほどなく&lt;rt&gt;まもなく&lt;/rt&gt;&lt;/ruby&gt;失せにけりと聞き侍りし。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;九月二十日&lt;/b&gt;＝陰暦九月二十日。月の出がおそい。　&lt;b&gt;案内せさせて&lt;/b&gt;＝取り次ぎを頼んで。　&lt;b&gt;露しげき&lt;/b&gt;＝露が多く降りている。　&lt;b&gt;わざとならぬ匂ひ&lt;/b&gt;＝わざとらしくない、自然な香のかおり。　&lt;b&gt;忍びたるけはひ&lt;/b&gt;＝ひっそりと暮らしている様子。　&lt;b&gt;よきほどにて&lt;/b&gt;＝ちょうどよい頃合いで。　&lt;b&gt;事ざまの優に&lt;/b&gt;＝その場のようすが優雅に。　&lt;b&gt;妻戸&lt;/b&gt;＝両開きの戸。　&lt;b&gt;かけこもらましかば&lt;/b&gt;＝（戸を）閉めて引きこもってしまったなら。　&lt;b&gt;口惜しからまし&lt;/b&gt;＝残念であっただろう。　&lt;b&gt;いかでか知らん&lt;/b&gt;＝どうして知っていようか。　&lt;b&gt;失せにけり&lt;/b&gt;＝亡くなってしまった。</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>&lt;p&gt;陰暦九月二十日ごろ、ある人にお誘いいただいて、夜明けまで月を見て歩き回ることがありましたが、（その人が）思い出しなさる家があって、取り次ぎを頼んでお入りになった。荒れた庭に露がたくさん降りているところに、わざとらしくない自然な香のかおりがしっとりと漂って、ひっそりと暮らしている様子が、たいそうしみじみと趣深い。&lt;/p&gt;&lt;p&gt;ちょうどよい頃合いで（その人は）お出になったけれど、やはりその場のようすが優雅に思われて、物陰からしばらく見ていたところ、（家の女主人は）両開きの戸をもう少し押し開けて、月を見ている様子である。もし（客を送り出して）すぐに戸を閉めて引きこもってしまったなら、残念であっただろう。（客が帰った）あとまで見ている人がいようとは、どうして知っていようか。このようなことは、ただ、ふだんからの心がけによるものであろう。&lt;/p&gt;&lt;p&gt;その人は、まもなく亡くなってしまったと聞きました。&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1317,22 +1439,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="58" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="56" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1363,40 +1486,45 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>空欄文</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>話し合い文</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>選択肢ア</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>選択肢イ</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>選択肢ウ</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>選択肢エ</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>正解</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>解説</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>配点</t>
         </is>
@@ -1420,46 +1548,47 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>主語・語意</t>
+          <t>主語・指示語</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>傍線部①「&lt;span class="kb"&gt;あさましきこと&lt;/span&gt;」とあるが、その意味として最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部Ａ〜Ｃの主語の組み合わせとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>情けなく、見苦しいことだ</t>
-        </is>
-      </c>
+      <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>驚きあきれることだ</t>
+          <t>Ａ　良秀　　　Ｂ　良秀　　　Ｃ　良秀</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>うらやましく、ねたましいことだ</t>
+          <t>Ａ　良秀　　　Ｂ　見舞いに来た人々　　　Ｃ　良秀</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>みっともなく、卑しいことだ</t>
+          <t>Ａ　見舞いに来た人々　　　Ｂ　良秀　　　Ｃ　良秀</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
+          <t>Ａ　良秀　　　Ｂ　良秀　　　Ｃ　見舞いに来た人々</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
           <t>イ</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>古語の「&lt;b&gt;あさまし&lt;/b&gt;」は「驚きあきれる」の意。現代語の「あさましい（下品だ・卑しい）」とは意味が異なる、頻出の要注意語です。ここは、家が焼けているのに騒がない良秀を見た人々の言葉なので「驚きあきれる」が合います。</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="n">
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Ａ「騒がず」は、見舞いに来た人々に対して&lt;b&gt;良秀&lt;/b&gt;が騒がないという意味。Ｂは直前の「とぶらひに来たる者ども」が主語で、Ｃ「立てりけれ」は、あざ笑って立っていた&lt;b&gt;良秀&lt;/b&gt;。&lt;b&gt;会話の直前にある人物&lt;/b&gt;をたどるのが、主語をつかむこつです。</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1486,41 +1615,42 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>傍線部②「&lt;span class="kb"&gt;向かひ&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部①「&lt;span class="kb"&gt;向かひ&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>むかい</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>むかひ</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>むこう</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>むかえ</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>語頭以外の「&lt;b&gt;は・ひ・ふ・へ・ほ&lt;/b&gt;」は「&lt;b&gt;わ・い・う・え・お&lt;/b&gt;」に直します（は行転呼）。「向かひ」→「むかい」。埼玉県では問2でこの直し方が毎年問われます。</t>
         </is>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="N3" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1547,41 +1677,46 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>傍線部③「&lt;span class="kb"&gt;時々笑ひけり&lt;/span&gt;」とあるが、良秀が笑ったのはなぜか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>家も妻子も失ったつらさを人に見せまいと、無理に平気なふりをしていたから。</t>
-        </is>
-      </c>
+          <t>傍線部②「&lt;span class="kb"&gt;これこそせうとくよ&lt;/span&gt;」とありますが、良秀はどのようなことをもうけものだと言っているのですか。次の空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>家が焼けたおかげで、&lt;span class="blank"&gt;　　&lt;/span&gt;こと。</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>見舞いに来た人々が自分を心配してくれるのが、うれしくてたまらなかったから。</t>
+          <t>新しい家を建て直す機会を得た</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>燃えさかる炎を見て、これまでうまく描けなかった不動明王の火炎の描き方を会得したから。</t>
+          <t>妻子や仏の絵を失わずにすんだ</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>自分だけが火事から逃げおおせたことを、まわりの人に自慢したかったから。</t>
+          <t>これまでうまく描けなかった不動明王の火炎の描き方がわかった</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
+          <t>多くの人が見舞いに来てくれた</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
           <t>ウ</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>良秀自身が「年ごろ不動尊の火焰をあしく書きけるなり。今見れば、かうこそ燃えけれと、&lt;b&gt;心得つるなり&lt;/b&gt;」と語っています。「心得つ」＝会得した、の意。「つらさを隠して無理に平気なふりをしていた」という説明は、本文からは読み取れません。</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>直前に「年ごろ不動尊の火焰をあしく書きけるなり。今見れば、かうこそ燃えけれと、&lt;b&gt;心得つるなり&lt;/b&gt;」とあります。「心得つ」＝会得した。燃えさかる本物の炎を見て、描き方をつかんだことを「せうとく（もうけもの）」と言っています。</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1608,45 +1743,46 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>次は、この文章を読んだ生徒たちと先生の話し合いの一部である。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「この話は、良秀という絵仏師の姿を通して何を描いているでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「家が焼けているのに騒がず、それどころか笑っています。ふつうの感覚ではありませんね。」&lt;br&gt;&lt;span class="sp"&gt;Ｂさん&lt;/span&gt;「でも良秀は『これこそせうとくよ』と言っています。つまり良秀にとっては&lt;span class="blank"&gt;　　&lt;/span&gt;ということなのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そうですね。だからこそ、最後に『よぢり不動』が名作として語り伝えられているのですね。」</t>
-        </is>
-      </c>
+          <t>次は、この文章を読んだあとの先生とＡさんの会話です。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>火事に遭ったのは、絵の腕を上げよという神仏のはからいだ</t>
+          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「この文章で、良秀はどのような人物として描かれているでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「家が焼けているのに騒がず、それどころか笑っています。傍線部②の言葉から考えると、良秀は&lt;span class="blank"&gt;　　&lt;/span&gt;人物として描かれているのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。だからこそ最後に、良秀のかいた不動明王の絵が名作として語り伝えられているのですね。」</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>人に笑われても気にしないことが、絵仏師として生きるための心得だ</t>
+          <t>損得に敏感で、何事も金銭に結びつけて考える</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>焼けた家の損害は、絵を売ればすぐに取り返せるものだ</t>
+          <t>家族思いで、まわりの人への気配りを忘れない</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>家族や財産を失うことよりも、絵の道を究めることのほうが大切だ</t>
+          <t>何事にも動じず、人の意見にはいっさい耳を貸さない</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
+          <t>家族や財産よりも、絵の道を究めることを大切にする</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
           <t>エ</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>良秀は、妻子も仏画も家の中にあるのに気にかけず、炎の描き方を会得したことを「せうとく（もうけもの）」と言い切ります。&lt;b&gt;芸道を何よりも優先する執念&lt;/b&gt;が描かれた話です。「神仏のはからい」「人に笑われても気にしない心得」「絵を売れば取り返せる」といった内容は、本文中に述べられていません。</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>良秀は、妻子も仏の絵も家の中にあるのに気にかけず、炎の描き方を会得したことだけを「せうとく」と言い切ります。&lt;b&gt;芸の道を何よりも優先する姿&lt;/b&gt;が描かれた話です。</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1668,46 +1804,47 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>内容理解</t>
+          <t>主語・指示語</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>傍線部①「&lt;span class="kb"&gt;丹後へつかはしける人は参りたりや。いかに心もとなくおぼすらむ&lt;/span&gt;」とあるが、定頼中納言がこう言ったのはどういうつもりからか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部Ａ〜Ｃの主語の組み合わせとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>歌合に出る自信のない小式部内侍に、助言をしてやろうとしている。</t>
-        </is>
-      </c>
+      <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>母の代わりに歌をよまなければならない小式部内侍を、心から気の毒に思っている。</t>
+          <t>Ａ　小式部内侍　　　Ｂ　小式部内侍　　　Ｃ　定頼中納言</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>母に歌の代作を頼んだ使いの返事がまだ来ないだろうと、小式部内侍をからかっている。</t>
+          <t>Ａ　定頼中納言　　　Ｂ　小式部内侍　　　Ｃ　小式部内侍</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>遠く丹後にいる母の身を案じている小式部内侍を、なぐさめようとしている。</t>
+          <t>Ａ　定頼中納言　　　Ｂ　小式部内侍　　　Ｃ　定頼中納言</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
+          <t>Ａ　定頼中納言　　　Ｂ　定頼中納言　　　Ｃ　小式部内侍</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
           <t>ウ</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>直前に「&lt;b&gt;たはぶれて&lt;/b&gt;（＝ふざけて）」とあるのが手がかり。小式部内侍の歌は母の代作だという噂をふまえ、「代作を頼みに丹後へやった使いはもう帰ってきましたか」とからかったのです。</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Ａはからかいの言葉なので&lt;b&gt;定頼中納言&lt;/b&gt;。Ｂは袖を引きとめて歌をよみかけた&lt;b&gt;小式部内侍&lt;/b&gt;。Ｃ「逃げられけり」の「&lt;b&gt;られ&lt;/b&gt;」は尊敬で、身分の高い定頼への敬意を表します。&lt;b&gt;敬語の有無&lt;/b&gt;も主語を見分ける手がかりになります。</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1734,41 +1871,42 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>傍線部②「&lt;span class="kb"&gt;わづかに&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部①「&lt;span class="kb"&gt;わづかに&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>わつかに</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>わじかに</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>わづかに</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>わずかに</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>エ</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>歴史的仮名遣いの「&lt;b&gt;ぢ・づ&lt;/b&gt;」は、現代仮名遣いでは「&lt;b&gt;じ・ず&lt;/b&gt;」に直します。「わづかに」→「わずかに」。</t>
         </is>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1795,41 +1933,46 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>傍線部③「&lt;span class="kb"&gt;返しにも及ばず、袖を引き放ちて逃げられけり&lt;/span&gt;」とあるが、定頼中納言がこのようにしたのはなぜか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>代作を疑ってからかった相手が、その場でみごとな歌をよんだので、驚ききまり悪くなったから。</t>
-        </is>
-      </c>
+          <t>傍線部②「&lt;span class="kb"&gt;思はずにあさましくて&lt;/span&gt;」とありますが、定頼中納言がこのようになったのはなぜですか。次の空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>からかった相手の小式部内侍が、&lt;span class="blank"&gt;　　&lt;/span&gt;から。</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>小式部内侍に袖をつかまれた姿を人に見られるのが、恥ずかしかったから。</t>
+          <t>その場ですぐに、みごとな歌をよみかけてきた</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>小式部内侍の歌があまりに下手で、返歌をする気にもなれなかったから。</t>
+          <t>歌合に出るのをやめると言い出した</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>歌合の始まる時刻が迫っていて、返歌をする余裕がなかったから。</t>
+          <t>母に代作を頼んだことを、その場で正直に認めた</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
+          <t>からかいに腹を立てて、無言で袖をつかんできた</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>「&lt;b&gt;思はずにあさましくて&lt;/b&gt;」＝思いがけないことで驚きあきれて、が直接の手がかり。からかった相手にその場で即興の名歌を返され、返歌もできずに逃げ出した、という場面です。</t>
-        </is>
-      </c>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>「あさまし」は&lt;b&gt;驚きあきれる&lt;/b&gt;の意。代作を疑ってからかった相手が、その場で即興の名歌を返してきたので、返歌もできずに逃げ出した、という場面です。</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1856,45 +1999,46 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>次は、この文章を読んだ生徒たちと先生の話し合いの一部である。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「小式部内侍の歌には、どんな工夫がありますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「地名の『いくの』に『行く野』を、『ふみ』に『踏み』と『文』を掛けています。」&lt;br&gt;&lt;span class="sp"&gt;Ｂさん&lt;/span&gt;「そのうえでこの歌は、&lt;span class="blank"&gt;　　&lt;/span&gt;という意味になり、定頼のからかいへの切り返しになっていると思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。だからこそ定頼は返歌もできなかったのですね。」</t>
-        </is>
-      </c>
+          <t>次は、この文章を読んだあとの先生とＡさんの会話です。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
+          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「小式部内侍の歌には、どのような工夫がありますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「地名の『いくの』に『行く野』を、『ふみ』に『踏み』と『文』を掛けています。そのうえでこの歌は&lt;span class="blank"&gt;　　&lt;/span&gt;という意味になり、定頼のからかいへの切り返しになっています。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。だから定頼は返歌もできなかったのですね。」</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>天の橋立の景色を実際に見なければ、すぐれた歌はよむことができない</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>母のいる丹後は遠いので、まだ天の橋立の地を踏んでもいないし、母からの手紙も見ていない</t>
-        </is>
-      </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>母のいる丹後は近いので、いつでも自由に手紙のやりとりをすることができる</t>
+          <t>母のいる丹後は遠いので、天の橋立を踏んだことも、母からの手紙を見たこともない</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
+          <t>母のいる丹後は近いので、いつでも自由に手紙のやりとりができる</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
           <t>母に代作を頼んだのだから、返事が来るまでもうしばらく待ってほしい</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>イ</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>「まだ&lt;b&gt;ふみ&lt;/b&gt;もみず」に「（天の橋立を）踏み」と「（母からの）文」が掛けてあります。&lt;b&gt;手紙のやりとりすらしていない＝代作などしていない&lt;/b&gt;、という反論になっているのです。</t>
         </is>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="N9" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1916,46 +2060,47 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>主語・語意</t>
+          <t>主語・指示語</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>傍線部①「&lt;span class="kb"&gt;あやまちすな。心して降りよ&lt;/span&gt;」とあるが、この言葉を言ったのは誰か。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部Ａ〜Ｃの主語の組み合わせとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>作者（兼好法師）</t>
-        </is>
-      </c>
+      <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>その場で見物していた人々</t>
+          <t>Ａ　木に登った人　　　Ｂ　木登りの名人　　　Ｃ　木登りの名人</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>高い木に登った人</t>
+          <t>Ａ　木登りの名人　　　Ｂ　木登りの名人　　　Ｃ　木に登った人</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>木登りの名人といわれた男</t>
+          <t>Ａ　木に登った人　　　Ｂ　木登りの名人　　　Ｃ　木に登った人</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
+          <t>Ａ　木登りの名人　　　Ｂ　木に登った人　　　Ｃ　木登りの名人</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
           <t>エ</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>直前が「（男が人を）&lt;b&gt;掟てて&lt;/b&gt;、高き木に&lt;b&gt;登せて&lt;/b&gt;梢を切らせしに」なので、動作の主体は一貫して「高名の木登りといひしをのこ」。声をかけられた側が「いかにかく言ふぞ」と問い返している点からも確認できます。&lt;b&gt;主語（動作主）を問う問題は埼玉県の定番&lt;/b&gt;です。</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="n">
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>声をかけたＡ、その理由を語るＣが&lt;b&gt;木登りの名人&lt;/b&gt;。「いかにかく言ふぞ（どうしてそのように言うのか）」と問い返しているＢが&lt;b&gt;木に登った人&lt;/b&gt;です。&lt;b&gt;問いかけと答えが交互になる&lt;/b&gt;ことをつかむと見分けられます。</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1982,41 +2127,42 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>傍線部②「&lt;span class="kb"&gt;危ふく&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部①「&lt;span class="kb"&gt;危ふく&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>あやゆく</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>あやふく</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>あやうく</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>あやおく</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>ウ</t>
         </is>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>語頭以外の「ふ」は「う」に直すので、「あやふく」→「&lt;b&gt;あやうく&lt;/b&gt;」。</t>
         </is>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="N11" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2043,41 +2189,46 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>傍線部③について、男が、高い所では何も言わず、安全な高さになってから注意したのはなぜか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>高い所では、声をかけても相手に届かないから。</t>
-        </is>
-      </c>
+          <t>傍線部②「&lt;span class="kb"&gt;あやまちは、安き所になりて、必ず仕る事に候ふ&lt;/span&gt;」とありますが、この男はけがをする理由をどのように考えていますか。次の空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>けがは、&lt;span class="blank"&gt;　　&lt;/span&gt;ときに起こるものだから。</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>危険な所では本人が自分で恐れて用心しているが、安全な所になると油断してけがをするものだから。</t>
+          <t>本人が自分で恐れて、用心している</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>高い所で声をかけると、相手が驚いて落ちてしまうから。</t>
+          <t>安全な高さになって、気をゆるめた</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>高い所での作業は、自分が指図できる範囲を超えているから。</t>
+          <t>人から声をかけられて、驚いた</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
+          <t>目がくらむような、高く危ない所にいる</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
           <t>イ</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>本文に「&lt;b&gt;おのれが恐れ侍れば申さず&lt;/b&gt;」「あやまちは、&lt;b&gt;安き所になりて、必ず仕る事&lt;/b&gt;に候ふ」とあります。「声をかけると驚いて落ちてしまうから」という理由は、一見もっともらしいですが本文には書かれていません。</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="n">
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>本文に「目くるめき、枝危ふきほどは、&lt;b&gt;おのれが恐れ侍れば申さず&lt;/b&gt;」とあります。危険なうちは本人が用心しているので言わない、安全になってからが危ない、という考え方です。</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2104,45 +2255,46 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>次は、この文章を読んだ生徒たちと先生の話し合いの一部である。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「作者は、この木登りの言葉をどう受け止めていますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「『あやしき下臈なれども、聖人の戒めにかなへり』と述べています。」&lt;br&gt;&lt;span class="sp"&gt;Ｂさん&lt;/span&gt;「つまり作者は、&lt;span class="blank"&gt;　　&lt;/span&gt;と考えているのですね。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そうですね。だから最後に蹴鞠の例も挙げているのです。」</t>
-        </is>
-      </c>
+          <t>次は、この文章を読んだあとの先生とＡさんの会話です。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>身分は低くても、その言葉は聖人の教えに通じる道理を含み、あらゆる事にあてはまる</t>
+          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「作者は、この男の言葉をどのように受け止めていますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「『あやしき下臈なれども、聖人の戒めにかなへり』とあります。そのあとに蹴鞠の例も挙げているので、作者は&lt;span class="blank"&gt;　　&lt;/span&gt;と考えているのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。」</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>危険な仕事をする者は、聖人と同じように尊敬されなければならない</t>
+          <t>この教えは木登りだけでなく、あらゆる事にあてはまる</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
+          <t>木登りや蹴鞠のような技芸は、書物による学問よりもすぐれている</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>危険な仕事をする者こそ、聖人と同じように尊敬されるべきだ</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
           <t>身分の低い者の言うことは、たいてい聖人の教えと同じ内容になる</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>木登りや蹴鞠のような技芸は、書物による学問よりもすぐれている</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>「あやしき下臈&lt;b&gt;なれども&lt;/b&gt;（＝身分は低いけれども）」という逆接がポイント。さらに蹴鞠の例を挙げて、この教えが&lt;b&gt;他の物事にも広くあてはまる&lt;/b&gt;ことを示しています。</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="n">
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>「あやしき下臈&lt;b&gt;なれども&lt;/b&gt;（＝身分は低いけれども）」という逆接に加え、蹴鞠という別の分野の例を挙げることで、&lt;b&gt;他の物事にも広くあてはまる&lt;/b&gt;教えだと示しています。</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2164,46 +2316,47 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>主語・語意</t>
+          <t>主語・指示語</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>傍線部①「&lt;span class="kb"&gt;かばかりと心得て帰りにけり&lt;/span&gt;」の意味として最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部Ａ〜Ｃの主語の組み合わせとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>これだけのものだと思い込んで帰ってしまった</t>
-        </is>
-      </c>
+      <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>これほど尊いものかと感激して帰った</t>
+          <t>Ａ　法師　　　Ｂ　ほかの参拝者　　　Ｃ　法師</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>これくらいの時間で帰れると見当をつけて帰った</t>
+          <t>Ａ　法師　　　Ｂ　ほかの参拝者　　　Ｃ　かたへの人</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>これでは足りないと気づいて帰った</t>
+          <t>Ａ　ほかの参拝者　　　Ｂ　法師　　　Ｃ　法師</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
+          <t>Ａ　法師　　　Ｂ　法師　　　Ｃ　かたへの人</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>「かばかり」＝これだけ、これほど。「心得」＝理解する、思い込む。ふもとの寺社だけを拝んで「石清水はこれだけのものだ」と&lt;b&gt;早合点した&lt;/b&gt;ことを表します。</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="n">
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Ａ・Ｃはどちらも&lt;b&gt;法師&lt;/b&gt;。Ｂは「参りたる人ごとに」とあるとおり、法師が見ていた&lt;b&gt;ほかの参拝者&lt;/b&gt;です。法師はその人たちが山へ登るわけがわからないまま帰っています。</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2230,41 +2383,42 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>傍線部②「&lt;span class="kb"&gt;まうでけり&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部①「&lt;span class="kb"&gt;まうでけり&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>まうでけり</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>もうでけり</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>まいでけり</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>まおでけり</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>イ</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>「&lt;b&gt;au&lt;/b&gt;」と続く音は「&lt;b&gt;ô（オー）&lt;/b&gt;」と読み、現代仮名遣いでは「おう」と書きます。「まうで（ma-u-de）」→「&lt;b&gt;もうで&lt;/b&gt;」。同じ例に「けふ（kefu→kyô）→きょう」「やうやう→ようよう」があります。</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="n">
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>「&lt;b&gt;au&lt;/b&gt;」と続く音は「&lt;b&gt;ô（オー）&lt;/b&gt;」と読み、現代仮名遣いでは「おう」と書きます。「まうで（ma-u-de）」→「&lt;b&gt;もうで&lt;/b&gt;」。同じ例に「けふ→きょう」「やうやう→ようよう」があります。</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2291,41 +2445,46 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>傍線部③から、この法師が石清水八幡宮を拝めなかった理由が分かる。その理由として最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>参拝の作法を知らず、社殿に入れてもらえなかったから。</t>
-        </is>
-      </c>
+          <t>傍線部②「&lt;span class="kb"&gt;ゆかしかりしかど&lt;/span&gt;」とありますが、法師はこのあとどうしましたか。次の空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>ほかの参拝者が山へ登るわけを、&lt;span class="blank"&gt;　　&lt;/span&gt;。</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>一人で出かけたため、途中で道に迷ってしまったから。</t>
+          <t>知ってはいたが、あえて登らずに帰った</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>山道が険しく、途中で引き返してしまったから。</t>
+          <t>人にたずねてみたが、教えてもらえなかった</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>ふもとの極楽寺・高良などを石清水八幡宮だと思い込み、山上まで登らなかったから。</t>
+          <t>まったく気にもとめずに帰った</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
+          <t>知りたいと思ったが、人にたずねずに帰った</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
           <t>エ</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>石清水八幡宮は&lt;b&gt;男山の山上&lt;/b&gt;にあります。法師はふもとの極楽寺・高良を拝んだだけで満足し、他の参拝者が山へ登る意味も分からないまま帰ってしまいました。</t>
-        </is>
-      </c>
-      <c r="M16" s="4" t="n">
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>「何事かありけん、&lt;b&gt;ゆかしかりしかど&lt;/b&gt;（＝知りたかったけれど）」が根拠。知りたいと思いながら人にたずねなかったことが、最後の「先達はあらまほしき」につながります。</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2352,45 +2511,46 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>次は、この文章を読んだ生徒たちと先生の話し合いの一部である。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「最後の一文『少しのことにも、先達はあらまほしきことなり』は、どういうことですか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「法師は、ほかの参拝者が山へ登るのを見ながらも、自分の思い込みで&lt;span class="blank"&gt;　　&lt;/span&gt;。」&lt;br&gt;&lt;span class="sp"&gt;Ｂさん&lt;/span&gt;「だから作者は、ちょっとしたことでも案内してくれる人がいてほしいものだ、と述べているのですね。」</t>
-        </is>
-      </c>
+          <t>次は、この文章を読んだあとの先生とＡさんの会話です。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>仲間に自慢話をして、かえって笑われてしまいました</t>
+          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「最後の一文『少しのことにも、先達はあらまほしきことなり』は、どういうことですか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「法師は&lt;span class="blank"&gt;　　&lt;/span&gt;のに、そのことに気づかないまま満足して帰っています。だから作者は、ちょっとしたことでも案内者はいてほしいものだ、と述べているのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。」</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>何度も同じ場所をお参りして、時間を無駄にしてしまいました</t>
+          <t>同じ場所を何度もお参りして、時間を無駄にしてしまった</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>人にたずねることをせず、肝心の石清水八幡宮を拝まずに帰ってしまいました</t>
+          <t>山の上からの景色を見ることを、あきらめてしまった</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>山の上からの景色を楽しむことを、あきらめてしまいました</t>
+          <t>ふもとの寺社を拝んだだけで、肝心の石清水八幡宮を拝んでいない</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
+          <t>仲間に自慢話をして、かえって笑われてしまった</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
           <t>ウ</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>法師は「ゆかしかりしかど」と&lt;b&gt;疑問を感じながらも人にたずねず&lt;/b&gt;、目的を果たせないまま満足して帰りました。だからこそ「先達（案内者）はあらまほしき」と結ばれるのです。</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="n">
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>石清水八幡宮は&lt;b&gt;男山の山上&lt;/b&gt;にあります（注）。法師はふもとの極楽寺・高良を拝んだだけで「かばかり（これだけのものだ）」と早合点し、本来の目的を果たせずに帰ったのです。</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2412,46 +2572,47 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>内容理解</t>
+          <t>主語・指示語</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>傍線部①「&lt;span class="kb"&gt;うれしとは思へども、ただ一度にいらへむも、待ちけるかともぞ思ふ&lt;/span&gt;」とあるが、児がすぐに返事をしなかったのはなぜか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部Ａ〜Ｃの主語の組み合わせとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>ほんとうに眠ってしまい、目を覚ますことができなかったから。</t>
-        </is>
-      </c>
+      <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>ぼたもちが好きではなく、食べたいと思わなかったから。</t>
+          <t>Ａ　児　　　Ｂ　児　　　Ｃ　僧</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>すぐに返事をすると、ぼたもちを待っていたのだと僧たちに思われそうだったから。</t>
+          <t>Ａ　僧たち　　　Ｂ　児　　　Ｃ　児</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>僧たちの呼ぶ声が小さくて、よく聞き取れなかったから。</t>
+          <t>Ａ　僧たち　　　Ｂ　児　　　Ｃ　僧</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
+          <t>Ａ　僧たち　　　Ｂ　僧たち　　　Ｃ　児</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
           <t>ウ</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>「待ちけるか&lt;b&gt;ともぞ思ふ&lt;/b&gt;」＝「待っていたのかと（僧たちが）思うといけない」の意。「もぞ」は&lt;b&gt;心配・危惧&lt;/b&gt;を表します。ぼたもちを待ちわびていたと思われたくない、という児の見えっぱりな心情です。</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="n">
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Ａ「いざ、かいもちひせむ」と言ったのは&lt;b&gt;僧たち&lt;/b&gt;。Ｂ「出で来るを待ちける」のは、寝たふりをしていた&lt;b&gt;児&lt;/b&gt;。Ｃ「幼き人は寝入りたまひにけり」と言ったのは&lt;b&gt;僧&lt;/b&gt;です。</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2478,41 +2639,42 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>傍線部②「&lt;span class="kb"&gt;いらへむ&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部①「&lt;span class="kb"&gt;いらへむ&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>いらえん</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>いらえむ</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>いらへむ</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>いらへん</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>語頭以外の「へ」は「え」に直し、さらに&lt;b&gt;助動詞「む」は「ん」&lt;/b&gt;と書き直します。「いらへむ」→「&lt;b&gt;いらえん&lt;/b&gt;」。</t>
         </is>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="N19" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2539,41 +2701,46 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>傍線部③「&lt;span class="kb"&gt;あな、わびし&lt;/span&gt;」とあるが、児がこう思ったのはなぜか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>僧たちが自分をきらって、わざと起こさなかったのだと気づいたから。</t>
-        </is>
-      </c>
+          <t>傍線部②「&lt;span class="kb"&gt;待ちけるかともぞ思ふ&lt;/span&gt;」とありますが、児がすぐに返事をしなかったのはなぜですか。次の空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>すぐに返事をすると、&lt;span class="blank"&gt;　　&lt;/span&gt;と思ったから。</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>ぼたもちを作る手伝いをさせられそうになったから。</t>
+          <t>寝たふりをしていたことを叱られる</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>寝たふりをしていたことを、僧たちに見破られてしまったから。</t>
+          <t>僧たちの眠りをさまたげてしまう</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>もう一度呼んでもらえず、そのまま寝入ったものと思われてしまったから。</t>
+          <t>ぼたもちを分けてもらえなくなる</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
+          <t>ぼたもちを待っていたのだと僧たちに思われてしまう</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
           <t>エ</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>直前の僧の言葉「な起こしたてまつりそ。&lt;b&gt;幼き人は寝入りたまひにけり&lt;/b&gt;」がきっかけ。もう一声呼ばれるのを待っていたのに、呼ばれなくなってしまった、というがっかり感です。</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="n">
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>「待ちけるか&lt;b&gt;ともぞ思ふ&lt;/b&gt;」＝「待っていたのかと（僧たちが）思うといけない」の意。「もぞ」は&lt;b&gt;心配・危惧&lt;/b&gt;を表します。待ちわびていたと思われたくない、という見えっぱりな心情です。</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2600,45 +2767,46 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>次は、この文章を読んだ生徒と先生の話し合いの一部である。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「傍線部④で僧たちが『笑ふこと限りなし』となったのは、なぜでしょう。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「児が『えい』と返事をしたのが、&lt;span class="blank"&gt;　　&lt;/span&gt;だったからです。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そうですね。その一言で、寝たふりをして待っていたことがすっかり分かってしまう。児のいじらしくもおかしみのある姿が、生き生きと描かれていますね。」</t>
-        </is>
-      </c>
+          <t>次は、この文章を読んだあとの先生とＡさんの会話です。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
+          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「最後に僧たちが『笑ふこと限りなし』となったのは、なぜでしょう。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「児が『えい』と返事をしたのが&lt;span class="blank"&gt;　　&lt;/span&gt;だったので、寝たふりをして待っていたことが、すっかりわかってしまったからだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。児のいじらしくもおかしみのある姿が、生き生きと描かれていますね。」</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>寝言のように小さく、ほとんど聞き取れない返事</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>僧たちが食べる音がしてから、ずいぶんたったあとの返事</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
           <t>声をかけられてすぐの、たいへん元気のよい返事</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>呼ばれてからずいぶん時間がたったあとの、間の抜けた返事</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>僧たちの問いかけとは、まったく関係のない返事</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>寝言のように小さく、ほとんど聞き取れない返事</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>イ</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>「&lt;b&gt;無期ののちに&lt;/b&gt;（＝ずいぶん時間がたってから）」がポイント。食べる音がしてからようやく「えい」と答えたので、寝たふりをして待っていたことが見え見えになってしまったのです。</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="n">
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>「&lt;b&gt;無期ののちに&lt;/b&gt;（＝ずいぶん時間がたってから）」がポイント。食べる音がしてからようやく返事をしたので、寝たふりをして待っていたことが見え見えになってしまったのです。</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2660,46 +2828,47 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>主語・語意</t>
+          <t>主語・指示語</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>傍線部①「&lt;span class="kb"&gt;あはれなるありさまかな&lt;/span&gt;」とあるが、このように思ったのは誰か。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部Ａ〜Ｃの主語の組み合わせとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>蟻</t>
-        </is>
-      </c>
+      <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>鳩</t>
+          <t>Ａ　蟻　　　Ｂ　鳩　　　Ｃ　蟻</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>ある人</t>
+          <t>Ａ　鳩　　　Ｂ　蟻　　　Ｃ　鳩</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>作者</t>
+          <t>Ａ　鳩　　　Ｂ　蟻　　　Ｃ　ある人</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
+          <t>Ａ　蟻　　　Ｂ　蟻　　　Ｃ　鳩</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
           <t>イ</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>直前が「鳩、こずゑよりこれを見て」なので、主語は&lt;b&gt;鳩&lt;/b&gt;。このあと「こずゑをちと食ひ切つて」と、鳩が蟻を助ける行動へと続きます。</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="n">
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Ａは「鳩、こずゑよりこれを見て」なので&lt;b&gt;鳩&lt;/b&gt;。Ｂは足にかみついた&lt;b&gt;蟻&lt;/b&gt;。Ｃ「悟りて」は、そのあと空へ逃げのびた&lt;b&gt;鳩&lt;/b&gt;です。</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2726,41 +2895,42 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>傍線部②「&lt;span class="kb"&gt;こずゑ&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部①「&lt;span class="kb"&gt;こずゑ&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>こずゑ</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>こづえ</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>こずへ</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>こずえ</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>エ</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>「&lt;b&gt;ゑ&lt;/b&gt;」は「&lt;b&gt;え&lt;/b&gt;」に直します（「ゐ」→「い」、「を」→「お」も同様）。現代仮名遣いでは「梢」は「&lt;b&gt;こずえ&lt;/b&gt;」と書くので、「こづえ」ではありません。</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="n">
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>「&lt;b&gt;ゑ&lt;/b&gt;」は「&lt;b&gt;え&lt;/b&gt;」に直します（「ゐ」→「い」、「を」→「お」も同様）。なお現代仮名遣いでは「梢」は「&lt;b&gt;こずえ&lt;/b&gt;」と書くので、「こづえ」ではありません。</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2787,41 +2957,46 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>傍線部③について、蟻が人の足にかみついたのはなぜか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr"/>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>自分の通り道をふさがれて、腹を立てたから。</t>
-        </is>
-      </c>
+          <t>傍線部②「&lt;span class="kb"&gt;ただ今の恩を送らん&lt;/span&gt;」とありますが、蟻はどうしようと思ったのですか。次の空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>たった今、&lt;span class="blank"&gt;　　&lt;/span&gt;に恩返しをしよう。</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>川に流された仕返しをしようと思ったから。</t>
+          <t>自分を捕らえずにいてくれた人</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>命を助けてくれた鳩の恩に報いようと思ったから。</t>
+          <t>自分を渚まで運んでくれた水</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>鳥もちのにおいが、気に入らなかったから。</t>
+          <t>自分を川から助けてくれた鳩</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
+          <t>木の枝を落としてくれた風</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
           <t>ウ</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>蟻の心内語「&lt;b&gt;ただ今の恩を送らん&lt;/b&gt;（＝たった今受けた恩を返そう）」が根拠。鳩が捕らえられそうになっているのを見て、助けようとしたのです。</t>
-        </is>
-      </c>
-      <c r="M24" s="4" t="n">
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>直前の場面で、蟻は&lt;b&gt;鳩&lt;/b&gt;が落とした枝に乗って助かっています。その鳩が捕らえられそうになったので、今度は自分が助けようとしたのです。</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2848,45 +3023,46 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>次は、この文章を読んだ生徒たちと先生の話し合いの一部である。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「この話の結びには、作者の考えが述べられていますね。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「はい。傍線部④に『人の恩を受けたらん者は、いかさまにもその報いをなすべきなり』とあります。」&lt;br&gt;&lt;span class="sp"&gt;Ｂさん&lt;/span&gt;「つまり、&lt;span class="blank"&gt;　　&lt;/span&gt;ということですね。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。物語の出来事から教訓を引き出す、という書き方になっています。」</t>
-        </is>
-      </c>
+          <t>次は、この文章を読んだあとの先生とＡさんの会話です。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
+          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「この話の結びには、作者の考えが述べられていますね。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「はい。『人の恩を受けたらん者は、いかさまにもその報いをなすべきなり』とあります。つまり&lt;span class="blank"&gt;　　&lt;/span&gt;ということですね。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。物語の出来事から教訓を引き出す、という書き方になっています。」</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
           <t>恩を受けた者は、どのような方法であってもその恩に報いるべきだ</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>恩を受けたら、必ずそれと同じだけの品物を返すべきだ</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>弱い者どうしは、助け合わなければ生きていくことができない</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>人に恩を売っておけば、いつか自分が得をすることがある</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>「&lt;b&gt;いかさまにも&lt;/b&gt;」＝どのようにしてでも。「同じだけの品物を返せ」とも、「恩を売れば得をする」とも述べていません。小さな蟻が、体は小さくとも自分にできるやり方で恩を返した点が要旨です。</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="n">
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>「&lt;b&gt;いかさまにも&lt;/b&gt;」＝どのようにしてでも。体の小さな蟻が、自分にできるやり方で恩を返した点が要旨です。</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2908,46 +3084,47 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>内容理解</t>
+          <t>主語・指示語</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>傍線部①「&lt;span class="kb"&gt;え申し候はじ&lt;/span&gt;」とあるが、篁が初めこのように言ったのはなぜか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部Ａ〜Ｃの主語の組み合わせとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>帝の命令に従うのが面倒で、断ろうとしたから。</t>
-        </is>
-      </c>
+      <c r="G26" s="4" t="inlineStr"/>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>札を書いた者をかばってやろうと思ったから。</t>
+          <t>Ａ　帝　　　Ｂ　帝　　　Ｃ　篁</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>文字が難しすぎて、本当に読むことができなかったから。</t>
+          <t>Ａ　帝　　　Ｂ　篁　　　Ｃ　帝</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>読めば帝を呪う内容になってしまい、自分に罪が及ぶことを恐れたから。</t>
+          <t>Ａ　篁　　　Ｂ　篁　　　Ｃ　帝</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
+          <t>Ａ　篁　　　Ｂ　帝　　　Ｃ　篁</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
           <t>エ</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>「読みは読み候ひなん（＝読むことは読めます）。&lt;b&gt;されど、恐れにて候へば&lt;/b&gt;」とあるので、読めないのではありません。内容が天皇を呪うものだと分かったので、口に出すことをはばかったのです。</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="n">
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Ａ「奏す」は&lt;b&gt;天皇に申し上げる&lt;/b&gt;という意味の言葉なので、主語は&lt;b&gt;篁&lt;/b&gt;。Ｂ「仰せらる」は&lt;b&gt;おっしゃる&lt;/b&gt;という尊敬語なので&lt;b&gt;帝&lt;/b&gt;。Ｃで「子」の字を読んだのは&lt;b&gt;篁&lt;/b&gt;です。&lt;b&gt;謙譲語（奏す）と尊敬語（仰せらる）の使い分け&lt;/b&gt;が手がかりになります。</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2969,46 +3146,47 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>内容理解</t>
+          <t>仮名遣い</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>傍線部②「&lt;span class="kb"&gt;おのれ放ちては、誰か書かん&lt;/span&gt;」とあるが、この言葉には帝のどのような気持ちが表れているか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部①「&lt;span class="kb"&gt;給ひて&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>この札を書いたのは篁に違いない、と疑う気持ち。</t>
-        </is>
-      </c>
+      <c r="G27" s="4" t="inlineStr"/>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>篁に、その札を書き直させようとする気持ち。</t>
+          <t>たまいて</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>誰にも読めないだろうと、あきらめる気持ち。</t>
+          <t>たもうて</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>篁の学識の広さを、心からほめたたえる気持ち。</t>
+          <t>たまえて</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
+          <t>たまひて</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>「誰か書かん」は&lt;b&gt;反語&lt;/b&gt;で「誰が書くだろうか、いや、おまえ以外にいない」の意。読めるということは書いた本人だろう、という疑いです。篁が「さればこそ（＝だからこそ）」と返しているのも手がかり。</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="n">
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>語頭以外の「ひ」は「い」に直します。「給ひて」→「&lt;b&gt;たまいて&lt;/b&gt;」。</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3030,46 +3208,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>仮名遣い</t>
+          <t>内容理解</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>傍線部③「&lt;span class="kb"&gt;給ひて&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>たまひて</t>
-        </is>
-      </c>
+          <t>傍線部②「&lt;span class="kb"&gt;おのれ放ちては、誰か書かん&lt;/span&gt;」とありますが、この言葉には帝のどのような気持ちが表れていますか。次の空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>この札を書いたのは、&lt;span class="blank"&gt;　　&lt;/span&gt;という気持ち。</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr"/>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>たまいて</t>
+          <t>誰にももう読めないだろう</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>たもうて</t>
+          <t>篁に違いない</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>たまえて</t>
+          <t>誰なのか早く探し出したい</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
+          <t>篁に書き直させたい</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
           <t>イ</t>
         </is>
       </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>語頭以外の「ひ」は「い」に直します。「給ひて」→「&lt;b&gt;たまいて&lt;/b&gt;」。</t>
-        </is>
-      </c>
-      <c r="M28" s="4" t="n">
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>「誰か書かん」は&lt;b&gt;反語&lt;/b&gt;で「誰が書くだろうか、いや、おまえ以外にいない」の意。読めるということは書いた本人だろう、という疑いです。篁が「さればこそ（＝だからこそ）」と返しているのも手がかり。</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3096,45 +3279,46 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>次は、この文章を読んだ生徒と先生の話し合いの一部である。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「傍線部④で帝が『ほほ笑ませ給ひて、事なくてやみにけり』となったのは、なぜでしょう。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「帝は篁を疑っていましたが、&lt;span class="blank"&gt;　　&lt;/span&gt;ので、機嫌を直したのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そうですね。題名の『広才』とは、学識が広いという意味です。この話は篁の才知をたたえた話なのですね。」</t>
-        </is>
-      </c>
+          <t>次は、この文章を読んだあとの先生とＡさんの会話です。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>篁が、帝をたたえるすぐれた歌をその場でよんでみせた</t>
+          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「最後に帝が『ほほ笑ませ給ひて、事なくてやみにけり』となったのは、なぜでしょう。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「帝は篁を疑っていましたが、篁が&lt;span class="blank"&gt;　　&lt;/span&gt;ので、感心して機嫌を直したのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。題名の『広才』とは、学識が広いという意味です。」</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>篁が、札を書いた犯人を突き止めて帝に報告した</t>
+          <t>札を書いたのは自分だと素直に認めて謝った</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>篁が「子」の字十二文字をみごとに読み解き、その学識の広さを示した</t>
+          <t>帝をたたえるすぐれた歌を、その場でよんでみせた</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>篁が、札を書いたのは自分であると素直に認めて謝った</t>
+          <t>「子」の字十二文字をみごとに読み解いてみせた</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
+          <t>札を書いた犯人を突き止めて帝に報告した</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
           <t>ウ</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>帝が出した「子子子子子子子子子子子子」という難題を、篁は「&lt;b&gt;ねこの子のこねこ、ししの子のこじし&lt;/b&gt;」と読み解きました。その才知に感心したので、疑いはうやむやになって終わったのです。</t>
         </is>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3156,46 +3340,47 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>内容理解</t>
+          <t>主語・指示語</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>傍線部①「&lt;span class="kb"&gt;初心の人、二つの矢を持つことなかれ&lt;/span&gt;」とあるが、師がこのように言うのはなぜか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部Ａ〜Ｃの主語の組み合わせとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>二本目をあてにして、一本目を射る心がいいかげんになるから。</t>
-        </is>
-      </c>
+      <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>二本の矢を同時に射るのは、たいへん危険だから。</t>
+          <t>Ａ　弓を習う人　　　Ｂ　師　　　Ｃ　師</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>初心者のうちは、矢を無駄に使ってはいけないから。</t>
+          <t>Ａ　弓を習う人　　　Ｂ　弓を習う人　　　Ｃ　師</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>二本持つと手が重くなり、的をねらいにくくなるから。</t>
+          <t>Ａ　師　　　Ｂ　師　　　Ｃ　弓を習う人</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
+          <t>Ａ　弓を習う人　　　Ｂ　師　　　Ｃ　弓を習う人</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>すぐあとに理由が示されています。「&lt;b&gt;後の矢を頼みて、初めの矢に等閑の心あり&lt;/b&gt;」＝あとの矢をあてにして、初めの矢をいいかげんに扱う心が生じる。</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="n">
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>Ａ「的に向かふ」のは&lt;b&gt;弓を習う人&lt;/b&gt;。Ｂはその直前に「師の言はく」とあるので&lt;b&gt;師&lt;/b&gt;。Ｃは「師これを知る」と書かれているとおり&lt;b&gt;師&lt;/b&gt;です。</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3222,41 +3407,42 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>傍線部②「&lt;span class="kb"&gt;言はく&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部①「&lt;span class="kb"&gt;言はく&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>いあく</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>いはく</t>
         </is>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>いわく</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>ゆわく</t>
         </is>
       </c>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>ウ</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>語頭以外の「は」は「わ」に直します。「言はく」→「&lt;b&gt;いわく&lt;/b&gt;」。「〜の言はく」は「〜が言うことには」という決まった言い方です。</t>
         </is>
       </c>
-      <c r="M31" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3278,46 +3464,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>主語・語意</t>
+          <t>内容理解</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>傍線部③「&lt;span class="kb"&gt;懈怠の心、みづから知らずといへども、師これを知る&lt;/span&gt;」の意味として最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>なまけ心は、師から教えられて初めて生まれるものである。</t>
-        </is>
-      </c>
+          <t>傍線部②「&lt;span class="kb"&gt;後の矢を頼みて、初めの矢に等閑の心あり&lt;/span&gt;」とありますが、どういうことですか。次の空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>二本目があると思うと、&lt;span class="blank"&gt;　　&lt;/span&gt;ということ。</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr"/>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>なまけ心は、自分では気づかないけれども、師は見抜いている。</t>
+          <t>師の前で緊張してしまう</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>なまけ心は、自分だけが知っていて、師にはわからない。</t>
+          <t>一本目をいいかげんに射てしまう</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>なまけ心は、自分にも師にも、決して知られることはない。</t>
+          <t>二本目もねらいが定まらなくなる</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
+          <t>矢が重くなって的をねらいにくくなる</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
           <t>イ</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>「みづから」＝自分で。「〜といへども」＝〜けれども（逆接）。&lt;b&gt;本人は無自覚でも、師には見えている&lt;/b&gt;という対比を読み取ります。</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="n">
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>「頼みて」＝あてにして、「等閑の心」＝いいかげんな気持ち（いずれも注）。&lt;b&gt;後の矢をあてにすると、一本目がおろそかになる&lt;/b&gt;という意味です。</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3344,45 +3535,46 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>次は、この文章を読んだ生徒たちと先生の話し合いの一部である。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「後半で作者は、話をどのように広げていますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「弓の稽古の話から、仏道を学ぶ人の話へと広げています。」&lt;br&gt;&lt;span class="sp"&gt;Ｂさん&lt;/span&gt;「そして傍線部④で、『ただ今の一念において、直ちにすること』の難しさを述べています。つまり作者が言いたいのは、&lt;span class="blank"&gt;　　&lt;/span&gt;ということですね。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そうですね。『この戒め、万事にわたるべし』という一文が、そのつなぎ目になっています。」</t>
-        </is>
-      </c>
+          <t>次は、この文章を読んだあとの先生とＡさんの会話です。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr">
         <is>
+          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「後半で作者は、弓の話をどのように広げていますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「仏道を学ぶ人の話に広げ、『ただ今の一念において、直ちにすること』の難しさを述べています。つまり作者は&lt;span class="blank"&gt;　　&lt;/span&gt;と言いたいのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。『この戒め、万事にわたるべし』という一文が、そのつなぎ目になっています。」</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
           <t>弓の稽古は、仏道の修行よりもはるかに難しいものである</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>師の教えといっても、必ずしも正しいとは限らない</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>朝と夕方とでは、人の心は大きく変わってしまうものだ</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>何事も、次の機会をあてにせず、今この一瞬に実行することが大切だ</t>
         </is>
       </c>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>エ</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>「二本目の矢をあてにする」＝「明日をあてにする」という同じ構造でとらえます。&lt;b&gt;今この一瞬に、すぐ実行せよ&lt;/b&gt;というのが、弓の話から導かれた作者の主張です。</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="n">
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>「二本目の矢をあてにする」と「明日をあてにする」は同じ構造です。&lt;b&gt;今この一瞬に、すぐ実行せよ&lt;/b&gt;というのが、弓の話から導かれた作者の主張です。</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3404,46 +3596,47 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>内容理解</t>
+          <t>主語・指示語</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>傍線部①「&lt;span class="kb"&gt;無言の行に、もの言ふべきか&lt;/span&gt;」とあるが、第二の僧がこう言ったのはどのような気持ちからか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部Ａ〜Ｃが指し示すものの組み合わせとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>自分もそろそろ話をしてみたいという気持ち。</t>
-        </is>
-      </c>
+      <c r="G34" s="4" t="inlineStr"/>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>下座の僧が行の約束を破ったことを、非難する気持ち。</t>
+          <t>Ａ　灯明が消えたこと　　　Ｂ　下座の僧と第二の僧　　　Ｃ　下座の僧</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>暗いままでは危ないと、仲間の身を心配する気持ち。</t>
+          <t>Ａ　下座の僧がものを言ったこと　　　Ｂ　下座の僧と第二の僧　　　Ｃ　上座の僧</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>自分も早く火をつけてほしいと、願う気持ち。</t>
+          <t>Ａ　灯明が消えたこと　　　Ｂ　第二の僧と第三の僧　　　Ｃ　第三の僧</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
+          <t>Ａ　下座の僧がものを言ったこと　　　Ｂ　第二の僧と第三の僧　　　Ｃ　上座の僧</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
           <t>イ</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>「&lt;b&gt;にがにがしげにとがめけり&lt;/b&gt;」＝不愉快そうに非難した、が根拠。「べきか」は反語で「言ってよいものか、いや、よくない」の意です。</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="n">
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>Ａ「これ」は、第二の僧が聞きとがめた内容なので、&lt;b&gt;下座の僧が口をきいたこと&lt;/b&gt;。Ｂ「二人」は、第三の僧から見てすでに口をきいてしまった&lt;b&gt;下座の僧と第二の僧&lt;/b&gt;。Ｃ「われ」は、その言葉を発した&lt;b&gt;上座の僧&lt;/b&gt;自身です。</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3470,41 +3663,42 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>傍線部②「&lt;span class="kb"&gt;言ふべきか&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部①「&lt;span class="kb"&gt;言ふべきか&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>いふべきか</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>ゆうべきか</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>いうべきか</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>いをべきか</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>ウ</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>語頭以外の「ふ」は「う」に直すので、「言ふ」→「&lt;b&gt;いう&lt;/b&gt;」。読み方が「ゆう」であっても、&lt;b&gt;書き表すときは「いう」&lt;/b&gt;となる点に注意しましょう。</t>
         </is>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="N35" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3531,41 +3725,46 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>傍線部③「&lt;span class="kb"&gt;われ一人こそもの言はね&lt;/span&gt;」とあるが、この言葉のおかしさはどこにあるか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>自分だけ行を続けようとして、仲間の僧たちを見捨てている点。</t>
-        </is>
-      </c>
+          <t>傍線部②を含む「&lt;span class="kb"&gt;われ一人こそもの言はね&lt;/span&gt;」という上座の僧の言葉には、おかしさがあります。それはどのような点ですか。次の空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>自分だけは口をきいていないと言いながら、&lt;span class="blank"&gt;　　&lt;/span&gt;という点。</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>あかりを消したのが自分であることを、最後まで隠している点。</t>
+          <t>仲間の僧たちを見捨てている</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>ほかの三人の僧の言葉を、まったく聞いていなかった点。</t>
+          <t>ほかの僧の言葉をまったく聞いていない</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>自分だけは口をきいていないと言いながら、そう言うこと自体が口をきいていることになる点。</t>
+          <t>実は自分が最初に口をきいていた</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
+          <t>そう言うこと自体が、口をきいたことになる</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
           <t>エ</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr">
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>「こそ〜ね」は&lt;b&gt;係り結び&lt;/b&gt;で、「〜だけは…ない」と強調する言い方。「自分だけは言っていない」と&lt;b&gt;口に出した瞬間に&lt;/b&gt;、その主張が成り立たなくなるところがおかしみです。</t>
         </is>
       </c>
-      <c r="M36" s="4" t="n">
+      <c r="N36" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3592,45 +3791,46 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>次は、この文章を読んだ生徒と先生の話し合いの一部である。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「四人の僧が、次々に口をきいてしまいますね。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「はい。しかも、あとの僧ほど&lt;span class="blank"&gt;　　&lt;/span&gt;という形になっています。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのくり返しが、この話のおもしろさを生んでいるのですね。」</t>
-        </is>
-      </c>
+          <t>次は、この文章を読んだあとの先生とＡさんの会話です。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
+          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「四人の僧が、次々に口をきいてしまいますね。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「はい。しかも、あとの僧ほど&lt;span class="blank"&gt;　　&lt;/span&gt;という形になっていて、そのくり返しがこの話のおもしろさを生んでいると思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。」</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
           <t>人を責めることに気を取られ、自分も同じ過ちを犯していることに気づいていない</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>位が低くなっていき、発言の重みが失われていく</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>修行の厳しさに耐えかねて、寺を出ていこうとしている</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>声がしだいに小さくなり、少しずつ無言の行に戻っている</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>位が低くなっていき、発言の重みが失われていく</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>下座→第二→第三→上座と、&lt;b&gt;人を非難するその言葉じたいが行を破っている&lt;/b&gt;という同じ失敗をくり返します。最後の上座の僧がその極みで、他人には厳しく自分には気づかない人間の姿を笑った話です。</t>
         </is>
       </c>
-      <c r="M37" s="4" t="n">
+      <c r="N37" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3652,46 +3852,47 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>内容理解</t>
+          <t>主語・指示語</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>傍線部①「&lt;span class="kb"&gt;思し出づる所ありて、案内せさせて入り給ひぬ&lt;/span&gt;」とあるが、「ある人」がこのようにしたのはなぜか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部Ａ〜Ｃの主語の組み合わせとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>その家のようすを、作者に見せたいと思ったから。</t>
-        </is>
-      </c>
+      <c r="G38" s="4" t="inlineStr"/>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>夜が更けてきたので、休む場所を探していたから。</t>
+          <t>Ａ　作者　　　Ｂ　作者　　　Ｃ　その家の女主人</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>月を見て歩くうちに、ふと思い出した家があったから。</t>
+          <t>Ａ　作者　　　Ｂ　ある人　　　Ｃ　その家の女主人</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>道に迷ってしまい、人にたずねようとしたから。</t>
+          <t>Ａ　ある人　　　Ｂ　ある人　　　Ｃ　その家の女主人</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
+          <t>Ａ　ある人　　　Ｂ　作者　　　Ｃ　作者</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
           <t>ウ</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>「思し出づる所ありて」＝&lt;b&gt;思い出しなさる家があって&lt;/b&gt;。「思し出づ」は「思ひ出づ」の尊敬語で、主語は「ある人」です。</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="n">
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>Ａ・Ｂの「&lt;b&gt;給ふ&lt;/b&gt;」は尊敬語で、作者が敬っている&lt;b&gt;ある人&lt;/b&gt;の動作。Ｃは、その人が帰ったあとに戸を押し開けて月を見ていた&lt;b&gt;その家の女主人&lt;/b&gt;です。作者自身の動作には敬語が付かない点に注意しましょう。</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3718,41 +3919,42 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>傍線部②「&lt;span class="kb"&gt;見ゐたる&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
+          <t>傍線部①「&lt;span class="kb"&gt;見ゐたる&lt;/span&gt;」を現代仮名遣いに直したものとして正しいものを、次のア〜エの中から一つ選びなさい。</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>みゐたる</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>みいたる</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>みひたる</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>みうたる</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>イ</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>「&lt;b&gt;ゐ&lt;/b&gt;」は「&lt;b&gt;い&lt;/b&gt;」に直します。「見ゐたる」→「&lt;b&gt;みいたる&lt;/b&gt;」。「ゐ→い」「ゑ→え」「を→お」はセットで覚えましょう。</t>
         </is>
       </c>
-      <c r="M39" s="4" t="n">
+      <c r="N39" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3779,41 +3981,46 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>傍線部③のとき、この家の女主人はどうしていたか。最も適切なものを、次のア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr"/>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>妻戸をもう少し押し開けて、月を眺めていた。</t>
-        </is>
-      </c>
+          <t>傍線部②「&lt;span class="kb"&gt;妻戸をいま少し押し開けて&lt;/span&gt;」とありますが、この家の女主人はどうしていたのですか。次の空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>客を送り出したあとも、&lt;span class="blank"&gt;　　&lt;/span&gt;。</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>帰る客を追いかけて、外へ出てきた。</t>
+          <t>戸をもう少し開けて、月を眺めていた</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>あかりをともして、書物を読み始めた。</t>
+          <t>あかりをともして、書物を読んでいた</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>すぐに戸を閉めて、奥へ引きこもってしまった。</t>
+          <t>すぐに戸を閉めて、奥へ引きこもっていた</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
+          <t>帰る客を追いかけて、外へ出てきていた</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
           <t>ア</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>本文そのままに「妻戸を&lt;b&gt;いま少し押し開けて&lt;/b&gt;、月見るけしきなり」とあります。「すぐに戸を閉めて奥へ引きこもった」というのは、そのあとの「やがてかけこもら&lt;b&gt;ましかば&lt;/b&gt;、口惜しから&lt;b&gt;まし&lt;/b&gt;（＝もし〜だったら残念だっただろう）」という&lt;b&gt;反実仮想&lt;/b&gt;の内容で、実際には起きていません。</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="n">
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>本文そのままに「妻戸を&lt;b&gt;いま少し押し開けて&lt;/b&gt;、月見るけしきなり」とあります。「すぐに戸を閉めて引きこもった」というのは、そのあとの「やがてかけこもら&lt;b&gt;ましかば&lt;/b&gt;、口惜しから&lt;b&gt;まし&lt;/b&gt;（＝もし〜だったら残念だっただろう）」という&lt;b&gt;反実仮想&lt;/b&gt;の内容で、実際には起きていません。</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3840,45 +4047,46 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>次は、この文章を読んだ生徒たちと先生の話し合いの一部である。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「作者は、この女性のふるまいをどのように評価していますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「傍線部④に『あとまで見る人ありとは、いかでか知らん』とあります。見られているとは思っていなかったのですね。」&lt;br&gt;&lt;span class="sp"&gt;Ｂさん&lt;/span&gt;「それでも月を眺め続けていたのですから、作者は&lt;span class="blank"&gt;　　&lt;/span&gt;と考えているのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そうですね。『ただ朝夕の心づかひによるべし』という一文が、その考えを表しています。」</t>
-        </is>
-      </c>
+          <t>次は、この文章を読んだあとの先生とＡさんの会話です。空欄にあてはまる内容として最も適切なものを、あとのア〜エの中から一つ選びなさい。</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>夜遅くまで起きて月を見るのは、感心できないことである</t>
+          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「作者は、この家の女主人のふるまいをどのように評価していますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「『あとまで見る人ありとは、いかでか知らん』『ただ朝夕の心づかひによるべし』とあるので、作者は&lt;span class="blank"&gt;　　&lt;/span&gt;と考えているのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。」</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
+          <t>客が帰ったあとは誰も見ていないのだから、気を抜いてもかまわない</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>夜遅くまで起きて月を眺めるのは、感心できないことである</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
           <t>月見をするなら、一人よりも大勢で楽しむほうがよい</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>客が帰ったあとは誰も見ていないのだから、気を抜いてもかまわない</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>人が見ていないときのふるまいこそが、その人のふだんの心づかいを表す</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>エ</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>「&lt;b&gt;朝夕の心づかひ&lt;/b&gt;」＝ふだんからの心がけ。誰も見ていないと思われる場面でなお美しくふるまえるのは、日ごろの心がけによるものだ、というのが作者の考えです。</t>
         </is>
       </c>
-      <c r="M41" s="4" t="n">
+      <c r="N41" s="4" t="n">
         <v>3</v>
       </c>
     </row>

--- a/saitama-kobun4/gas/古典クエスト_問題マスター.xlsx
+++ b/saitama-kobun4/gas/古典クエスト_問題マスター.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A60"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -847,6 +847,58 @@
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>表記を一部改めています。設問・解説はオリジナルです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>【ふりがな】</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>常用漢字外の字や、読みにくい固有名詞・熟字訓には、次のように読みを付けます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &lt;ruby class="rd"&gt;梢&lt;rt&gt;こずゑ&lt;/rt&gt;&lt;/ruby&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  縦書きなら字の右、横書きなら上に出ます（ふつうのふりがなの位置）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  古文なので、読みは本文と同じ歴史的仮名遣いで示します（実際の入試もこの方式）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  「口語訳あり／なし」ボタンでは消えません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ※ 口語訳のルビ（class="gl"）と入れ子にはできません。どちらか一方にしてください。</t>
         </is>
       </c>
     </row>
@@ -956,7 +1008,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;これも今は昔、絵仏師良秀といふありけり。家の隣より火出で来て、風おしおほひてせめければ、逃げ出でて大路へ出でにけり。人の書かする仏もおはしけり。また、衣着ぬ妻子なども、&lt;ruby class="gl"&gt;さながら&lt;rt&gt;そのまま&lt;/rt&gt;&lt;/ruby&gt;内にありけり。それも知らず、ただ逃げ出でたるをことにして、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;向かひ&lt;/span&gt;のつらに立てり。&lt;/p&gt;&lt;p&gt;見れば、すでにわが家に移りて、煙・炎くゆりけるまで、&lt;ruby class="gl"&gt;おほかた&lt;rt&gt;ずっと&lt;/rt&gt;&lt;/ruby&gt;、向かひのつらに立ちて眺めければ、「あさましきこと」とて、人ども来とぶらひけれど、&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;騒がず&lt;/span&gt;。「いかに」と人言ひければ、向かひに立ちて、家の焼くるを見て、うちうなづきて、時々笑ひけり。「あはれ、しつるせうとくかな。&lt;ruby class="gl"&gt;年ごろはわろく&lt;rt&gt;長年へたに&lt;/rt&gt;&lt;/ruby&gt;書きけるものかな」と言ふ時に、とぶらひに来たる者ども、「こはいかに、かくては立ち給へるぞ。もののつき給へるか」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;言ひければ&lt;/span&gt;、「なんでふ物のつくべきぞ。年ごろ不動尊の火焰をあしく書きけるなり。今見れば、かうこそ燃えけれと、心得つるなり。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;これこそせうとくよ&lt;/span&gt;」と言ひて、&lt;ruby class="gl"&gt;あざ笑ひて&lt;rt&gt;あざけり笑って&lt;/rt&gt;&lt;/ruby&gt;&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;立てりけれ&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;その後にや、良秀がよぢり不動とて、今に人々めで合へり。&lt;/p&gt;</t>
+          <t>&lt;p&gt;これも今は昔、絵仏師良秀といふありけり。家の隣より火出で来て、風おしおほひてせめければ、逃げ出でて大路へ出でにけり。人の書かする仏もおはしけり。また、衣着ぬ妻子なども、&lt;ruby class="gl"&gt;さながら&lt;rt&gt;そのまま&lt;/rt&gt;&lt;/ruby&gt;内にありけり。それも知らず、ただ逃げ出でたるをことにして、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;向かひ&lt;/span&gt;のつらに立てり。&lt;/p&gt;&lt;p&gt;見れば、すでにわが家に移りて、煙・炎くゆりけるまで、&lt;ruby class="gl"&gt;おほかた&lt;rt&gt;ずっと&lt;/rt&gt;&lt;/ruby&gt;、向かひのつらに立ちて眺めければ、「あさましきこと」とて、人ども来とぶらひけれど、&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;騒がず&lt;/span&gt;。「いかに」と人言ひければ、向かひに立ちて、家の焼くるを見て、うちうなづきて、時々笑ひけり。「あはれ、しつるせうとくかな。&lt;ruby class="gl"&gt;年ごろはわろく&lt;rt&gt;長年へたに&lt;/rt&gt;&lt;/ruby&gt;書きけるものかな」と言ふ時に、とぶらひに来たる者ども、「こはいかに、かくては立ち給へるぞ。もののつき給へるか」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;言ひければ&lt;/span&gt;、「なんでふ物のつくべきぞ。年ごろ不動尊の火&lt;ruby class="rd"&gt;焰&lt;rt&gt;えん&lt;/rt&gt;&lt;/ruby&gt;をあしく書きけるなり。今見れば、かうこそ燃えけれと、心得つるなり。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;これこそせうとくよ&lt;/span&gt;」と言ひて、&lt;ruby class="gl"&gt;あざ笑ひて&lt;rt&gt;あざけり笑って&lt;/rt&gt;&lt;/ruby&gt;&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;立てりけれ&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;その後にや、良秀がよぢり不動とて、今に人々めで合へり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -1006,7 +1058,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;和泉式部、保昌が妻にて丹後に&lt;ruby class="gl"&gt;下りけるほどに&lt;rt&gt;下っていたころ&lt;/rt&gt;&lt;/ruby&gt;、京に歌合ありけるに、小式部内侍、歌よみにとられてよみけるを、定頼中納言たはぶれて、小式部内侍ありけるに、「丹後へつかはしける人は参りたりや。いかに心もとなくおぼすらむ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;言ひて&lt;/span&gt;、局の前を過ぎられけるを、御簾よりなから出でて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;わづかに&lt;/span&gt;直衣の袖をひかへて、&lt;/p&gt;&lt;p&gt;　大江山いくのの道の遠ければまだふみもみず天の橋立&lt;/p&gt;&lt;p&gt;と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;よみかけけり&lt;/span&gt;。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;思はずにあさましくて&lt;/span&gt;、「こはいかに、&lt;ruby class="gl"&gt;かかるやうやはある&lt;rt&gt;こんなことがあるものか&lt;/rt&gt;&lt;/ruby&gt;」とばかり言ひて、返しにも及ばず、袖を引き放ちて&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;逃げられけり&lt;/span&gt;。小式部、&lt;ruby class="gl"&gt;これより&lt;rt&gt;これ以降&lt;/rt&gt;&lt;/ruby&gt;歌よみの世&lt;ruby class="gl"&gt;おぼえ&lt;rt&gt;評判&lt;/rt&gt;&lt;/ruby&gt;出で来にけり。&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;ruby class="rd"&gt;和泉式部&lt;rt&gt;いづみしきぶ&lt;/rt&gt;&lt;/ruby&gt;、&lt;ruby class="rd"&gt;保昌&lt;rt&gt;やすまさ&lt;/rt&gt;&lt;/ruby&gt;が妻にて&lt;ruby class="rd"&gt;丹後&lt;rt&gt;たんご&lt;/rt&gt;&lt;/ruby&gt;に&lt;ruby class="gl"&gt;下りけるほどに&lt;rt&gt;下っていたころ&lt;/rt&gt;&lt;/ruby&gt;、京に歌合ありけるに、&lt;ruby class="rd"&gt;小式部内侍&lt;rt&gt;こしきぶのないし&lt;/rt&gt;&lt;/ruby&gt;、歌よみにとられてよみけるを、&lt;ruby class="rd"&gt;定頼&lt;rt&gt;さだより&lt;/rt&gt;&lt;/ruby&gt;中納言たはぶれて、小式部内侍ありけるに、「丹後へつかはしける人は参りたりや。いかに心もとなくおぼすらむ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;言ひて&lt;/span&gt;、局の前を過ぎられけるを、&lt;ruby class="rd"&gt;御簾&lt;rt&gt;みす&lt;/rt&gt;&lt;/ruby&gt;よりなから出でて、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;わづかに&lt;/span&gt;&lt;ruby class="rd"&gt;直衣&lt;rt&gt;なほし&lt;/rt&gt;&lt;/ruby&gt;の袖をひかへて、&lt;/p&gt;&lt;p&gt;　&lt;ruby class="rd"&gt;大江山&lt;rt&gt;おほえやま&lt;/rt&gt;&lt;/ruby&gt;いくのの道の遠ければまだふみもみず天の橋立&lt;/p&gt;&lt;p&gt;と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;よみかけけり&lt;/span&gt;。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;思はずにあさましくて&lt;/span&gt;、「こはいかに、&lt;ruby class="gl"&gt;かかるやうやはある&lt;rt&gt;こんなことがあるものか&lt;/rt&gt;&lt;/ruby&gt;」とばかり言ひて、返しにも及ばず、袖を引き放ちて&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;逃げられけり&lt;/span&gt;。小式部、&lt;ruby class="gl"&gt;これより&lt;rt&gt;これ以降&lt;/rt&gt;&lt;/ruby&gt;歌よみの世&lt;ruby class="gl"&gt;おぼえ&lt;rt&gt;評判&lt;/rt&gt;&lt;/ruby&gt;出で来にけり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1056,12 +1108,12 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;高名の木登りといひしをのこ、人を掟てて、高き木に&lt;ruby class="gl"&gt;登せて&lt;rt&gt;登らせて&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby class="gl"&gt;梢&lt;rt&gt;枝の先&lt;/rt&gt;&lt;/ruby&gt;を切らせしに、いと&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;危ふく&lt;/span&gt;見えしほどは言ふこともなくて、下るるときに、軒たけばかりになりて、「あやまちすな。心して降りよ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;言葉をかけ侍りし&lt;/span&gt;を、「かばかりになりては、飛び降るとも&lt;ruby class="gl"&gt;降りなん&lt;rt&gt;降りられるだろう&lt;/rt&gt;&lt;/ruby&gt;。いかにかく言ふぞ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;申し侍りしかば&lt;/span&gt;、「その事に候ふ。目くるめき、枝危ふきほどは、おのれが恐れ侍れば申さず。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;あやまちは、安き所になりて、必ず仕る事に候ふ&lt;/span&gt;」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;言ふ&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;あやしき下臈なれども、聖人の戒めにかなへり。鞠も、難き所を蹴出して後、&lt;ruby class="gl"&gt;安く思へば&lt;rt&gt;簡単だと思うと&lt;/rt&gt;&lt;/ruby&gt;、必ず落つと侍るやらん。&lt;/p&gt;</t>
+          <t>&lt;p&gt;高名の木登りといひしをのこ、人を&lt;ruby class="rd"&gt;掟&lt;rt&gt;おき&lt;/rt&gt;&lt;/ruby&gt;てて、高き木に&lt;ruby class="gl"&gt;登せて&lt;rt&gt;登らせて&lt;/rt&gt;&lt;/ruby&gt;&lt;ruby class="rd"&gt;梢&lt;rt&gt;こずゑ&lt;/rt&gt;&lt;/ruby&gt;を切らせしに、いと&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;危ふく&lt;/span&gt;見えしほどは言ふこともなくて、下るるときに、軒たけばかりになりて、「あやまちすな。心して降りよ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;言葉をかけ侍りし&lt;/span&gt;を、「かばかりになりては、飛び降るとも&lt;ruby class="gl"&gt;降りなん&lt;rt&gt;降りられるだろう&lt;/rt&gt;&lt;/ruby&gt;。いかにかく言ふぞ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;申し侍りしかば&lt;/span&gt;、「その事に候ふ。目くるめき、枝危ふきほどは、おのれが恐れ侍れば申さず。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;あやまちは、安き所になりて、必ず仕る事に候ふ&lt;/span&gt;」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;言ふ&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;あやしき&lt;ruby class="rd"&gt;下臈&lt;rt&gt;げらふ&lt;/rt&gt;&lt;/ruby&gt;なれども、聖人の戒めにかなへり。&lt;ruby class="rd"&gt;鞠&lt;rt&gt;まり&lt;/rt&gt;&lt;/ruby&gt;も、難き所を蹴出して後、&lt;ruby class="gl"&gt;安く思へば&lt;rt&gt;簡単だと思うと&lt;/rt&gt;&lt;/ruby&gt;、必ず落つと侍るやらん。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;高名の&lt;/b&gt;＝有名な。　&lt;b&gt;をのこ&lt;/b&gt;＝男。　&lt;b&gt;掟てて&lt;/b&gt;＝指図して。　&lt;b&gt;軒たけ&lt;/b&gt;＝家の軒の高さ。　&lt;b&gt;あやまち&lt;/b&gt;＝失敗。けが。　&lt;b&gt;候ふ&lt;/b&gt;＝ございます。　&lt;b&gt;目くるめき&lt;/b&gt;＝目がくらみ。　&lt;b&gt;仕る&lt;/b&gt;＝いたす。　&lt;b&gt;あやしき下臈&lt;/b&gt;＝身分の低い者。　&lt;b&gt;聖人の戒め&lt;/b&gt;＝すぐれた人の教え。　&lt;b&gt;鞠&lt;/b&gt;＝蹴鞠。</t>
+          <t>&lt;b&gt;高名の&lt;/b&gt;＝有名な。　&lt;b&gt;をのこ&lt;/b&gt;＝男。　&lt;b&gt;掟てて&lt;/b&gt;＝指図して。　&lt;b&gt;梢&lt;/b&gt;＝枝の先。　&lt;b&gt;軒たけ&lt;/b&gt;＝家の軒の高さ。　&lt;b&gt;あやまち&lt;/b&gt;＝失敗。けが。　&lt;b&gt;候ふ&lt;/b&gt;＝ございます。　&lt;b&gt;目くるめき&lt;/b&gt;＝目がくらみ。　&lt;b&gt;仕る&lt;/b&gt;＝いたす。　&lt;b&gt;あやしき下臈&lt;/b&gt;＝身分の低い者。　&lt;b&gt;聖人の戒め&lt;/b&gt;＝すぐれた人の教え。　&lt;b&gt;鞠&lt;/b&gt;＝蹴鞠。</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1106,7 +1158,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;仁和寺にある法師、年寄るまで石清水を&lt;ruby class="gl"&gt;拝まざりければ&lt;rt&gt;参拝しなかったので&lt;/rt&gt;&lt;/ruby&gt;、心うく覚えて、あるとき思ひ立ちて、ただひとり、徒歩より&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;まうでけり&lt;/span&gt;。極楽寺・高良などを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;拝みて&lt;/span&gt;、かばかりと心得て帰りにけり。&lt;/p&gt;&lt;p&gt;さて、かたへの人にあひて、「年ごろ思ひつること、&lt;ruby class="gl"&gt;果たし侍りぬ&lt;rt&gt;果たしました&lt;/rt&gt;&lt;/ruby&gt;。&lt;ruby class="gl"&gt;聞きしにも過ぎて&lt;rt&gt;聞いていた以上に&lt;/rt&gt;&lt;/ruby&gt;尊くこそ&lt;ruby class="gl"&gt;おはしけれ&lt;rt&gt;いらっしゃった&lt;/rt&gt;&lt;/ruby&gt;。そも、参りたる人ごとに山へ&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;登りし&lt;/span&gt;は、何事かありけん、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;ゆかしかりしかど&lt;/span&gt;、神へ参るこそ本意なれと思ひて、山までは見ず」とぞ&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;言ひける&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;少しのことにも、先達は&lt;ruby class="gl"&gt;あらまほしき&lt;rt&gt;あってほしい&lt;/rt&gt;&lt;/ruby&gt;ことなり。&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;ruby class="rd"&gt;仁和寺&lt;rt&gt;にんなじ&lt;/rt&gt;&lt;/ruby&gt;にある法師、年寄るまで&lt;ruby class="rd"&gt;石清水&lt;rt&gt;いはしみづ&lt;/rt&gt;&lt;/ruby&gt;を&lt;ruby class="gl"&gt;拝まざりければ&lt;rt&gt;参拝しなかったので&lt;/rt&gt;&lt;/ruby&gt;、心うく覚えて、あるとき思ひ立ちて、ただひとり、&lt;ruby class="rd"&gt;徒歩&lt;rt&gt;かち&lt;/rt&gt;&lt;/ruby&gt;より&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;まうでけり&lt;/span&gt;。&lt;ruby class="rd"&gt;極楽寺&lt;rt&gt;ごくらくじ&lt;/rt&gt;&lt;/ruby&gt;・&lt;ruby class="rd"&gt;高良&lt;rt&gt;かうら&lt;/rt&gt;&lt;/ruby&gt;などを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;拝みて&lt;/span&gt;、かばかりと心得て帰りにけり。&lt;/p&gt;&lt;p&gt;さて、かたへの人にあひて、「年ごろ思ひつること、&lt;ruby class="gl"&gt;果たし侍りぬ&lt;rt&gt;果たしました&lt;/rt&gt;&lt;/ruby&gt;。&lt;ruby class="gl"&gt;聞きしにも過ぎて&lt;rt&gt;聞いていた以上に&lt;/rt&gt;&lt;/ruby&gt;尊くこそ&lt;ruby class="gl"&gt;おはしけれ&lt;rt&gt;いらっしゃった&lt;/rt&gt;&lt;/ruby&gt;。そも、参りたる人ごとに山へ&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;登りし&lt;/span&gt;は、何事かありけん、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;ゆかしかりしかど&lt;/span&gt;、神へ参るこそ本意なれと思ひて、山までは見ず」とぞ&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;言ひける&lt;/span&gt;。&lt;/p&gt;&lt;p&gt;少しのことにも、&lt;ruby class="rd"&gt;先達&lt;rt&gt;せんだち&lt;/rt&gt;&lt;/ruby&gt;は&lt;ruby class="gl"&gt;あらまほしき&lt;rt&gt;あってほしい&lt;/rt&gt;&lt;/ruby&gt;ことなり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1156,7 +1208,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;これも今は昔、比叡の山に児ありけり。僧たち、宵のつれづれに、「いざ、かいもちひせむ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;言ひける&lt;/span&gt;を、この児、心寄せに聞きけり。&lt;ruby class="gl"&gt;さりとて&lt;rt&gt;とはいっても&lt;/rt&gt;&lt;/ruby&gt;、し出ださむを待ちて寝ざらむも、わろかりなむと思ひて、片方に寄りて、寝たるよしにて、出で来るを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;待ちける&lt;/span&gt;に、すでにし出だしたるさまにて、ひしめき合ひたり。&lt;/p&gt;&lt;p&gt;この児、&lt;ruby class="gl"&gt;さだめて&lt;rt&gt;きっと&lt;/rt&gt;&lt;/ruby&gt;驚かさむずらむと待ちゐたるに、僧の、「もの申しさぶらはむ。驚かせたまへ」と言ふを、うれしとは思へども、ただ一度に&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;いらへむ&lt;/span&gt;も、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;待ちけるかともぞ思ふ&lt;/span&gt;とて、&lt;ruby class="gl"&gt;今一声&lt;rt&gt;もう一声&lt;/rt&gt;&lt;/ruby&gt;呼ばれていらへむと、念じて寝たるほどに、「や、な起こしたてまつりそ。幼き人は寝入りたまひにけり」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;言ふ声&lt;/span&gt;のしければ、あな、わびしと思ひて、いま一度&lt;ruby class="gl"&gt;起こせかし&lt;rt&gt;起こしてほしい&lt;/rt&gt;&lt;/ruby&gt;と、思ひ寝に聞けば、ひしひしと、ただ食ひに食ふ音のしければ、ずちなくて、無期ののちに、「えい」といらへたりければ、僧たち笑ふこと限りなし。&lt;/p&gt;</t>
+          <t>&lt;p&gt;これも今は昔、&lt;ruby class="rd"&gt;比叡&lt;rt&gt;ひえい&lt;/rt&gt;&lt;/ruby&gt;の山に&lt;ruby class="rd"&gt;児&lt;rt&gt;ちご&lt;/rt&gt;&lt;/ruby&gt;ありけり。僧たち、宵のつれづれに、「いざ、かいもちひせむ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;言ひける&lt;/span&gt;を、この児、心寄せに聞きけり。&lt;ruby class="gl"&gt;さりとて&lt;rt&gt;とはいっても&lt;/rt&gt;&lt;/ruby&gt;、し出ださむを待ちて寝ざらむも、わろかりなむと思ひて、片方に寄りて、寝たるよしにて、出で来るを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;待ちける&lt;/span&gt;に、すでにし出だしたるさまにて、ひしめき合ひたり。&lt;/p&gt;&lt;p&gt;この児、&lt;ruby class="gl"&gt;さだめて&lt;rt&gt;きっと&lt;/rt&gt;&lt;/ruby&gt;驚かさむずらむと待ちゐたるに、僧の、「もの申しさぶらはむ。驚かせたまへ」と言ふを、うれしとは思へども、ただ一度に&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;いらへむ&lt;/span&gt;も、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;待ちけるかともぞ思ふ&lt;/span&gt;とて、&lt;ruby class="gl"&gt;今一声&lt;rt&gt;もう一声&lt;/rt&gt;&lt;/ruby&gt;呼ばれていらへむと、念じて寝たるほどに、「や、な起こしたてまつりそ。幼き人は寝入りたまひにけり」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;言ふ声&lt;/span&gt;のしければ、あな、わびしと思ひて、いま一度&lt;ruby class="gl"&gt;起こせかし&lt;rt&gt;起こしてほしい&lt;/rt&gt;&lt;/ruby&gt;と、思ひ寝に聞けば、ひしひしと、ただ食ひに食ふ音のしければ、ずちなくて、無期ののちに、「えい」といらへたりければ、僧たち笑ふこと限りなし。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -1206,7 +1258,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;ある川のほとりに、蟻遊ぶことありけり。&lt;ruby class="gl"&gt;にはかに&lt;rt&gt;急に&lt;/rt&gt;&lt;/ruby&gt;水かさまさりて、かの蟻を&lt;ruby class="gl"&gt;誘ひ流る&lt;rt&gt;さらって流す&lt;/rt&gt;&lt;/ruby&gt;。&lt;ruby class="gl"&gt;浮きぬ沈みぬ&lt;rt&gt;浮いたり沈んだり&lt;/rt&gt;&lt;/ruby&gt;する所に、鳩、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;こずゑ&lt;/span&gt;よりこれを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;見て&lt;/span&gt;、「あはれなるありさまかな」と、こずゑをちと食ひ切つて川の中へ落としければ、蟻これに乗りて、渚に上がりぬ。&lt;/p&gt;&lt;p&gt;かかりける所に、ある人、竿の先に鳥もちを付けて、かの鳩をささんとす。蟻、&lt;ruby class="gl"&gt;心に思ふやう&lt;rt&gt;思うことには&lt;/rt&gt;&lt;/ruby&gt;、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;ただ今の恩を送らん&lt;/span&gt;」と思ひ、かの人の足にしつかと&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;食ひつきければ&lt;/span&gt;、おびえあがつて、竿をかしこに投げ捨てけり。鳩これを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;悟りて&lt;/span&gt;、はるかの空へぞ&lt;ruby class="gl"&gt;逃げ延びにける&lt;rt&gt;逃げのびた&lt;/rt&gt;&lt;/ruby&gt;。&lt;/p&gt;&lt;p&gt;そのごとく、人の恩を受けたらん者は、いかさまにもその報いをなすべきなり。&lt;/p&gt;</t>
+          <t>&lt;p&gt;ある川のほとりに、&lt;ruby class="rd"&gt;蟻&lt;rt&gt;あり&lt;/rt&gt;&lt;/ruby&gt;遊ぶことありけり。&lt;ruby class="gl"&gt;にはかに&lt;rt&gt;急に&lt;/rt&gt;&lt;/ruby&gt;水かさまさりて、かの蟻を&lt;ruby class="gl"&gt;誘ひ流る&lt;rt&gt;さらって流す&lt;/rt&gt;&lt;/ruby&gt;。&lt;ruby class="gl"&gt;浮きぬ沈みぬ&lt;rt&gt;浮いたり沈んだり&lt;/rt&gt;&lt;/ruby&gt;する所に、&lt;ruby class="rd"&gt;鳩&lt;rt&gt;はと&lt;/rt&gt;&lt;/ruby&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;こずゑ&lt;/span&gt;よりこれを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;見て&lt;/span&gt;、「あはれなるありさまかな」と、こずゑをちと食ひ切つて川の中へ落としければ、蟻これに乗りて、&lt;ruby class="rd"&gt;渚&lt;rt&gt;なぎさ&lt;/rt&gt;&lt;/ruby&gt;に上がりぬ。&lt;/p&gt;&lt;p&gt;かかりける所に、ある人、&lt;ruby class="rd"&gt;竿&lt;rt&gt;さを&lt;/rt&gt;&lt;/ruby&gt;の先に鳥もちを付けて、かの鳩をささんとす。蟻、&lt;ruby class="gl"&gt;心に思ふやう&lt;rt&gt;思うことには&lt;/rt&gt;&lt;/ruby&gt;、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;ただ今の恩を送らん&lt;/span&gt;」と思ひ、かの人の足にしつかと&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;食ひつきければ&lt;/span&gt;、おびえあがつて、竿をかしこに投げ捨てけり。鳩これを&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;悟りて&lt;/span&gt;、はるかの空へぞ&lt;ruby class="gl"&gt;逃げ延びにける&lt;rt&gt;逃げのびた&lt;/rt&gt;&lt;/ruby&gt;。&lt;/p&gt;&lt;p&gt;そのごとく、人の恩を受けたらん者は、いかさまにもその報いをなすべきなり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1256,7 +1308,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;今は昔、小野篁といふ人&lt;ruby class="gl"&gt;おはしけり&lt;rt&gt;いらっしゃった&lt;/rt&gt;&lt;/ruby&gt;。嵯峨の帝の御時に、内裏に札を立てたりけるに、「無悪善」と書きたりけり。帝、篁に、「読め」と&lt;ruby class="gl"&gt;仰せられたりければ&lt;rt&gt;おっしゃったので&lt;/rt&gt;&lt;/ruby&gt;、「読みは読み候ひなん。されど、恐れにて候へば、え申し候はじ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;奏しければ&lt;/span&gt;、「ただ申せ」と、たびたび仰せられければ、「さがなくて&lt;ruby class="gl"&gt;よからん&lt;rt&gt;よいだろう&lt;/rt&gt;&lt;/ruby&gt;と申して候ふぞ。されば、君を呪ひ参らせて候ふなり」と申しければ、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;おのれ放ちては、誰か書かん&lt;/span&gt;」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;仰せられければ&lt;/span&gt;、「さればこそ、申し候はじとは申して候ひつれ」と申すに、帝、「さて、何も書きたらん物は、読みてんや」と仰せられければ、「&lt;ruby class="gl"&gt;何にても&lt;rt&gt;何であっても&lt;/rt&gt;&lt;/ruby&gt;読み候ひなん」と申しければ、片仮名の子文字を十二書かせ&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;給ひて&lt;/span&gt;、「読め」と仰せられければ、「ねこの子のこねこ、ししの子のこじし」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;読みたりければ&lt;/span&gt;、帝、ほほ笑ませ給ひて、事なくてやみにけり。&lt;/p&gt;</t>
+          <t>&lt;p&gt;今は昔、&lt;ruby class="rd"&gt;小野篁&lt;rt&gt;をののたかむら&lt;/rt&gt;&lt;/ruby&gt;といふ人&lt;ruby class="gl"&gt;おはしけり&lt;rt&gt;いらっしゃった&lt;/rt&gt;&lt;/ruby&gt;。&lt;ruby class="rd"&gt;嵯峨&lt;rt&gt;さが&lt;/rt&gt;&lt;/ruby&gt;の帝の御時に、&lt;ruby class="rd"&gt;内裏&lt;rt&gt;だいり&lt;/rt&gt;&lt;/ruby&gt;に札を立てたりけるに、「無悪善」と書きたりけり。帝、篁に、「読め」と&lt;ruby class="gl"&gt;仰せられたりければ&lt;rt&gt;おっしゃったので&lt;/rt&gt;&lt;/ruby&gt;、「読みは読み候ひなん。されど、恐れにて候へば、え申し候はじ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;奏しければ&lt;/span&gt;、「ただ申せ」と、たびたび仰せられければ、「さがなくて&lt;ruby class="gl"&gt;よからん&lt;rt&gt;よいだろう&lt;/rt&gt;&lt;/ruby&gt;と申して候ふぞ。されば、君を呪ひ参らせて候ふなり」と申しければ、「&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;おのれ放ちては、誰か書かん&lt;/span&gt;」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;仰せられければ&lt;/span&gt;、「さればこそ、申し候はじとは申して候ひつれ」と申すに、帝、「さて、何も書きたらん物は、読みてんや」と仰せられければ、「&lt;ruby class="gl"&gt;何にても&lt;rt&gt;何であっても&lt;/rt&gt;&lt;/ruby&gt;読み候ひなん」と申しければ、片仮名の子文字を十二書かせ&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;給ひて&lt;/span&gt;、「読め」と仰せられければ、「ねこの子のこねこ、ししの子のこじし」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;読みたりければ&lt;/span&gt;、帝、ほほ笑ませ給ひて、事なくてやみにけり。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1306,7 +1358,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;ある人、弓射ることを習ふに、諸矢をたばさみて的に&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;向かふ&lt;/span&gt;。師の&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;言はく&lt;/span&gt;、「初心の人、二つの矢を持つことなかれ。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;後の矢を頼みて、初めの矢に等閑の心あり&lt;/span&gt;。毎度ただ得失なく、この一矢に定むべしと思へ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;言ふ&lt;/span&gt;。&lt;ruby class="gl"&gt;わづかに&lt;rt&gt;わずか&lt;/rt&gt;&lt;/ruby&gt;二つの矢、師の前にて一つをおろかにせんと&lt;ruby class="gl"&gt;思はんや&lt;rt&gt;思うだろうか&lt;/rt&gt;&lt;/ruby&gt;。懈怠の心、みづから知らずといへども、師&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;これを知る&lt;/span&gt;。この戒め、万事にわたるべし。&lt;/p&gt;&lt;p&gt;道を学する人、夕べには朝あらんことを思ひ、朝には夕べあらんことを思ひて、重ねてねんごろに修せんことを期す。&lt;ruby class="gl"&gt;いはんや&lt;rt&gt;まして&lt;/rt&gt;&lt;/ruby&gt;一刹那のうちにおいて、懈怠の心あることを知らんや。なんぞ、ただ今の一念において、直ちにすることの、はなはだ難き。&lt;/p&gt;</t>
+          <t>&lt;p&gt;ある人、弓射ることを習ふに、&lt;ruby class="rd"&gt;諸矢&lt;rt&gt;もろや&lt;/rt&gt;&lt;/ruby&gt;をたばさみて的に&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;向かふ&lt;/span&gt;。師の&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;言はく&lt;/span&gt;、「初心の人、二つの矢を持つことなかれ。&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;後の矢を頼みて、初めの矢に&lt;ruby class="rd"&gt;等閑&lt;rt&gt;なほざり&lt;/rt&gt;&lt;/ruby&gt;の心あり&lt;/span&gt;。毎度ただ得失なく、この一矢に定むべしと思へ」と&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;言ふ&lt;/span&gt;。&lt;ruby class="gl"&gt;わづかに&lt;rt&gt;わずか&lt;/rt&gt;&lt;/ruby&gt;二つの矢、師の前にて一つをおろかにせんと&lt;ruby class="gl"&gt;思はんや&lt;rt&gt;思うだろうか&lt;/rt&gt;&lt;/ruby&gt;。&lt;ruby class="rd"&gt;懈怠&lt;rt&gt;けだい&lt;/rt&gt;&lt;/ruby&gt;の心、みづから知らずといへども、師&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;これを知る&lt;/span&gt;。この戒め、万事にわたるべし。&lt;/p&gt;&lt;p&gt;道を学する人、夕べには朝あらんことを思ひ、朝には夕べあらんことを思ひて、重ねてねんごろに修せんことを期す。&lt;ruby class="gl"&gt;いはんや&lt;rt&gt;まして&lt;/rt&gt;&lt;/ruby&gt;一刹那のうちにおいて、懈怠の心あることを知らんや。なんぞ、ただ今の一念において、直ちにすることの、はなはだ難き。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1406,7 +1458,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;九月二十日のころ、ある人に誘はれたてまつりて、明くるまで&lt;ruby class="gl"&gt;月見ありく&lt;rt&gt;月を見て歩き回る&lt;/rt&gt;&lt;/ruby&gt;こと侍りしに、思し出づる所ありて、案内せさせて&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;入り給ひぬ&lt;/span&gt;。荒れたる庭の露しげきに、わざとならぬ匂ひ、しめやかに&lt;ruby class="gl"&gt;うち薫りて&lt;rt&gt;漂って&lt;/rt&gt;&lt;/ruby&gt;、忍びたるけはひ、&lt;ruby class="gl"&gt;いとものあはれなり&lt;rt&gt;たいそう趣深い&lt;/rt&gt;&lt;/ruby&gt;。&lt;/p&gt;&lt;p&gt;よきほどにて&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;出で給ひぬれ&lt;/span&gt;ど、&lt;ruby class="gl"&gt;なほ&lt;rt&gt;やはり&lt;/rt&gt;&lt;/ruby&gt;事ざまの優におぼえて、物の隠れよりしばし&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;見ゐたる&lt;/span&gt;に、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;妻戸をいま少し押し開けて&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;月見る&lt;/span&gt;&lt;ruby class="gl"&gt;けしきなり&lt;rt&gt;様子である&lt;/rt&gt;&lt;/ruby&gt;。やがてかけこもらましかば、口惜しからまし。あとまで見る人ありとは、いかでか知らん。かやうのことは、ただ朝夕の心づかひによるべし。&lt;/p&gt;&lt;p&gt;その人、&lt;ruby class="gl"&gt;ほどなく&lt;rt&gt;まもなく&lt;/rt&gt;&lt;/ruby&gt;失せにけりと聞き侍りし。&lt;/p&gt;</t>
+          <t>&lt;p&gt;&lt;ruby class="rd"&gt;九月&lt;rt&gt;ながつき&lt;/rt&gt;&lt;/ruby&gt;二十日のころ、ある人に誘はれたてまつりて、明くるまで&lt;ruby class="gl"&gt;月見ありく&lt;rt&gt;月を見て歩き回る&lt;/rt&gt;&lt;/ruby&gt;こと侍りしに、思し出づる所ありて、案内せさせて&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ａ&lt;/span&gt;入り給ひぬ&lt;/span&gt;。荒れたる庭の露しげきに、わざとならぬ匂ひ、しめやかに&lt;ruby class="gl"&gt;うち薫りて&lt;rt&gt;漂って&lt;/rt&gt;&lt;/ruby&gt;、忍びたるけはひ、&lt;ruby class="gl"&gt;いとものあはれなり&lt;rt&gt;たいそう趣深い&lt;/rt&gt;&lt;/ruby&gt;。&lt;/p&gt;&lt;p&gt;よきほどにて&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｂ&lt;/span&gt;出で給ひぬれ&lt;/span&gt;ど、&lt;ruby class="gl"&gt;なほ&lt;rt&gt;やはり&lt;/rt&gt;&lt;/ruby&gt;事ざまの優におぼえて、物の隠れよりしばし&lt;span class="ul"&gt;&lt;span class="mk"&gt;①&lt;/span&gt;見ゐたる&lt;/span&gt;に、&lt;span class="ul"&gt;&lt;span class="mk"&gt;②&lt;/span&gt;&lt;ruby class="rd"&gt;妻戸&lt;rt&gt;つまど&lt;/rt&gt;&lt;/ruby&gt;をいま少し押し開けて&lt;/span&gt;、&lt;span class="ul"&gt;&lt;span class="mk"&gt;Ｃ&lt;/span&gt;月見る&lt;/span&gt;&lt;ruby class="gl"&gt;けしきなり&lt;rt&gt;様子である&lt;/rt&gt;&lt;/ruby&gt;。やがてかけこもらましかば、口惜しからまし。あとまで見る人ありとは、いかでか知らん。かやうのことは、ただ朝夕の心づかひによるべし。&lt;/p&gt;&lt;p&gt;その人、&lt;ruby class="gl"&gt;ほどなく&lt;rt&gt;まもなく&lt;/rt&gt;&lt;/ruby&gt;失せにけりと聞き侍りし。&lt;/p&gt;</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1749,27 +1801,27 @@
       <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「この文章で、良秀はどのような人物として描かれているでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「家が焼けているのに騒がず、それどころか笑っています。傍線部②の言葉から考えると、良秀は&lt;span class="blank"&gt;　　&lt;/span&gt;人物として描かれているのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。だからこそ最後に、良秀のかいた不動明王の絵が名作として語り伝えられているのですね。」</t>
+          <t>&lt;span class="sp"&gt;先　生&lt;/span&gt;「この文章は、良秀という絵仏師を通して、何を描こうとしているのでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「本文中に『これこそせうとくよ』とあります。良秀は、家が焼けるのを見ながら、火炎の描き方がわかったことをもうけものだと言っています。つまりこの話は、&lt;span class="blank"&gt;　　&lt;/span&gt;ということだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先　生&lt;/span&gt;「そのとおりです。だからこそ最後に、良秀のかいた不動明王の絵が名作として語り伝えられているのですね。」</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>損得に敏感で、何事も金銭に結びつけて考える</t>
+          <t>思いがけない不幸も、考え方しだいで幸運に変えることができる</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>家族思いで、まわりの人への気配りを忘れない</t>
+          <t>絵は実物を見て描かなければ、決して人の心を打つものにはならない</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>何事にも動じず、人の意見にはいっさい耳を貸さない</t>
+          <t>名人と呼ばれる人は、家族や財産を失っても平気でいられるものだ</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>家族や財産よりも、絵の道を究めることを大切にする</t>
+          <t>芸の道を究めようとする者は、自分の損得を超えたところに心を向けている</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -1779,7 +1831,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>良秀は、妻子も仏の絵も家の中にあるのに気にかけず、炎の描き方を会得したことだけを「せうとく」と言い切ります。&lt;b&gt;芸の道を何よりも優先する姿&lt;/b&gt;が描かれた話です。</t>
+          <t>良秀は、妻子も仏の絵も家の中にあるのに気にかけず、火炎の描き方を会得したことだけを「せうとく」と言い切ります。&lt;b&gt;芸の道を何よりも優先する姿&lt;/b&gt;を描いた話です。家や財産の損得の話ではありません。</t>
         </is>
       </c>
       <c r="N5" s="4" t="n">
@@ -2005,27 +2057,27 @@
       <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「小式部内侍の歌には、どのような工夫がありますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「地名の『いくの』に『行く野』を、『ふみ』に『踏み』と『文』を掛けています。そのうえでこの歌は&lt;span class="blank"&gt;　　&lt;/span&gt;という意味になり、定頼のからかいへの切り返しになっています。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。だから定頼は返歌もできなかったのですね。」</t>
+          <t>&lt;span class="sp"&gt;先　生&lt;/span&gt;「この話で、作者は小式部内侍のどのようなところを伝えたかったのでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「本文中に『小式部、これより歌よみの世おぼえ出で来にけり』とあります。つまりこの話は、&lt;span class="blank"&gt;　　&lt;/span&gt;ということだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先　生&lt;/span&gt;「そのとおりです。からかった定頼が、返歌もできずに逃げ出したことが、それをよく表していますね。」</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>天の橋立の景色を実際に見なければ、すぐれた歌はよむことができない</t>
+          <t>すぐれた歌をよむには、その土地を実際に訪れなければならない</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>母のいる丹後は遠いので、天の橋立を踏んだことも、母からの手紙を見たこともない</t>
+          <t>その場で見事な歌をよむ力が、人の評判を決めることもある</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>母のいる丹後は近いので、いつでも自由に手紙のやりとりができる</t>
+          <t>親の名声が高い子どもほど、苦労することになる</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>母に代作を頼んだのだから、返事が来るまでもうしばらく待ってほしい</t>
+          <t>人にからかわれたときは、言い返さずに黙っているのがよい</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -2035,7 +2087,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>「まだ&lt;b&gt;ふみ&lt;/b&gt;もみず」に「（天の橋立を）踏み」と「（母からの）文」が掛けてあります。&lt;b&gt;手紙のやりとりすらしていない＝代作などしていない&lt;/b&gt;、という反論になっているのです。</t>
+          <t>結びの「歌よみの世おぼえ出で来にけり」＝&lt;b&gt;歌人としての評判が世に立った&lt;/b&gt;が手がかり。代作を疑われた小式部内侍が、その場で即興の名歌を返したことで評価を得た、という話です。</t>
         </is>
       </c>
       <c r="N9" s="4" t="n">
@@ -2261,27 +2313,27 @@
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「作者は、この男の言葉をどのように受け止めていますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「『あやしき下臈なれども、聖人の戒めにかなへり』とあります。そのあとに蹴鞠の例も挙げているので、作者は&lt;span class="blank"&gt;　　&lt;/span&gt;と考えているのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。」</t>
+          <t>&lt;span class="sp"&gt;先　生&lt;/span&gt;「この文章で、作者は何を伝えようとしているのでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「本文中に『あやしき下臈なれども、聖人の戒めにかなへり』とあり、そのあとに蹴鞠の例も挙げられています。つまり作者は、&lt;span class="blank"&gt;　　&lt;/span&gt;ということだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先　生&lt;/span&gt;「そのとおりです。木登りの話が、そのまま他の物事にもあてはまるという形になっていますね。」</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>この教えは木登りだけでなく、あらゆる事にあてはまる</t>
+          <t>危険な場面よりも、もう安心だと思ったときにこそ失敗は起こる</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>木登りや蹴鞠のような技芸は、書物による学問よりもすぐれている</t>
+          <t>身分の低い者の言うことは、すべて聞き入れるべきである</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>危険な仕事をする者こそ、聖人と同じように尊敬されるべきだ</t>
+          <t>技芸を身につけるには、必ずすぐれた師につかなければならない</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>身分の低い者の言うことは、たいてい聖人の教えと同じ内容になる</t>
+          <t>高い所での作業は、経験を積んだ者にまかせるのがよい</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -2291,7 +2343,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>「あやしき下臈&lt;b&gt;なれども&lt;/b&gt;（＝身分は低いけれども）」という逆接に加え、蹴鞠という別の分野の例を挙げることで、&lt;b&gt;他の物事にも広くあてはまる&lt;/b&gt;教えだと示しています。</t>
+          <t>男の言葉「あやまちは、安き所になりて、必ず仕る事に候ふ」が話の中心。作者はそれを「聖人の戒めにかなへり」と評価し、蹴鞠の例を挙げて&lt;b&gt;あらゆる事にあてはまる教訓&lt;/b&gt;だと示しています。</t>
         </is>
       </c>
       <c r="N13" s="4" t="n">
@@ -2517,27 +2569,27 @@
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「最後の一文『少しのことにも、先達はあらまほしきことなり』は、どういうことですか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「法師は&lt;span class="blank"&gt;　　&lt;/span&gt;のに、そのことに気づかないまま満足して帰っています。だから作者は、ちょっとしたことでも案内者はいてほしいものだ、と述べているのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。」</t>
+          <t>&lt;span class="sp"&gt;先　生&lt;/span&gt;「この文章で、作者は何を伝えようとしているのでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「本文中に『少しのことにも、先達はあらまほしきことなり』とあります。法師のふるまいから考えると、作者は、&lt;span class="blank"&gt;　　&lt;/span&gt;ということだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先　生&lt;/span&gt;「そのとおりです。法師は最後まで、自分が目的を果たしていないことに気づいていませんね。」</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>同じ場所を何度もお参りして、時間を無駄にしてしまった</t>
+          <t>参拝するときは、必ず仲間と連れ立って行くほうがよい</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>山の上からの景色を見ることを、あきらめてしまった</t>
+          <t>年をとってからでは、遠出をすることは難しくなる</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>ふもとの寺社を拝んだだけで、肝心の石清水八幡宮を拝んでいない</t>
+          <t>自分だけの思い込みで済ませず、道案内をしてくれる人に導かれることが大切だ</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>仲間に自慢話をして、かえって笑われてしまった</t>
+          <t>長年の願いは、思い立ったらすぐに実行に移すべきだ</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -2547,7 +2599,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>石清水八幡宮は&lt;b&gt;男山の山上&lt;/b&gt;にあります（注）。法師はふもとの極楽寺・高良を拝んだだけで「かばかり（これだけのものだ）」と早合点し、本来の目的を果たせずに帰ったのです。</t>
+          <t>法師は、ほかの参拝者が山へ登るわけを知りたいと思いながら、誰にもたずねずに帰りました。その結果、肝心の石清水八幡宮を拝まないまま満足しています。&lt;b&gt;ちょっとしたことでも案内者が必要だ&lt;/b&gt;というのが結びです。</t>
         </is>
       </c>
       <c r="N17" s="4" t="n">
@@ -2773,27 +2825,27 @@
       <c r="F21" s="4" t="inlineStr"/>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「最後に僧たちが『笑ふこと限りなし』となったのは、なぜでしょう。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「児が『えい』と返事をしたのが&lt;span class="blank"&gt;　　&lt;/span&gt;だったので、寝たふりをして待っていたことが、すっかりわかってしまったからだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。児のいじらしくもおかしみのある姿が、生き生きと描かれていますね。」</t>
+          <t>&lt;span class="sp"&gt;先　生&lt;/span&gt;「この話は、児のどのような姿を描いているのでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「本文中に『待ちけるかともぞ思ふ』とあり、最後は『無期ののちに、「えい」といらへたりければ』となっています。つまりこの話は、&lt;span class="blank"&gt;　　&lt;/span&gt;ということだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先　生&lt;/span&gt;「そのとおりです。児のいじらしくもおかしみのある姿が、生き生きと描かれていますね。」</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>寝言のように小さく、ほとんど聞き取れない返事</t>
+          <t>目上の人の前では、遠慮して自分の望みを言わないほうがよい</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>僧たちが食べる音がしてから、ずいぶんたったあとの返事</t>
+          <t>体裁を気にして素直になれないうちに、かえって機会を逃してしまう</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>声をかけられてすぐの、たいへん元気のよい返事</t>
+          <t>寝たふりをして人をだまそうとすると、必ず見破られるものだ</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>僧たちの問いかけとは、まったく関係のない返事</t>
+          <t>子どもは食べ物のことになると、我を忘れて夢中になってしまう</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2803,7 +2855,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>「&lt;b&gt;無期ののちに&lt;/b&gt;（＝ずいぶん時間がたってから）」がポイント。食べる音がしてからようやく返事をしたので、寝たふりをして待っていたことが見え見えになってしまったのです。</t>
+          <t>児は「待っていたと思われたくない」という見えから返事を我慢し、結局ぼたもちを食べる音を聞くはめになります。&lt;b&gt;体裁を気にしたために機会を逃す&lt;/b&gt;おかしみを描いた話です。</t>
         </is>
       </c>
       <c r="N21" s="4" t="n">
@@ -3029,17 +3081,17 @@
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「この話の結びには、作者の考えが述べられていますね。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「はい。『人の恩を受けたらん者は、いかさまにもその報いをなすべきなり』とあります。つまり&lt;span class="blank"&gt;　　&lt;/span&gt;ということですね。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。物語の出来事から教訓を引き出す、という書き方になっています。」</t>
+          <t>&lt;span class="sp"&gt;先　生&lt;/span&gt;「この話で、作者は何を伝えようとしているのでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「本文中に『人の恩を受けたらん者は、いかさまにもその報いをなすべきなり』とあります。つまり、&lt;span class="blank"&gt;　　&lt;/span&gt;ということだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先　生&lt;/span&gt;「そのとおりです。物語の出来事から教訓を引き出す、という書き方になっていますね。」</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>恩を受けた者は、どのような方法であってもその恩に報いるべきだ</t>
+          <t>恩を受けた者は、自分にできるやり方で必ずその恩に報いるべきだ</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>恩を受けたら、必ずそれと同じだけの品物を返すべきだ</t>
+          <t>恩を受けたら、必ずそれと同じだけの品物を返さなければならない</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3059,7 +3111,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>「&lt;b&gt;いかさまにも&lt;/b&gt;」＝どのようにしてでも。体の小さな蟻が、自分にできるやり方で恩を返した点が要旨です。</t>
+          <t>「&lt;b&gt;いかさまにも&lt;/b&gt;」＝どのようにしてでも。体の小さな蟻が、かみつくという自分にできるやり方で鳩を助けた点が要旨です。品物を返せとも、損得のためとも述べていません。</t>
         </is>
       </c>
       <c r="N25" s="4" t="n">
@@ -3285,27 +3337,27 @@
       <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「最後に帝が『ほほ笑ませ給ひて、事なくてやみにけり』となったのは、なぜでしょう。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「帝は篁を疑っていましたが、篁が&lt;span class="blank"&gt;　　&lt;/span&gt;ので、感心して機嫌を直したのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。題名の『広才』とは、学識が広いという意味です。」</t>
+          <t>&lt;span class="sp"&gt;先　生&lt;/span&gt;「この話で、作者は篁のどのようなところを伝えたかったのでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「本文中に『帝、ほほ笑ませ給ひて、事なくてやみにけり』とあります。つまりこの話は、&lt;span class="blank"&gt;　　&lt;/span&gt;ということだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先　生&lt;/span&gt;「そのとおりです。題名の「広才」とは、学識が広いという意味です。」</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>札を書いたのは自分だと素直に認めて謝った</t>
+          <t>天皇の命令には、どんなときでも従わなければならない</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>帝をたたえるすぐれた歌を、その場でよんでみせた</t>
+          <t>いたずら書きをした者は、必ず罰を受けることになる</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>「子」の字十二文字をみごとに読み解いてみせた</t>
+          <t>すぐれた学識は、疑いをかけられるような窮地さえも切り抜けさせる</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>札を書いた犯人を突き止めて帝に報告した</t>
+          <t>難しい文字は、学者でなければ読むことができない</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3315,7 +3367,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>帝が出した「子子子子子子子子子子子子」という難題を、篁は「&lt;b&gt;ねこの子のこねこ、ししの子のこじし&lt;/b&gt;」と読み解きました。その才知に感心したので、疑いはうやむやになって終わったのです。</t>
+          <t>篁は札を読んだために「書いたのはおまえだろう」と疑われますが、帝が出した「子」十二文字の難題をみごとに読み解き、&lt;b&gt;その才知によって疑いをうやむやにして&lt;/b&gt;切り抜けています。</t>
         </is>
       </c>
       <c r="N29" s="4" t="n">
@@ -3541,27 +3593,27 @@
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「後半で作者は、弓の話をどのように広げていますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「仏道を学ぶ人の話に広げ、『ただ今の一念において、直ちにすること』の難しさを述べています。つまり作者は&lt;span class="blank"&gt;　　&lt;/span&gt;と言いたいのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。『この戒め、万事にわたるべし』という一文が、そのつなぎ目になっています。」</t>
+          <t>&lt;span class="sp"&gt;先　生&lt;/span&gt;「この文章で、作者は何を伝えようとしているのでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「本文中に『この戒め、万事にわたるべし』とあり、そのあとは仏道を学ぶ人の話へと広がっています。つまり作者は、&lt;span class="blank"&gt;　　&lt;/span&gt;ということだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先　生&lt;/span&gt;「そのとおりです。二本目の矢をあてにすることと、明日をあてにすることが、同じ形で語られていますね。」</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>弓の稽古は、仏道の修行よりもはるかに難しいものである</t>
+          <t>弓の稽古では、必ず一本の矢だけを持つようにすべきだ</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>師の教えといっても、必ずしも正しいとは限らない</t>
+          <t>なまけ心は自分では気づけないので、よい師を選ぶことが何より大切だ</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>朝と夕方とでは、人の心は大きく変わってしまうものだ</t>
+          <t>朝と夕方とでは人の心が変わるので、修行は朝に行うのがよい</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>何事も、次の機会をあてにせず、今この一瞬に実行することが大切だ</t>
+          <t>次の機会をあてにする心を捨て、今この一瞬にすぐ実行することが大切だ</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3571,7 +3623,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>「二本目の矢をあてにする」と「明日をあてにする」は同じ構造です。&lt;b&gt;今この一瞬に、すぐ実行せよ&lt;/b&gt;というのが、弓の話から導かれた作者の主張です。</t>
+          <t>弓の「後の矢を頼みて」と、仏道の「夕べには朝あらんことを思ひ」は同じ構造です。結びの「ただ今の一念において、直ちにすることの、はなはだ難き」から、&lt;b&gt;今この一瞬に実行せよ&lt;/b&gt;という主張が読み取れます。</t>
         </is>
       </c>
       <c r="N33" s="4" t="n">
@@ -3797,27 +3849,27 @@
       <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「四人の僧が、次々に口をきいてしまいますね。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「はい。しかも、あとの僧ほど&lt;span class="blank"&gt;　　&lt;/span&gt;という形になっていて、そのくり返しがこの話のおもしろさを生んでいると思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。」</t>
+          <t>&lt;span class="sp"&gt;先　生&lt;/span&gt;「この話は、人間のどのようなところを描いているのでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「本文中に『われ一人こそもの言はね』とあります。つまりこの話は、&lt;span class="blank"&gt;　　&lt;/span&gt;ということだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先　生&lt;/span&gt;「そのとおりです。四人が順に同じ失敗をくり返すところに、おかしみがありますね。」</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>人を責めることに気を取られ、自分も同じ過ちを犯していることに気づいていない</t>
+          <t>人の過ちばかりが目につき、同じ過ちを犯している自分には気づかない</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>位が低くなっていき、発言の重みが失われていく</t>
+          <t>位の高い者ほど、決まりを守ろうとする気持ちが強いものである</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>修行の厳しさに耐えかねて、寺を出ていこうとしている</t>
+          <t>修行は一人で行うよりも、大勢で行うほうが長続きする</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>声がしだいに小さくなり、少しずつ無言の行に戻っている</t>
+          <t>言葉を使わなければ、人は互いに気持ちを伝え合うことができない</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3827,7 +3879,7 @@
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>下座→第二→第三→上座と、&lt;b&gt;人を非難するその言葉じたいが行を破っている&lt;/b&gt;という同じ失敗をくり返します。最後の上座の僧がその極みで、他人には厳しく自分には気づかない人間の姿を笑った話です。</t>
+          <t>下座の僧を責めた第二の僧も、その二人を責めた第三の僧も、責めた瞬間に自分が行を破っています。最後の上座の僧がその極みで、&lt;b&gt;他人には厳しく、自分の同じ過ちには気づかない&lt;/b&gt;人間の姿を笑った話です。</t>
         </is>
       </c>
       <c r="N37" s="4" t="n">
@@ -4053,27 +4105,27 @@
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>&lt;span class="sp"&gt;先生&lt;/span&gt;「作者は、この家の女主人のふるまいをどのように評価していますか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「『あとまで見る人ありとは、いかでか知らん』『ただ朝夕の心づかひによるべし』とあるので、作者は&lt;span class="blank"&gt;　　&lt;/span&gt;と考えているのだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先生&lt;/span&gt;「そのとおりです。」</t>
+          <t>&lt;span class="sp"&gt;先　生&lt;/span&gt;「この文章で、作者は何を伝えようとしているのでしょうか。」&lt;br&gt;&lt;span class="sp"&gt;Ａさん&lt;/span&gt;「本文中に『かやうのことは、ただ朝夕の心づかひによるべし』とあります。家の主のふるまいから考えると、作者は、&lt;span class="blank"&gt;　　&lt;/span&gt;ということだと思います。」&lt;br&gt;&lt;span class="sp"&gt;先　生&lt;/span&gt;「そのとおりです。「あとまで見る人ありとは、いかでか知らん」という一文が、それをよく表していますね。」</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>客が帰ったあとは誰も見ていないのだから、気を抜いてもかまわない</t>
+          <t>客を迎えるときは、香をたいてもてなすのが礼儀である</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>夜遅くまで起きて月を眺めるのは、感心できないことである</t>
+          <t>趣を解する人は、若くして亡くなってしまうことが多い</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>月見をするなら、一人よりも大勢で楽しむほうがよい</t>
+          <t>月を眺めるなら、荒れた庭のある古い家がふさわしい</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>人が見ていないときのふるまいこそが、その人のふだんの心づかいを表す</t>
+          <t>人が見ていないときのふるまいにこそ、ふだんの心がけが表れる</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4083,7 +4135,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>「&lt;b&gt;朝夕の心づかひ&lt;/b&gt;」＝ふだんからの心がけ。誰も見ていないと思われる場面でなお美しくふるまえるのは、日ごろの心がけによるものだ、というのが作者の考えです。</t>
+          <t>家の主は、客が帰ったあとも戸を開けて月を眺めていました。見られているとは思っていないその場面でなお美しくふるまえるのは、&lt;b&gt;ふだんからの心がけ（朝夕の心づかひ）&lt;/b&gt;によるものだ、というのが作者の考えです。</t>
         </is>
       </c>
       <c r="N41" s="4" t="n">
